--- a/테스트/테스트3차/5회/김태오/테스트시나리오_김태오.xlsx
+++ b/테스트/테스트3차/5회/김태오/테스트시나리오_김태오.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'환경설정'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'테스트시나리오'!$A$2:$T$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'테스트시나리오'!$A$2:$T$32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'테스트시나리오'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'결함관리'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'캡처목록'!$1:$1</definedName>
@@ -349,14 +349,11 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -368,7 +365,6 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -405,9 +401,13 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -834,7 +834,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CASE-01   |   End-to-End 통합 테스트   |   TC-001 ~ TC-018</t>
+          <t>CASE-01   |   End-to-End 통합 테스트   |   TC-001 ~ TC-019</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>18건 (TC-001 ~ TC-018)</t>
+          <t>19건 (TC-001 ~ TC-019)</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T33"/>
+  <dimension ref="A1:T32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1589,27 +1589,27 @@
       </c>
       <c r="C3" s="22" t="inlineStr">
         <is>
-          <t>거래처</t>
+          <t>접수</t>
         </is>
       </c>
       <c r="D3" s="23" t="inlineStr">
         <is>
-          <t>거래처 등록</t>
+          <t>처방자료 업로드 - 환자 조회</t>
         </is>
       </c>
       <c r="E3" s="23" t="inlineStr">
         <is>
-          <t>테스트 설정이 [테스트 자세]일 것</t>
+          <t>테스트 설정이 [테스트 자세]일 것 (환경설정 시트)</t>
         </is>
       </c>
       <c r="F3" s="23" t="inlineStr">
         <is>
-          <t>환자ㆍ처방 › 거래처 관리</t>
+          <t>환자ㆍ처방 › 처방자료 업로드</t>
         </is>
       </c>
       <c r="G3" s="23" t="inlineStr">
         <is>
-          <t>/patients</t>
+          <t>/prescriptions/upload</t>
         </is>
       </c>
       <c r="H3" s="24" t="n">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="I3" s="23" t="inlineStr">
         <is>
-          <t>거래처 관리 목록에서 신규 등록 창을 연다</t>
+          <t>처방자료 업로드 화면을 연다</t>
         </is>
       </c>
       <c r="J3" s="23" t="inlineStr">
@@ -1627,22 +1627,22 @@
       </c>
       <c r="K3" s="23" t="inlineStr">
         <is>
-          <t>［+ 거래처 등록］</t>
+          <t>좌측 메뉴 ［처방자료 업로드］</t>
         </is>
       </c>
       <c r="L3" s="25" t="inlineStr">
         <is>
-          <t>openAddModal() → openPatientEditor(). 등록이면 빈 창을 연다.</t>
+          <t>업무 시작점. 처방전이 접수되면 이 화면에서 시작한다.</t>
         </is>
       </c>
       <c r="M3" s="26" t="inlineStr">
         <is>
-          <t>［거래처 등록］ 팝업이 열린다</t>
+          <t>업로드 화면이 열리고 [이름 선택]이 비어 있다</t>
         </is>
       </c>
       <c r="N3" s="27" t="inlineStr">
         <is>
-          <t>화면/01_거래처관리-목록.png</t>
+          <t>화면/05_처방자료업로드-빈화면.png</t>
         </is>
       </c>
       <c r="O3" s="28" t="inlineStr"/>
@@ -1665,64 +1665,139 @@
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>사업부·이름·주민등록번호를 입력한다</t>
+          <t>환자를 조회한다</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>사업부: IC (카테터)
-이름: (T3-5)김태오
+          <t>검색어: 김태오</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>［조회］</t>
+        </is>
+      </c>
+      <c r="L4" s="32" t="inlineStr">
+        <is>
+          <t>pkOpen() — 거래처 조회 팝업. 이름 또는 연락처로 검색한다.</t>
+        </is>
+      </c>
+      <c r="M4" s="16" t="inlineStr">
+        <is>
+          <t>★ 검색 결과 0건 — 신규 환자이므로 미등록 상태 (기등록 환자면 TC-002 생략)</t>
+        </is>
+      </c>
+      <c r="N4" s="33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O4" s="34" t="inlineStr"/>
+      <c r="P4" s="35" t="inlineStr"/>
+      <c r="Q4" s="35" t="inlineStr"/>
+      <c r="R4" s="35" t="inlineStr"/>
+      <c r="S4" s="35" t="inlineStr"/>
+      <c r="T4" s="34" t="inlineStr"/>
+    </row>
+    <row r="5" ht="82" customHeight="1">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>TC-002</t>
+        </is>
+      </c>
+      <c r="B5" s="37" t="inlineStr">
+        <is>
+          <t>CASE-01 처방전·일반(10/90)·링크페이</t>
+        </is>
+      </c>
+      <c r="C5" s="38" t="inlineStr">
+        <is>
+          <t>접수</t>
+        </is>
+      </c>
+      <c r="D5" s="39" t="inlineStr">
+        <is>
+          <t>조회 팝업에서 거래처 신규 등록</t>
+        </is>
+      </c>
+      <c r="E5" s="39" t="inlineStr">
+        <is>
+          <t>TC-001 결과 0건 (신규 환자)</t>
+        </is>
+      </c>
+      <c r="F5" s="39" t="inlineStr">
+        <is>
+          <t>처방자료 업로드 › [조회] 팝업</t>
+        </is>
+      </c>
+      <c r="G5" s="39" t="inlineStr">
+        <is>
+          <t>/prescriptions/upload</t>
+        </is>
+      </c>
+      <c r="H5" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="39" t="inlineStr">
+        <is>
+          <t>조회 결과가 없을 때 나타나는 [신규] 버튼을 누른다</t>
+        </is>
+      </c>
+      <c r="J5" s="39" t="inlineStr">
+        <is>
+          <t>이름: (T3-5)김태오
 주민등록번호: 850203-1000001</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="32" t="inlineStr">
-        <is>
-          <t>peBirthFromRrn() — 주민번호 앞 7자리로 생년월일을 자동 계산. 없는 날짜는 역검증으로 제외.</t>
-        </is>
-      </c>
-      <c r="M4" s="33" t="inlineStr">
-        <is>
-          <t>① 생년월일 1985-02-03 자동 입력
-② 만 41세 성년이므로 [보호자] 입력 영역이 표시되지 않음</t>
-        </is>
-      </c>
-      <c r="N4" s="34" t="inlineStr">
-        <is>
-          <t>화면/02_거래처등록-창.png</t>
-        </is>
-      </c>
-      <c r="O4" s="35" t="inlineStr"/>
-      <c r="P4" s="36" t="inlineStr"/>
-      <c r="Q4" s="36" t="inlineStr"/>
-      <c r="R4" s="36" t="inlineStr"/>
-      <c r="S4" s="36" t="inlineStr"/>
-      <c r="T4" s="35" t="inlineStr"/>
-    </row>
-    <row r="5" ht="82" customHeight="1">
-      <c r="A5" s="30" t="n"/>
-      <c r="B5" s="30" t="n"/>
-      <c r="C5" s="30" t="n"/>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="30" t="n"/>
-      <c r="H5" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>나머지 항목을 모두 입력한다</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>성별: 남 / 환자구분: SB-N / 연락 상태: 정상
-연락 선호: 업무폰2586 문자
+      <c r="K5" s="39" t="inlineStr">
+        <is>
+          <t>［신규］</t>
+        </is>
+      </c>
+      <c r="L5" s="41" t="inlineStr">
+        <is>
+          <t>pkCreate() — 조회 결과가 없을 때만 [신규] 버튼이 노출된다. 조회된 사람이 있으면 숨겨 동일인 중복 등록을 막는다. 등록 전 주민번호 앞자리로 중복 여부를 재확인한다.</t>
+        </is>
+      </c>
+      <c r="M5" s="42" t="inlineStr">
+        <is>
+          <t>① 거래처가 등록되고 [이름 선택]에 자동 반영
+② 사업부 IC이면 이름 앞에 (E) 자동 부여</t>
+        </is>
+      </c>
+      <c r="N5" s="43" t="inlineStr">
+        <is>
+          <t>화면/01_거래처관리-목록.png</t>
+        </is>
+      </c>
+      <c r="O5" s="28" t="inlineStr"/>
+      <c r="P5" s="29" t="inlineStr"/>
+      <c r="Q5" s="29" t="inlineStr"/>
+      <c r="R5" s="29" t="inlineStr"/>
+      <c r="S5" s="29" t="inlineStr"/>
+      <c r="T5" s="28" t="inlineStr"/>
+    </row>
+    <row r="6" ht="82" customHeight="1">
+      <c r="A6" s="30" t="n"/>
+      <c r="B6" s="30" t="n"/>
+      <c r="C6" s="30" t="n"/>
+      <c r="D6" s="30" t="n"/>
+      <c r="E6" s="30" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
+      <c r="H6" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>거래처 상세 정보를 보완 입력한다</t>
+        </is>
+      </c>
+      <c r="J6" s="15" t="inlineStr">
+        <is>
+          <t>사업부: IC (카테터) / 성별: 남 / 환자구분: SB-N
+연락 상태: 정상 / 연락 선호: 업무폰2586 문자
 전화번호1: 관리자·010-5799-0084 (선택)
 전화번호2: 010-8716-0133
 Email: test-kto@example.com / Fax: 02-0000-0000
@@ -1731,149 +1806,107 @@
 건보등록: 신규 등록 완료 · 2026-09-07</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="32" t="inlineStr">
-        <is>
-          <t>전화번호1은 [웹 화면=테스트]일 때 콤보박스로 전환되어 CE Admin 사용자 번호만 선택 가능</t>
-        </is>
-      </c>
-      <c r="M5" s="33" t="inlineStr">
-        <is>
-          <t>입력값이 모두 반영된다</t>
-        </is>
-      </c>
-      <c r="N5" s="34" t="inlineStr">
-        <is>
-          <t>화면/03_거래처등록-채움.png</t>
-        </is>
-      </c>
-      <c r="O5" s="35" t="inlineStr"/>
-      <c r="P5" s="36" t="inlineStr"/>
-      <c r="Q5" s="36" t="inlineStr"/>
-      <c r="R5" s="36" t="inlineStr"/>
-      <c r="S5" s="36" t="inlineStr"/>
-      <c r="T5" s="35" t="inlineStr"/>
-    </row>
-    <row r="6" ht="82" customHeight="1">
-      <c r="A6" s="37" t="n"/>
-      <c r="B6" s="37" t="n"/>
-      <c r="C6" s="37" t="n"/>
-      <c r="D6" s="37" t="n"/>
-      <c r="E6" s="37" t="n"/>
-      <c r="F6" s="37" t="n"/>
-      <c r="G6" s="37" t="n"/>
-      <c r="H6" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>저장한다</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>［저장］</t>
-        </is>
-      </c>
-      <c r="L6" s="32" t="inlineStr">
-        <is>
-          <t>POST /patients — ① 주민번호 암호화 저장 + 마스킹값 별도 보관 ② 사업부 IC면 이름 앞에 (E) 자동 부여 ③ 저장 후 거래처 상세로 이동</t>
-        </is>
-      </c>
-      <c r="M6" s="33" t="inlineStr">
-        <is>
-          <t>① 거래처명이 (E)(T3-5)김태오 로 등록
-② /patients/178 상세 화면으로 이동</t>
-        </is>
-      </c>
-      <c r="N6" s="34" t="inlineStr">
-        <is>
-          <t>화면/04_거래처상세.png</t>
-        </is>
-      </c>
-      <c r="O6" s="35" t="inlineStr"/>
-      <c r="P6" s="36" t="inlineStr"/>
-      <c r="Q6" s="36" t="inlineStr"/>
-      <c r="R6" s="36" t="inlineStr"/>
-      <c r="S6" s="36" t="inlineStr"/>
-      <c r="T6" s="35" t="inlineStr"/>
+      <c r="K6" s="15" t="inlineStr">
+        <is>
+          <t>［거래처 수정］ 또는 환자ㆍ처방 › 거래처 관리</t>
+        </is>
+      </c>
+      <c r="L6" s="45" t="inlineStr">
+        <is>
+          <t>POST/PUT /patients — ① 주민번호 암호화 저장 + 마스킹값 별도 보관 ② 주민번호 입력 시 생년월일 자동 계산(peBirthFromRrn) ③ 만 19세 미만이면 [보호자] 입력 영역이 자동 노출</t>
+        </is>
+      </c>
+      <c r="M6" s="46" t="inlineStr">
+        <is>
+          <t>① 생년월일 1985-02-03 자동 입력
+② 만 41세 성년이므로 [보호자] 영역 미노출
+③ 거래처명 (E)(T3-5)김태오</t>
+        </is>
+      </c>
+      <c r="N6" s="47" t="inlineStr">
+        <is>
+          <t>화면/02_거래처등록-창.png
+화면/03_거래처등록-채움.png
+화면/04_거래처상세.png</t>
+        </is>
+      </c>
+      <c r="O6" s="34" t="inlineStr"/>
+      <c r="P6" s="35" t="inlineStr"/>
+      <c r="Q6" s="35" t="inlineStr"/>
+      <c r="R6" s="35" t="inlineStr"/>
+      <c r="S6" s="35" t="inlineStr"/>
+      <c r="T6" s="34" t="inlineStr"/>
     </row>
     <row r="7" ht="82" customHeight="1">
-      <c r="A7" s="38" t="inlineStr">
-        <is>
-          <t>TC-002</t>
-        </is>
-      </c>
-      <c r="B7" s="39" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>TC-003</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>CASE-01 처방전·일반(10/90)·링크페이</t>
         </is>
       </c>
-      <c r="C7" s="40" t="inlineStr">
-        <is>
-          <t>처방</t>
-        </is>
-      </c>
-      <c r="D7" s="41" t="inlineStr">
-        <is>
-          <t>처방자료 업로드</t>
-        </is>
-      </c>
-      <c r="E7" s="41" t="inlineStr">
-        <is>
-          <t>TC-001 완료</t>
-        </is>
-      </c>
-      <c r="F7" s="41" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>접수</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>처방 서류 업로드 및 등록</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>TC-002 완료 (환자 선택 상태)</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>환자ㆍ처방 › 처방자료 업로드</t>
         </is>
       </c>
-      <c r="G7" s="41" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>/prescriptions/upload</t>
         </is>
       </c>
-      <c r="H7" s="42" t="n">
+      <c r="H7" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="41" t="inlineStr">
-        <is>
-          <t>대상 환자를 조회하여 선택한다</t>
-        </is>
-      </c>
-      <c r="J7" s="41" t="inlineStr">
-        <is>
-          <t>이름 선택: (E)(T3-5)김태오</t>
-        </is>
-      </c>
-      <c r="K7" s="41" t="inlineStr">
-        <is>
-          <t>［조회］ → 환자 선택</t>
-        </is>
-      </c>
-      <c r="L7" s="43" t="inlineStr">
-        <is>
-          <t>selectPatient() — 처방전을 붙일 거래처를 확정한다</t>
-        </is>
-      </c>
-      <c r="M7" s="44" t="inlineStr">
-        <is>
-          <t>이름 선택 칸에 환자명이 표시된다</t>
-        </is>
-      </c>
-      <c r="N7" s="45" t="inlineStr">
-        <is>
-          <t>화면/05_처방자료업로드-빈화면.png</t>
+      <c r="I7" s="23" t="inlineStr">
+        <is>
+          <t>서류 유형을 바꿔가며 파일을 업로드한다</t>
+        </is>
+      </c>
+      <c r="J7" s="23" t="inlineStr">
+        <is>
+          <t>처방전: 김태오_처방전.jpg (1건)
+신분증: 김태오_신분증_TEST.jpg (1건)
+등록신청서: 김태오_자가도뇨소모성재료_등록신청서_TEST.jpg (1건)
+결과지: 김태오_결과지_01~08_TEST.jpg (8건)</t>
+        </is>
+      </c>
+      <c r="K7" s="23" t="inlineStr">
+        <is>
+          <t>서류 유형 콤보 → 파일 선택 (유형별 4회 반복)</t>
+        </is>
+      </c>
+      <c r="L7" s="25" t="inlineStr">
+        <is>
+          <t>파일마다 업로드 시점의 [서류 유형]이 부여된다. 유형은 개별 타일에서 변경 가능.</t>
+        </is>
+      </c>
+      <c r="M7" s="26" t="inlineStr">
+        <is>
+          <t>총 11건이 유형별로 배치된다 (처방전1·신분증1·등록신청서1·결과지8)</t>
+        </is>
+      </c>
+      <c r="N7" s="27" t="inlineStr">
+        <is>
+          <t>화면/06_처방자료업로드-11건.png</t>
         </is>
       </c>
       <c r="O7" s="28" t="inlineStr"/>
@@ -1891,144 +1924,93 @@
       <c r="E8" s="30" t="n"/>
       <c r="F8" s="30" t="n"/>
       <c r="G8" s="30" t="n"/>
-      <c r="H8" s="46" t="n">
+      <c r="H8" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="I8" s="15" t="inlineStr">
-        <is>
-          <t>서류 유형을 바꿔가며 파일을 업로드한다</t>
-        </is>
-      </c>
-      <c r="J8" s="15" t="inlineStr">
-        <is>
-          <t>처방전: 김태오_처방전.jpg (1)
-신분증: 김태오_신분증_TEST.jpg (1)
-등록신청서: 김태오_자가도뇨소모성재료_등록신청서_TEST.jpg (1)
-결과지: 김태오_결과지_01~08_TEST.jpg (8)</t>
-        </is>
-      </c>
-      <c r="K8" s="15" t="inlineStr">
-        <is>
-          <t>서류 유형 콤보 → 파일 선택</t>
-        </is>
-      </c>
-      <c r="L8" s="47" t="inlineStr">
-        <is>
-          <t>파일마다 업로드 시점의 [서류 유형]이 부여된다. 유형은 타일에서 개별 변경 가능.</t>
-        </is>
-      </c>
-      <c r="M8" s="48" t="inlineStr">
-        <is>
-          <t>총 11건이 유형별로 배치된다 (처방전1·신분증1·등록신청서1·결과지8)</t>
-        </is>
-      </c>
-      <c r="N8" s="49" t="inlineStr">
-        <is>
-          <t>화면/06_처방자료업로드-11건.png</t>
-        </is>
-      </c>
-      <c r="O8" s="35" t="inlineStr"/>
-      <c r="P8" s="36" t="inlineStr"/>
-      <c r="Q8" s="36" t="inlineStr"/>
-      <c r="R8" s="36" t="inlineStr"/>
-      <c r="S8" s="36" t="inlineStr"/>
-      <c r="T8" s="35" t="inlineStr"/>
-    </row>
-    <row r="9" ht="82" customHeight="1">
-      <c r="A9" s="37" t="n"/>
-      <c r="B9" s="37" t="n"/>
-      <c r="C9" s="37" t="n"/>
-      <c r="D9" s="37" t="n"/>
-      <c r="E9" s="37" t="n"/>
-      <c r="F9" s="37" t="n"/>
-      <c r="G9" s="37" t="n"/>
-      <c r="H9" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="I9" s="15" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>담당자와 메모를 입력하고 등록한다</t>
         </is>
       </c>
-      <c r="J9" s="15" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>담당자: 원동희
 메모: 3차 5회 · 1번 김태오 · 일반 10/90 · 링크페이 · 기준 한 바퀴</t>
         </is>
       </c>
-      <c r="K9" s="15" t="inlineStr">
+      <c r="K8" s="6" t="inlineStr">
         <is>
           <t>［등록］</t>
         </is>
       </c>
-      <c r="L9" s="47" t="inlineStr">
+      <c r="L8" s="32" t="inlineStr">
         <is>
           <t>POST /prescriptions — ① 처방전 1장은 처방전 이미지로, 나머지는 첨부문서로 저장 ② 처방번호 RX-YYYYMMDD-NNN 자동 채번(삭제분 포함 채번하여 번호 재사용 방지) ③ 상태=검수 필요 ④ 새 탭으로 주문 등록 화면 오픈</t>
         </is>
       </c>
-      <c r="M9" s="48" t="inlineStr">
+      <c r="M8" s="48" t="inlineStr">
         <is>
           <t>① RX-20260907-005 채번
 ② 새 탭에서 주문 등록 화면이 열림</t>
         </is>
       </c>
-      <c r="N9" s="49" t="inlineStr">
+      <c r="N8" s="33" t="inlineStr">
         <is>
           <t>화면/07_주문등록-열림.png</t>
         </is>
       </c>
-      <c r="O9" s="35" t="inlineStr"/>
-      <c r="P9" s="36" t="inlineStr"/>
-      <c r="Q9" s="36" t="inlineStr"/>
-      <c r="R9" s="36" t="inlineStr"/>
-      <c r="S9" s="36" t="inlineStr"/>
-      <c r="T9" s="35" t="inlineStr"/>
-    </row>
-    <row r="10" ht="82" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>TC-003</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="O8" s="34" t="inlineStr"/>
+      <c r="P8" s="35" t="inlineStr"/>
+      <c r="Q8" s="35" t="inlineStr"/>
+      <c r="R8" s="35" t="inlineStr"/>
+      <c r="S8" s="35" t="inlineStr"/>
+      <c r="T8" s="34" t="inlineStr"/>
+    </row>
+    <row r="9" ht="82" customHeight="1">
+      <c r="A9" s="36" t="inlineStr">
+        <is>
+          <t>TC-004</t>
+        </is>
+      </c>
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>CASE-01 처방전·일반(10/90)·링크페이</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C9" s="38" t="inlineStr">
         <is>
           <t>처방</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D9" s="39" t="inlineStr">
         <is>
           <t>상세 목록 - 상담ㆍ환자 정보</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>TC-002 완료</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="E9" s="39" t="inlineStr">
+        <is>
+          <t>TC-003 완료</t>
+        </is>
+      </c>
+      <c r="F9" s="39" t="inlineStr">
         <is>
           <t>주문ㆍ재구매 › 주문 등록 › [상세 목록] › 상담ㆍ환자 정보</t>
         </is>
       </c>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="G9" s="39" t="inlineStr">
         <is>
           <t>/prescriptions/RX-20260907-005</t>
         </is>
       </c>
-      <c r="H10" s="24" t="n">
+      <c r="H9" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="23" t="inlineStr">
+      <c r="I9" s="39" t="inlineStr">
         <is>
           <t>상세 목록 탭 › 상담ㆍ환자 정보에서 환자 항목을 입력한다</t>
         </is>
       </c>
-      <c r="J10" s="23" t="inlineStr">
+      <c r="J9" s="39" t="inlineStr">
         <is>
           <t>주민등록번호: 850203-1000001
 전화번호1: 관리자 · 01057990084 (선택)
@@ -2036,24 +2018,100 @@
 송금자명: 김태오</t>
         </is>
       </c>
+      <c r="K9" s="39" t="inlineStr">
+        <is>
+          <t>［상세 목록］ 탭 → ［상담ㆍ환자 정보］</t>
+        </is>
+      </c>
+      <c r="L9" s="41" t="inlineStr">
+        <is>
+          <t>[웹 화면=테스트]이면 전화번호가 콤보박스로 전환된다. 결제 방식도 이 탭에 위치한다(처방전 없이도 구매 가능하므로).</t>
+        </is>
+      </c>
+      <c r="M9" s="42" t="inlineStr">
+        <is>
+          <t>입력값이 반영되고 전화번호가 콤보박스로 표시된다</t>
+        </is>
+      </c>
+      <c r="N9" s="43" t="inlineStr">
+        <is>
+          <t>화면/08_상세목록-상담환자정보.png</t>
+        </is>
+      </c>
+      <c r="O9" s="28" t="inlineStr"/>
+      <c r="P9" s="29" t="inlineStr"/>
+      <c r="Q9" s="29" t="inlineStr"/>
+      <c r="R9" s="29" t="inlineStr"/>
+      <c r="S9" s="29" t="inlineStr"/>
+      <c r="T9" s="28" t="inlineStr"/>
+    </row>
+    <row r="10" ht="82" customHeight="1">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>TC-005</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>CASE-01 처방전·일반(10/90)·링크페이</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>처방</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>병원 조회 (마스터 미등록)</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>TC-004 진행 중</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>상세 목록 › 병원ㆍ처방 정보 › [병원 조회] 팝업</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>/prescriptions/RX-20260907-005</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t>병원 조회 팝업에서 병원명으로 검색한다</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="inlineStr">
+        <is>
+          <t>검색어: 서울가온</t>
+        </is>
+      </c>
       <c r="K10" s="23" t="inlineStr">
         <is>
-          <t>［상세 목록］ 탭 → ［상담ㆍ환자 정보］</t>
+          <t>［병원 조회］</t>
         </is>
       </c>
       <c r="L10" s="25" t="inlineStr">
         <is>
-          <t>[웹 화면=테스트]이면 전화번호가 콤보박스로 전환. 결제 방식도 이 탭에 위치(처방전 없이도 구매 가능하므로).</t>
-        </is>
-      </c>
-      <c r="M10" s="26" t="inlineStr">
-        <is>
-          <t>입력값이 반영되고 전화번호가 콤보박스로 표시된다</t>
+          <t>hospitalSearch() — 병원 마스터에서 이름/요양기관기호로 조회</t>
+        </is>
+      </c>
+      <c r="M10" s="49" t="inlineStr">
+        <is>
+          <t>★ 검색 결과 0건 — 5회 테스트 자료의 가상 병원 8곳은 마스터에 미등록 상태</t>
         </is>
       </c>
       <c r="N10" s="27" t="inlineStr">
         <is>
-          <t>화면/08_상세목록-상담환자정보.png</t>
+          <t>화면/09_병원조회-팝업.png</t>
         </is>
       </c>
       <c r="O10" s="28" t="inlineStr"/>
@@ -2064,222 +2122,146 @@
       <c r="T10" s="28" t="inlineStr"/>
     </row>
     <row r="11" ht="82" customHeight="1">
-      <c r="A11" s="38" t="inlineStr">
-        <is>
-          <t>TC-004</t>
-        </is>
-      </c>
-      <c r="B11" s="39" t="inlineStr">
+      <c r="A11" s="30" t="n"/>
+      <c r="B11" s="30" t="n"/>
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="30" t="n"/>
+      <c r="E11" s="30" t="n"/>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="30" t="n"/>
+      <c r="H11" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>요양기관기호로 재검색한다</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>검색어: 1231013</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>［검색］</t>
+        </is>
+      </c>
+      <c r="L11" s="32" t="inlineStr">
+        <is>
+          <t>동일 함수 — 기호 부분일치 조회</t>
+        </is>
+      </c>
+      <c r="M11" s="48" t="inlineStr">
+        <is>
+          <t>무관한 「연세재활의학과의원(12310131)」만 조회된다</t>
+        </is>
+      </c>
+      <c r="N11" s="33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O11" s="34" t="inlineStr"/>
+      <c r="P11" s="35" t="inlineStr"/>
+      <c r="Q11" s="35" t="inlineStr"/>
+      <c r="R11" s="35" t="inlineStr"/>
+      <c r="S11" s="35" t="inlineStr"/>
+      <c r="T11" s="34" t="inlineStr"/>
+    </row>
+    <row r="12" ht="82" customHeight="1">
+      <c r="A12" s="36" t="inlineStr">
+        <is>
+          <t>TC-006</t>
+        </is>
+      </c>
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>CASE-01 처방전·일반(10/90)·링크페이</t>
         </is>
       </c>
-      <c r="C11" s="40" t="inlineStr">
+      <c r="C12" s="38" t="inlineStr">
         <is>
           <t>처방</t>
         </is>
       </c>
-      <c r="D11" s="41" t="inlineStr">
-        <is>
-          <t>병원 조회 (마스터 미등록)</t>
-        </is>
-      </c>
-      <c r="E11" s="41" t="inlineStr">
-        <is>
-          <t>TC-003 진행 중</t>
-        </is>
-      </c>
-      <c r="F11" s="41" t="inlineStr">
-        <is>
-          <t>상세 목록 › 병원ㆍ처방 정보 › [병원 조회] 팝업</t>
-        </is>
-      </c>
-      <c r="G11" s="41" t="inlineStr">
+      <c r="D12" s="39" t="inlineStr">
+        <is>
+          <t>신규 병원 등록</t>
+        </is>
+      </c>
+      <c r="E12" s="39" t="inlineStr">
+        <is>
+          <t>TC-005 결과 0건</t>
+        </is>
+      </c>
+      <c r="F12" s="39" t="inlineStr">
+        <is>
+          <t>병원 조회 팝업 › [새 병원 등록]</t>
+        </is>
+      </c>
+      <c r="G12" s="39" t="inlineStr">
         <is>
           <t>/prescriptions/RX-20260907-005</t>
         </is>
       </c>
-      <c r="H11" s="42" t="n">
+      <c r="H12" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="41" t="inlineStr">
-        <is>
-          <t>병원 조회 팝업에서 병원명으로 검색한다</t>
-        </is>
-      </c>
-      <c r="J11" s="41" t="inlineStr">
-        <is>
-          <t>검색어: 서울가온</t>
-        </is>
-      </c>
-      <c r="K11" s="41" t="inlineStr">
-        <is>
-          <t>［병원 조회］</t>
-        </is>
-      </c>
-      <c r="L11" s="43" t="inlineStr">
-        <is>
-          <t>hospitalSearch() — 병원 마스터에서 이름/요양기관기호로 조회</t>
-        </is>
-      </c>
-      <c r="M11" s="50" t="inlineStr">
-        <is>
-          <t>★ 검색 결과 0건 — 5회 테스트 자료의 가상 병원 8곳은 마스터에 미등록 상태</t>
-        </is>
-      </c>
-      <c r="N11" s="45" t="inlineStr">
-        <is>
-          <t>화면/09_병원조회-팝업.png</t>
-        </is>
-      </c>
-      <c r="O11" s="28" t="inlineStr"/>
-      <c r="P11" s="29" t="inlineStr"/>
-      <c r="Q11" s="29" t="inlineStr"/>
-      <c r="R11" s="29" t="inlineStr"/>
-      <c r="S11" s="29" t="inlineStr"/>
-      <c r="T11" s="28" t="inlineStr"/>
-    </row>
-    <row r="12" ht="82" customHeight="1">
-      <c r="A12" s="37" t="n"/>
-      <c r="B12" s="37" t="n"/>
-      <c r="C12" s="37" t="n"/>
-      <c r="D12" s="37" t="n"/>
-      <c r="E12" s="37" t="n"/>
-      <c r="F12" s="37" t="n"/>
-      <c r="G12" s="37" t="n"/>
-      <c r="H12" s="46" t="n">
+      <c r="I12" s="39" t="inlineStr">
+        <is>
+          <t>신규 병원 등록 창을 연다</t>
+        </is>
+      </c>
+      <c r="J12" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="39" t="inlineStr">
+        <is>
+          <t>［새 병원 등록］</t>
+        </is>
+      </c>
+      <c r="L12" s="41" t="inlineStr">
+        <is>
+          <t>hospitalNewOpen() — 병원 신규 등록 입력 영역 노출</t>
+        </is>
+      </c>
+      <c r="M12" s="42" t="inlineStr">
+        <is>
+          <t>병원명·요양기관기호·진료과목·전화번호·주소 입력칸이 표시된다</t>
+        </is>
+      </c>
+      <c r="N12" s="43" t="inlineStr">
+        <is>
+          <t>화면/10_새병원등록-팝업.png</t>
+        </is>
+      </c>
+      <c r="O12" s="28" t="inlineStr"/>
+      <c r="P12" s="29" t="inlineStr"/>
+      <c r="Q12" s="29" t="inlineStr"/>
+      <c r="R12" s="29" t="inlineStr"/>
+      <c r="S12" s="29" t="inlineStr"/>
+      <c r="T12" s="28" t="inlineStr"/>
+    </row>
+    <row r="13" ht="82" customHeight="1">
+      <c r="A13" s="30" t="n"/>
+      <c r="B13" s="30" t="n"/>
+      <c r="C13" s="30" t="n"/>
+      <c r="D13" s="30" t="n"/>
+      <c r="E13" s="30" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
+      <c r="H13" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>요양기관기호로 재검색한다</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>검색어: 1231013</t>
-        </is>
-      </c>
-      <c r="K12" s="15" t="inlineStr">
-        <is>
-          <t>［검색］</t>
-        </is>
-      </c>
-      <c r="L12" s="47" t="inlineStr">
-        <is>
-          <t>동일 함수 — 기호 부분일치 조회</t>
-        </is>
-      </c>
-      <c r="M12" s="48" t="inlineStr">
-        <is>
-          <t>무관한 「연세재활의학과의원(12310131)」만 조회된다</t>
-        </is>
-      </c>
-      <c r="N12" s="49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O12" s="35" t="inlineStr"/>
-      <c r="P12" s="36" t="inlineStr"/>
-      <c r="Q12" s="36" t="inlineStr"/>
-      <c r="R12" s="36" t="inlineStr"/>
-      <c r="S12" s="36" t="inlineStr"/>
-      <c r="T12" s="35" t="inlineStr"/>
-    </row>
-    <row r="13" ht="82" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>TC-005</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>CASE-01 처방전·일반(10/90)·링크페이</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
-        <is>
-          <t>처방</t>
-        </is>
-      </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>신규 병원 등록</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>TC-004 결과 0건</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>병원 조회 팝업 › [새 병원 등록]</t>
-        </is>
-      </c>
-      <c r="G13" s="23" t="inlineStr">
-        <is>
-          <t>/prescriptions/RX-20260907-005</t>
-        </is>
-      </c>
-      <c r="H13" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="23" t="inlineStr">
-        <is>
-          <t>신규 병원 등록 창을 연다</t>
-        </is>
-      </c>
-      <c r="J13" s="23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K13" s="23" t="inlineStr">
-        <is>
-          <t>［새 병원 등록］</t>
-        </is>
-      </c>
-      <c r="L13" s="25" t="inlineStr">
-        <is>
-          <t>hospitalNewOpen() — 병원 신규 등록 입력 영역 표시</t>
-        </is>
-      </c>
-      <c r="M13" s="26" t="inlineStr">
-        <is>
-          <t>병원명·요양기관기호·진료과목·전화번호·주소 입력칸이 표시된다</t>
-        </is>
-      </c>
-      <c r="N13" s="27" t="inlineStr">
-        <is>
-          <t>화면/10_새병원등록-팝업.png</t>
-        </is>
-      </c>
-      <c r="O13" s="28" t="inlineStr"/>
-      <c r="P13" s="29" t="inlineStr"/>
-      <c r="Q13" s="29" t="inlineStr"/>
-      <c r="R13" s="29" t="inlineStr"/>
-      <c r="S13" s="29" t="inlineStr"/>
-      <c r="T13" s="28" t="inlineStr"/>
-    </row>
-    <row r="14" ht="82" customHeight="1">
-      <c r="A14" s="37" t="n"/>
-      <c r="B14" s="37" t="n"/>
-      <c r="C14" s="37" t="n"/>
-      <c r="D14" s="37" t="n"/>
-      <c r="E14" s="37" t="n"/>
-      <c r="F14" s="37" t="n"/>
-      <c r="G14" s="37" t="n"/>
-      <c r="H14" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I13" s="15" t="inlineStr">
         <is>
           <t>처방전에서 읽은 값으로 병원을 등록한다</t>
         </is>
       </c>
-      <c r="J14" s="6" t="inlineStr">
+      <c r="J13" s="15" t="inlineStr">
         <is>
           <t>병원명: 서울가온대학교병원
 요양기관 기호: 12310130
@@ -2288,80 +2270,80 @@
 주소: 서울특별시 광진구 구의동 631-1</t>
         </is>
       </c>
-      <c r="K14" s="6" t="inlineStr">
+      <c r="K13" s="15" t="inlineStr">
         <is>
           <t>［등록하고 고르기］</t>
         </is>
       </c>
-      <c r="L14" s="32" t="inlineStr">
+      <c r="L13" s="45" t="inlineStr">
         <is>
           <t>POST /hospitals — ① 병원 마스터에 신규 등록 ② 등록 즉시 해당 병원을 선택하여 병원명·요양병원 코드를 자동 채움</t>
         </is>
       </c>
-      <c r="M14" s="33" t="inlineStr">
+      <c r="M13" s="46" t="inlineStr">
         <is>
           <t>① 토스트 「서울가온대학교병원 · 12310130」
 ② 병원명·요양병원 코드가 자동 입력됨</t>
         </is>
       </c>
-      <c r="N14" s="34" t="inlineStr">
+      <c r="N13" s="47" t="inlineStr">
         <is>
           <t>화면/11_새병원등록-채움.png
 화면/12_병원채워짐.png</t>
         </is>
       </c>
-      <c r="O14" s="35" t="inlineStr"/>
-      <c r="P14" s="36" t="inlineStr"/>
-      <c r="Q14" s="36" t="inlineStr"/>
-      <c r="R14" s="36" t="inlineStr"/>
-      <c r="S14" s="36" t="inlineStr"/>
-      <c r="T14" s="35" t="inlineStr"/>
-    </row>
-    <row r="15" ht="82" customHeight="1">
-      <c r="A15" s="38" t="inlineStr">
-        <is>
-          <t>TC-006</t>
-        </is>
-      </c>
-      <c r="B15" s="39" t="inlineStr">
+      <c r="O13" s="34" t="inlineStr"/>
+      <c r="P13" s="35" t="inlineStr"/>
+      <c r="Q13" s="35" t="inlineStr"/>
+      <c r="R13" s="35" t="inlineStr"/>
+      <c r="S13" s="35" t="inlineStr"/>
+      <c r="T13" s="34" t="inlineStr"/>
+    </row>
+    <row r="14" ht="82" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>TC-007</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>CASE-01 처방전·일반(10/90)·링크페이</t>
         </is>
       </c>
-      <c r="C15" s="40" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>처방</t>
         </is>
       </c>
-      <c r="D15" s="41" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>상세 목록 - 병원ㆍ처방 정보</t>
         </is>
       </c>
-      <c r="E15" s="41" t="inlineStr">
-        <is>
-          <t>TC-005 완료</t>
-        </is>
-      </c>
-      <c r="F15" s="41" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>TC-006 완료</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>상세 목록 › 병원ㆍ처방 정보</t>
         </is>
       </c>
-      <c r="G15" s="41" t="inlineStr">
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>/prescriptions/RX-20260907-005</t>
         </is>
       </c>
-      <c r="H15" s="42" t="n">
+      <c r="H14" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="41" t="inlineStr">
+      <c r="I14" s="23" t="inlineStr">
         <is>
           <t>처방전 기재값과 시험값을 모두 입력한다</t>
         </is>
       </c>
-      <c r="J15" s="41" t="inlineStr">
+      <c r="J14" s="23" t="inlineStr">
         <is>
           <t>[처방전 판독값]
 상병코드: Q05.9 / 상병명: 이분척추·신경인성 방광
@@ -2380,25 +2362,103 @@
 주문 담당자: 원동희</t>
         </is>
       </c>
-      <c r="K15" s="41" t="inlineStr">
+      <c r="K14" s="23" t="inlineStr">
         <is>
           <t>［병원ㆍ처방 정보］ 탭</t>
         </is>
       </c>
-      <c r="L15" s="43" t="inlineStr">
+      <c r="L14" s="25" t="inlineStr">
         <is>
           <t>자격을 [일반]으로 선택하면 청구전략이 본인 10% / 공단 90%로 확정된다</t>
         </is>
       </c>
-      <c r="M15" s="44" t="inlineStr">
+      <c r="M14" s="26" t="inlineStr">
         <is>
           <t>① 처방전종료일이 발행일+90일 = 2026-12-06 으로 자동 계산
 ② 일일 도뇨 횟수 선택지가 1~10, 10 이상으로 표시 (단위 「회」 미표기)</t>
         </is>
       </c>
-      <c r="N15" s="45" t="inlineStr">
+      <c r="N14" s="27" t="inlineStr">
         <is>
           <t>화면/13_상세목록-병원처방정보.png</t>
+        </is>
+      </c>
+      <c r="O14" s="28" t="inlineStr"/>
+      <c r="P14" s="29" t="inlineStr"/>
+      <c r="Q14" s="29" t="inlineStr"/>
+      <c r="R14" s="29" t="inlineStr"/>
+      <c r="S14" s="29" t="inlineStr"/>
+      <c r="T14" s="28" t="inlineStr"/>
+    </row>
+    <row r="15" ht="82" customHeight="1">
+      <c r="A15" s="36" t="inlineStr">
+        <is>
+          <t>TC-008</t>
+        </is>
+      </c>
+      <c r="B15" s="37" t="inlineStr">
+        <is>
+          <t>CASE-01 처방전·일반(10/90)·링크페이</t>
+        </is>
+      </c>
+      <c r="C15" s="38" t="inlineStr">
+        <is>
+          <t>처방</t>
+        </is>
+      </c>
+      <c r="D15" s="39" t="inlineStr">
+        <is>
+          <t>관할 청구처 지정 및 저장</t>
+        </is>
+      </c>
+      <c r="E15" s="39" t="inlineStr">
+        <is>
+          <t>TC-007 완료</t>
+        </is>
+      </c>
+      <c r="F15" s="39" t="inlineStr">
+        <is>
+          <t>병원ㆍ처방 정보 › 관할 청구처 [찾기] 팝업</t>
+        </is>
+      </c>
+      <c r="G15" s="39" t="inlineStr">
+        <is>
+          <t>/prescriptions/RX-20260907-005</t>
+        </is>
+      </c>
+      <c r="H15" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="39" t="inlineStr">
+        <is>
+          <t>관할 청구처를 조회한다</t>
+        </is>
+      </c>
+      <c r="J15" s="39" t="inlineStr">
+        <is>
+          <t>읍ㆍ면ㆍ동: 소공동
+시ㆍ군ㆍ구: 중구(자동)</t>
+        </is>
+      </c>
+      <c r="K15" s="39" t="inlineStr">
+        <is>
+          <t>［찾기］</t>
+        </is>
+      </c>
+      <c r="L15" s="41" t="inlineStr">
+        <is>
+          <t>boFindRun() — ① 자사 청구처 마스터 우선 조회 ② 미존재 시 외부(공단·카카오)에 조회하여 후보 제시. ※ 기존 등록건을 선택해야 마스터 중복이 발생하지 않는다</t>
+        </is>
+      </c>
+      <c r="M15" s="42" t="inlineStr">
+        <is>
+          <t>「공단 중구지사 · 보험급여부」 1건이 조회된다 (기존 등록건)</t>
+        </is>
+      </c>
+      <c r="N15" s="43" t="inlineStr">
+        <is>
+          <t>화면/14_청구처찾기-팝업.png
+화면/15_청구처찾기-후보.png</t>
         </is>
       </c>
       <c r="O15" s="28" t="inlineStr"/>
@@ -2409,200 +2469,200 @@
       <c r="T15" s="28" t="inlineStr"/>
     </row>
     <row r="16" ht="82" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>TC-007</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>CASE-01 처방전·일반(10/90)·링크페이</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
-        <is>
-          <t>처방</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t>관할 청구처 지정 및 저장</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="inlineStr">
-        <is>
-          <t>TC-006 완료</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>병원ㆍ처방 정보 › 관할 청구처 [찾기] 팝업</t>
-        </is>
-      </c>
-      <c r="G16" s="23" t="inlineStr">
-        <is>
-          <t>/prescriptions/RX-20260907-005</t>
-        </is>
-      </c>
-      <c r="H16" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="23" t="inlineStr">
-        <is>
-          <t>관할 청구처를 조회한다</t>
-        </is>
-      </c>
-      <c r="J16" s="23" t="inlineStr">
-        <is>
-          <t>읍ㆍ면ㆍ동: 소공동
-시ㆍ군ㆍ구: 중구(자동)</t>
-        </is>
-      </c>
-      <c r="K16" s="23" t="inlineStr">
-        <is>
-          <t>［찾기］</t>
-        </is>
-      </c>
-      <c r="L16" s="25" t="inlineStr">
-        <is>
-          <t>boFindRun() — ① 자사 청구처 마스터 우선 조회 ② 미존재 시 외부(공단·카카오)에 조회하여 후보 제시. ※ 기존 등록건을 선택해야 마스터 중복이 발생하지 않음</t>
-        </is>
-      </c>
-      <c r="M16" s="26" t="inlineStr">
-        <is>
-          <t>「공단 중구지사 · 보험급여부」 1건이 조회된다 (기존 등록건)</t>
-        </is>
-      </c>
-      <c r="N16" s="27" t="inlineStr">
-        <is>
-          <t>화면/14_청구처찾기-팝업.png
-화면/15_청구처찾기-후보.png</t>
-        </is>
-      </c>
-      <c r="O16" s="28" t="inlineStr"/>
-      <c r="P16" s="29" t="inlineStr"/>
-      <c r="Q16" s="29" t="inlineStr"/>
-      <c r="R16" s="29" t="inlineStr"/>
-      <c r="S16" s="29" t="inlineStr"/>
-      <c r="T16" s="28" t="inlineStr"/>
-    </row>
-    <row r="17" ht="82" customHeight="1">
-      <c r="A17" s="37" t="n"/>
-      <c r="B17" s="37" t="n"/>
-      <c r="C17" s="37" t="n"/>
-      <c r="D17" s="37" t="n"/>
-      <c r="E17" s="37" t="n"/>
-      <c r="F17" s="37" t="n"/>
-      <c r="G17" s="37" t="n"/>
-      <c r="H17" s="31" t="n">
+      <c r="A16" s="30" t="n"/>
+      <c r="B16" s="30" t="n"/>
+      <c r="C16" s="30" t="n"/>
+      <c r="D16" s="30" t="n"/>
+      <c r="E16" s="30" t="n"/>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
+      <c r="H16" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I16" s="15" t="inlineStr">
         <is>
           <t>조회된 청구처를 선택하고 저장한다</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="J16" s="15" t="inlineStr">
         <is>
           <t>청구처: 공단 중구지사</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
+      <c r="K16" s="15" t="inlineStr">
         <is>
           <t>후보 클릭 → ［저장］</t>
         </is>
       </c>
-      <c r="L17" s="32" t="inlineStr">
+      <c r="L16" s="45" t="inlineStr">
         <is>
           <t>PUT /prescriptions/{rx}/ocr — ① 처방 항목 저장 ② 환자 귀속 항목(Email·전화2·건보등록 등)은 거래처로 승계 ③ 처방전을 환자에 연결 ④ 설정에 따라 접수 안내 문자 및 위임동의 링크 발송</t>
         </is>
       </c>
-      <c r="M17" s="33" t="inlineStr">
+      <c r="M16" s="46" t="inlineStr">
         <is>
           <t>① 토스트 「저장되었습니다」
 ② 관할 청구처에 공단 중구지사가 표시됨</t>
         </is>
       </c>
-      <c r="N17" s="34" t="inlineStr">
+      <c r="N16" s="47" t="inlineStr">
         <is>
           <t>화면/16_상세목록-저장.png</t>
         </is>
       </c>
-      <c r="O17" s="35" t="inlineStr"/>
-      <c r="P17" s="36" t="inlineStr"/>
-      <c r="Q17" s="36" t="inlineStr"/>
-      <c r="R17" s="36" t="inlineStr"/>
-      <c r="S17" s="36" t="inlineStr"/>
-      <c r="T17" s="35" t="inlineStr"/>
-    </row>
-    <row r="18" ht="82" customHeight="1">
-      <c r="A18" s="38" t="inlineStr">
-        <is>
-          <t>TC-008</t>
-        </is>
-      </c>
-      <c r="B18" s="39" t="inlineStr">
+      <c r="O16" s="34" t="inlineStr"/>
+      <c r="P16" s="35" t="inlineStr"/>
+      <c r="Q16" s="35" t="inlineStr"/>
+      <c r="R16" s="35" t="inlineStr"/>
+      <c r="S16" s="35" t="inlineStr"/>
+      <c r="T16" s="34" t="inlineStr"/>
+    </row>
+    <row r="17" ht="82" customHeight="1">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>TC-009</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>CASE-01 처방전·일반(10/90)·링크페이</t>
         </is>
       </c>
-      <c r="C18" s="40" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>검수</t>
         </is>
       </c>
-      <c r="D18" s="41" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>검수 요청</t>
         </is>
       </c>
-      <c r="E18" s="41" t="inlineStr">
-        <is>
-          <t>TC-007 완료</t>
-        </is>
-      </c>
-      <c r="F18" s="41" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>TC-008 완료</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>주문 등록 › 상세 목록 상단</t>
         </is>
       </c>
-      <c r="G18" s="41" t="inlineStr">
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>/prescriptions/RX-20260907-005</t>
         </is>
       </c>
-      <c r="H18" s="42" t="n">
+      <c r="H17" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="41" t="inlineStr">
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t>검수를 요청한다</t>
         </is>
       </c>
-      <c r="J18" s="41" t="inlineStr">
+      <c r="J17" s="23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K18" s="41" t="inlineStr">
+      <c r="K17" s="23" t="inlineStr">
         <is>
           <t>［검수 요청하기］ → 확인</t>
         </is>
       </c>
-      <c r="L18" s="43" t="inlineStr">
+      <c r="L17" s="25" t="inlineStr">
         <is>
           <t>POST /prescriptions/{rx}/request-review — ① 상태를 [검수 요청]으로 변경 ② 활동 이력 기록 ③ 검수 승인 권한 보유자 전원에게 알림 + 채팅 발송(「승인 요청」 방). 단, 요청자 본인은 수신 대상에서 제외</t>
         </is>
       </c>
-      <c r="M18" s="44" t="inlineStr">
+      <c r="M17" s="26" t="inlineStr">
         <is>
           <t>① 상태 = 검수 요청
 ② 승인 권한자 9명에게 알림 발송 (전체 10명 − 요청자 1명)</t>
         </is>
       </c>
-      <c r="N18" s="45" t="inlineStr">
+      <c r="N17" s="27" t="inlineStr">
         <is>
           <t>화면/17_검수요청.png</t>
+        </is>
+      </c>
+      <c r="O17" s="28" t="inlineStr"/>
+      <c r="P17" s="29" t="inlineStr"/>
+      <c r="Q17" s="29" t="inlineStr"/>
+      <c r="R17" s="29" t="inlineStr"/>
+      <c r="S17" s="29" t="inlineStr"/>
+      <c r="T17" s="28" t="inlineStr"/>
+    </row>
+    <row r="18" ht="82" customHeight="1">
+      <c r="A18" s="36" t="inlineStr">
+        <is>
+          <t>TC-010</t>
+        </is>
+      </c>
+      <c r="B18" s="37" t="inlineStr">
+        <is>
+          <t>CASE-01 처방전·일반(10/90)·링크페이</t>
+        </is>
+      </c>
+      <c r="C18" s="38" t="inlineStr">
+        <is>
+          <t>검수</t>
+        </is>
+      </c>
+      <c r="D18" s="39" t="inlineStr">
+        <is>
+          <t>검수 승인</t>
+        </is>
+      </c>
+      <c r="E18" s="39" t="inlineStr">
+        <is>
+          <t>TC-009 완료</t>
+        </is>
+      </c>
+      <c r="F18" s="39" t="inlineStr">
+        <is>
+          <t>주문 등록 › 상세 목록 상단</t>
+        </is>
+      </c>
+      <c r="G18" s="39" t="inlineStr">
+        <is>
+          <t>/prescriptions/RX-20260907-005</t>
+        </is>
+      </c>
+      <c r="H18" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="39" t="inlineStr">
+        <is>
+          <t>검수 승인 팝업에서 메모를 입력하고 승인한다</t>
+        </is>
+      </c>
+      <c r="J18" s="39" t="inlineStr">
+        <is>
+          <t>검수 메모: 3차 5회 · 1번 김태오 · 서류 11건 확인 · 일반 10/90</t>
+        </is>
+      </c>
+      <c r="K18" s="39" t="inlineStr">
+        <is>
+          <t>［검수 승인하기］ → 팝업 ［검수 승인하기］</t>
+        </is>
+      </c>
+      <c r="L18" s="41" t="inlineStr">
+        <is>
+          <t>POST /prescriptions/{rx}/approve — ① 상태를 [검수 완료]로 변경, 검수자·검수일시 기록 ② 요청 담당자에게 승인 결과 회신 알림 ③ 이미 승인된 건은 재승인 차단(검수자·일시 덮어쓰기 방지)</t>
+        </is>
+      </c>
+      <c r="M18" s="42" t="inlineStr">
+        <is>
+          <t>① 상태 = 검수 완료, 검수자 = 관리자
+② 담당자(원동희)에게 「검수가 승인되었습니다」 회신</t>
+        </is>
+      </c>
+      <c r="N18" s="43" t="inlineStr">
+        <is>
+          <t>화면/18_검수승인-팝업.png
+화면/19_검수완료.png</t>
         </is>
       </c>
       <c r="O18" s="28" t="inlineStr"/>
@@ -2615,7 +2675,7 @@
     <row r="19" ht="82" customHeight="1">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>TC-009</t>
+          <t>TC-011</t>
         </is>
       </c>
       <c r="B19" s="21" t="inlineStr">
@@ -2625,22 +2685,22 @@
       </c>
       <c r="C19" s="22" t="inlineStr">
         <is>
-          <t>검수</t>
+          <t>동의</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>검수 승인</t>
+          <t>위임동의 SMS 발송</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
         <is>
-          <t>TC-008 완료</t>
+          <t>TC-010 완료 · 문자 발송=우리에게만</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t>주문 등록 › 상세 목록 상단</t>
+          <t>주문 등록 › 상단 [위임동의] 팝오버</t>
         </is>
       </c>
       <c r="G19" s="23" t="inlineStr">
@@ -2653,34 +2713,35 @@
       </c>
       <c r="I19" s="23" t="inlineStr">
         <is>
-          <t>검수 승인 팝업에서 메모를 입력하고 승인한다</t>
+          <t>위임동의 발송 창에서 수신번호를 확인하고 발송한다</t>
         </is>
       </c>
       <c r="J19" s="23" t="inlineStr">
         <is>
-          <t>검수 메모: 3차 5회 · 1번 김태오 · 서류 11건 확인 · 일반 10/90</t>
+          <t>수신 번호: 010-5799-0084 (거래처 전화번호1 자동 표시)</t>
         </is>
       </c>
       <c r="K19" s="23" t="inlineStr">
         <is>
-          <t>［검수 승인하기］ → 팝업 ［검수 승인하기］</t>
+          <t>［위임동의］ → ［발송］</t>
         </is>
       </c>
       <c r="L19" s="25" t="inlineStr">
         <is>
-          <t>POST /prescriptions/{rx}/approve — ① 상태를 [검수 완료]로 변경, 검수자·검수일시 기록 ② 요청 담당자에게 승인 결과 회신 알림 ③ 이미 승인된 건은 재승인 차단(검수자·일시 덮어쓰기 방지)</t>
+          <t>POST /prescriptions/{rx}/consent-sms — ① 30분 유효 1회용 토큰으로 동의 레코드 선생성 ② 서명 링크를 SMS 발송 ③ 마스킹 주민번호로 미성년 여부 판정(원문 미조회) ④ 미성년이면 거래처 보호자 정보를 동의 레코드에 선반영 ⑤ 발송 실패 시 생성한 동의 레코드를 삭제</t>
         </is>
       </c>
       <c r="M19" s="26" t="inlineStr">
         <is>
-          <t>① 상태 = 검수 완료, 검수자 = 관리자
-② 담당자(원동희)에게 「검수가 승인되었습니다」 회신</t>
+          <t>① 발송 완료 · 팝빌 접수번호 채번
+② [우리에게만] 설정에 의해 01057990084로 우회 발송
+③ 성년이므로 is_minor = 0</t>
         </is>
       </c>
       <c r="N19" s="27" t="inlineStr">
         <is>
-          <t>화면/18_검수승인-팝업.png
-화면/19_검수완료.png</t>
+          <t>화면/20_위임동의-발송창.png
+화면/21_위임동의-발송결과.png</t>
         </is>
       </c>
       <c r="O19" s="28" t="inlineStr"/>
@@ -2691,75 +2752,73 @@
       <c r="T19" s="28" t="inlineStr"/>
     </row>
     <row r="20" ht="82" customHeight="1">
-      <c r="A20" s="38" t="inlineStr">
-        <is>
-          <t>TC-010</t>
-        </is>
-      </c>
-      <c r="B20" s="39" t="inlineStr">
+      <c r="A20" s="36" t="inlineStr">
+        <is>
+          <t>TC-012</t>
+        </is>
+      </c>
+      <c r="B20" s="37" t="inlineStr">
         <is>
           <t>CASE-01 처방전·일반(10/90)·링크페이</t>
         </is>
       </c>
-      <c r="C20" s="40" t="inlineStr">
+      <c r="C20" s="38" t="inlineStr">
         <is>
           <t>동의</t>
         </is>
       </c>
-      <c r="D20" s="41" t="inlineStr">
-        <is>
-          <t>위임동의 SMS 발송</t>
-        </is>
-      </c>
-      <c r="E20" s="41" t="inlineStr">
-        <is>
-          <t>TC-009 완료 · 문자 발송=우리에게만</t>
-        </is>
-      </c>
-      <c r="F20" s="41" t="inlineStr">
-        <is>
-          <t>주문 등록 › 상단 [위임동의] 팝오버</t>
-        </is>
-      </c>
-      <c r="G20" s="41" t="inlineStr">
-        <is>
-          <t>/prescriptions/RX-20260907-005</t>
-        </is>
-      </c>
-      <c r="H20" s="42" t="n">
+      <c r="D20" s="39" t="inlineStr">
+        <is>
+          <t>위임동의 서명 (환자 화면)</t>
+        </is>
+      </c>
+      <c r="E20" s="39" t="inlineStr">
+        <is>
+          <t>TC-011 완료 · 30분 이내</t>
+        </is>
+      </c>
+      <c r="F20" s="39" t="inlineStr">
+        <is>
+          <t>위임동의 서명 페이지 (비로그인 공개 화면)</t>
+        </is>
+      </c>
+      <c r="G20" s="39" t="inlineStr">
+        <is>
+          <t>/consent/{토큰}</t>
+        </is>
+      </c>
+      <c r="H20" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="41" t="inlineStr">
-        <is>
-          <t>위임동의 발송 창에서 수신번호를 확인하고 발송한다</t>
-        </is>
-      </c>
-      <c r="J20" s="41" t="inlineStr">
-        <is>
-          <t>수신 번호: 010-5799-0084 (거래처 전화번호1 자동 표시)</t>
-        </is>
-      </c>
-      <c r="K20" s="41" t="inlineStr">
-        <is>
-          <t>［위임동의］ → ［발송］</t>
-        </is>
-      </c>
-      <c r="L20" s="43" t="inlineStr">
-        <is>
-          <t>POST /prescriptions/{rx}/consent-sms — ① 30분 유효 1회용 토큰으로 동의 레코드 선생성 ② 서명 링크를 SMS 발송 ③ 마스킹 주민번호로 미성년 여부 판정(원문 미조회) ④ 미성년이면 거래처 보호자 정보를 동의 레코드에 선반영 ⑤ 발송 실패 시 생성한 동의 레코드를 삭제</t>
-        </is>
-      </c>
-      <c r="M20" s="44" t="inlineStr">
-        <is>
-          <t>① 발송 완료 · 팝빌 접수번호 채번
-② [우리에게만] 설정에 의해 01057990084로 우회 발송
-③ 성년이므로 is_minor = 0</t>
-        </is>
-      </c>
-      <c r="N20" s="45" t="inlineStr">
-        <is>
-          <t>화면/20_위임동의-발송창.png
-화면/21_위임동의-발송결과.png</t>
+      <c r="I20" s="39" t="inlineStr">
+        <is>
+          <t>서명 페이지를 열고 화면 구성을 확인한다</t>
+        </is>
+      </c>
+      <c r="J20" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="39" t="inlineStr">
+        <is>
+          <t>SMS 링크 클릭</t>
+        </is>
+      </c>
+      <c r="L20" s="41" t="inlineStr">
+        <is>
+          <t>토큰으로 동의 레코드를 조회하여 서명 화면을 구성한다. 미성년이면 보호자 입력·서명 영역이 추가로 노출된다.</t>
+        </is>
+      </c>
+      <c r="M20" s="42" t="inlineStr">
+        <is>
+          <t>① 본인 이름 확인·위임 내용·서명란 1개 표시
+② 성년이므로 보호자 영역 미노출</t>
+        </is>
+      </c>
+      <c r="N20" s="43" t="inlineStr">
+        <is>
+          <t>화면/22_서명화면.png</t>
         </is>
       </c>
       <c r="O20" s="28" t="inlineStr"/>
@@ -2770,130 +2829,101 @@
       <c r="T20" s="28" t="inlineStr"/>
     </row>
     <row r="21" ht="82" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>TC-011</t>
-        </is>
-      </c>
-      <c r="B21" s="21" t="inlineStr">
-        <is>
-          <t>CASE-01 처방전·일반(10/90)·링크페이</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="inlineStr">
-        <is>
-          <t>동의</t>
-        </is>
-      </c>
-      <c r="D21" s="23" t="inlineStr">
-        <is>
-          <t>위임동의 서명 (환자 화면)</t>
-        </is>
-      </c>
-      <c r="E21" s="23" t="inlineStr">
-        <is>
-          <t>TC-010 완료 · 30분 이내</t>
-        </is>
-      </c>
-      <c r="F21" s="23" t="inlineStr">
-        <is>
-          <t>위임동의 서명 페이지 (비로그인 공개 화면)</t>
-        </is>
-      </c>
-      <c r="G21" s="23" t="inlineStr">
-        <is>
-          <t>/consent/{토큰}</t>
-        </is>
-      </c>
-      <c r="H21" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="23" t="inlineStr">
-        <is>
-          <t>서명 페이지를 열고 화면 구성을 확인한다</t>
-        </is>
-      </c>
-      <c r="J21" s="23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K21" s="23" t="inlineStr">
-        <is>
-          <t>SMS 링크 클릭</t>
-        </is>
-      </c>
-      <c r="L21" s="25" t="inlineStr">
-        <is>
-          <t>토큰으로 동의 레코드를 조회하여 서명 화면을 구성. 미성년이면 보호자 입력·서명 영역이 추가로 표시된다.</t>
-        </is>
-      </c>
-      <c r="M21" s="26" t="inlineStr">
-        <is>
-          <t>① 본인 이름 확인·위임 내용·서명란 1개 표시
-② 성년이므로 보호자 영역 미표시</t>
-        </is>
-      </c>
-      <c r="N21" s="27" t="inlineStr">
-        <is>
-          <t>화면/22_서명화면.png</t>
-        </is>
-      </c>
-      <c r="O21" s="28" t="inlineStr"/>
-      <c r="P21" s="29" t="inlineStr"/>
-      <c r="Q21" s="29" t="inlineStr"/>
-      <c r="R21" s="29" t="inlineStr"/>
-      <c r="S21" s="29" t="inlineStr"/>
-      <c r="T21" s="28" t="inlineStr"/>
-    </row>
-    <row r="22" ht="82" customHeight="1">
-      <c r="A22" s="30" t="n"/>
-      <c r="B22" s="30" t="n"/>
-      <c r="C22" s="30" t="n"/>
-      <c r="D22" s="30" t="n"/>
-      <c r="E22" s="30" t="n"/>
-      <c r="F22" s="30" t="n"/>
-      <c r="G22" s="30" t="n"/>
-      <c r="H22" s="31" t="n">
+      <c r="A21" s="50" t="n"/>
+      <c r="B21" s="50" t="n"/>
+      <c r="C21" s="50" t="n"/>
+      <c r="D21" s="50" t="n"/>
+      <c r="E21" s="50" t="n"/>
+      <c r="F21" s="50" t="n"/>
+      <c r="G21" s="50" t="n"/>
+      <c r="H21" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="I22" s="6" t="inlineStr">
+      <c r="I21" s="15" t="inlineStr">
         <is>
           <t>개인정보 수집·이용 동의를 선택한다</t>
         </is>
       </c>
-      <c r="J22" s="6" t="inlineStr">
+      <c r="J21" s="15" t="inlineStr">
         <is>
           <t>신청 유형: 일반
 동의 항목: 일반·제3자·마케팅 모두 「동의함」</t>
         </is>
       </c>
-      <c r="K22" s="6" t="inlineStr">
+      <c r="K21" s="15" t="inlineStr">
         <is>
           <t>동의 항목 라디오 선택</t>
         </is>
       </c>
-      <c r="L22" s="32" t="inlineStr">
+      <c r="L21" s="45" t="inlineStr">
         <is>
           <t>privacyReady() — 신청 유형과 필수 동의 항목이 모두 충족되어야 서명 버튼이 활성화된다</t>
         </is>
       </c>
-      <c r="M22" s="33" t="inlineStr">
+      <c r="M21" s="46" t="inlineStr">
         <is>
           <t>필수 항목이 모두 선택된다</t>
         </is>
       </c>
-      <c r="N22" s="34" t="inlineStr">
+      <c r="N21" s="47" t="inlineStr">
         <is>
           <t>화면/23_개인정보동의.png</t>
         </is>
       </c>
-      <c r="O22" s="35" t="inlineStr"/>
-      <c r="P22" s="36" t="inlineStr"/>
-      <c r="Q22" s="36" t="inlineStr"/>
-      <c r="R22" s="36" t="inlineStr"/>
-      <c r="S22" s="36" t="inlineStr"/>
-      <c r="T22" s="35" t="inlineStr"/>
+      <c r="O21" s="34" t="inlineStr"/>
+      <c r="P21" s="35" t="inlineStr"/>
+      <c r="Q21" s="35" t="inlineStr"/>
+      <c r="R21" s="35" t="inlineStr"/>
+      <c r="S21" s="35" t="inlineStr"/>
+      <c r="T21" s="34" t="inlineStr"/>
+    </row>
+    <row r="22" ht="82" customHeight="1">
+      <c r="A22" s="50" t="n"/>
+      <c r="B22" s="50" t="n"/>
+      <c r="C22" s="50" t="n"/>
+      <c r="D22" s="50" t="n"/>
+      <c r="E22" s="50" t="n"/>
+      <c r="F22" s="50" t="n"/>
+      <c r="G22" s="50" t="n"/>
+      <c r="H22" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>휴대폰 본인확인을 수행한다</t>
+        </is>
+      </c>
+      <c r="J22" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="15" t="inlineStr">
+        <is>
+          <t>［본인확인］</t>
+        </is>
+      </c>
+      <c r="L22" s="45" t="inlineStr">
+        <is>
+          <t>startNice() — NICE 본인확인. [본인확인 시늉=켬]이면 실제 호출 없이 통과 처리</t>
+        </is>
+      </c>
+      <c r="M22" s="46" t="inlineStr">
+        <is>
+          <t>「확인됨 (테스트)」로 표시된다</t>
+        </is>
+      </c>
+      <c r="N22" s="47" t="inlineStr">
+        <is>
+          <t>화면/24_본인확인.png</t>
+        </is>
+      </c>
+      <c r="O22" s="34" t="inlineStr"/>
+      <c r="P22" s="35" t="inlineStr"/>
+      <c r="Q22" s="35" t="inlineStr"/>
+      <c r="R22" s="35" t="inlineStr"/>
+      <c r="S22" s="35" t="inlineStr"/>
+      <c r="T22" s="34" t="inlineStr"/>
     </row>
     <row r="23" ht="82" customHeight="1">
       <c r="A23" s="30" t="n"/>
@@ -2903,295 +2933,328 @@
       <c r="E23" s="30" t="n"/>
       <c r="F23" s="30" t="n"/>
       <c r="G23" s="30" t="n"/>
-      <c r="H23" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>휴대폰 본인확인을 수행한다</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>［본인확인］</t>
-        </is>
-      </c>
-      <c r="L23" s="32" t="inlineStr">
-        <is>
-          <t>startNice() — NICE 본인확인. [본인확인 시늉=켬]이면 실제 호출 없이 통과 처리</t>
-        </is>
-      </c>
-      <c r="M23" s="33" t="inlineStr">
-        <is>
-          <t>「확인됨 (테스트)」로 표시된다</t>
-        </is>
-      </c>
-      <c r="N23" s="34" t="inlineStr">
-        <is>
-          <t>화면/24_본인확인.png</t>
-        </is>
-      </c>
-      <c r="O23" s="35" t="inlineStr"/>
-      <c r="P23" s="36" t="inlineStr"/>
-      <c r="Q23" s="36" t="inlineStr"/>
-      <c r="R23" s="36" t="inlineStr"/>
-      <c r="S23" s="36" t="inlineStr"/>
-      <c r="T23" s="35" t="inlineStr"/>
-    </row>
-    <row r="24" ht="82" customHeight="1">
-      <c r="A24" s="37" t="n"/>
-      <c r="B24" s="37" t="n"/>
-      <c r="C24" s="37" t="n"/>
-      <c r="D24" s="37" t="n"/>
-      <c r="E24" s="37" t="n"/>
-      <c r="F24" s="37" t="n"/>
-      <c r="G24" s="37" t="n"/>
-      <c r="H24" s="31" t="n">
+      <c r="H23" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="I23" s="15" t="inlineStr">
         <is>
           <t>서명 후 동의를 제출한다</t>
         </is>
       </c>
-      <c r="J24" s="6" t="inlineStr">
+      <c r="J23" s="15" t="inlineStr">
         <is>
           <t>서명란에 서명 입력</t>
         </is>
       </c>
-      <c r="K24" s="6" t="inlineStr">
+      <c r="K23" s="15" t="inlineStr">
         <is>
           <t>［동의 서명］</t>
         </is>
       </c>
-      <c r="L24" s="32" t="inlineStr">
+      <c r="L23" s="45" t="inlineStr">
         <is>
           <t>POST /consent/{토큰} — ① 서명 이미지·동의 항목 저장 ② 위임동의서 PDF 및 요양비위임장(원본 서식 오버레이) 생성하여 첨부문서 등록 ③ 주문 관리에 주문 레코드 생성 ④ 설정 시 공단 등록 서류 팩스 자동 발송</t>
         </is>
       </c>
-      <c r="M24" s="33" t="inlineStr">
+      <c r="M23" s="46" t="inlineStr">
         <is>
           <t>① 「동의가 완료되었습니다」 표시
 ② 주문 EUD202609071734141 생성
 ③ 위임동의서·요양비위임장 첨부문서 등록</t>
         </is>
       </c>
-      <c r="N24" s="34" t="inlineStr">
+      <c r="N23" s="47" t="inlineStr">
         <is>
           <t>화면/22b_서명함.png
 화면/25_동의완료.png</t>
         </is>
       </c>
-      <c r="O24" s="35" t="inlineStr"/>
-      <c r="P24" s="36" t="inlineStr"/>
-      <c r="Q24" s="36" t="inlineStr"/>
-      <c r="R24" s="36" t="inlineStr"/>
-      <c r="S24" s="36" t="inlineStr"/>
-      <c r="T24" s="35" t="inlineStr"/>
-    </row>
-    <row r="25" ht="82" customHeight="1">
-      <c r="A25" s="38" t="inlineStr">
-        <is>
-          <t>TC-012</t>
-        </is>
-      </c>
-      <c r="B25" s="39" t="inlineStr">
+      <c r="O23" s="34" t="inlineStr"/>
+      <c r="P23" s="35" t="inlineStr"/>
+      <c r="Q23" s="35" t="inlineStr"/>
+      <c r="R23" s="35" t="inlineStr"/>
+      <c r="S23" s="35" t="inlineStr"/>
+      <c r="T23" s="34" t="inlineStr"/>
+    </row>
+    <row r="24" ht="82" customHeight="1">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>TC-013</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>CASE-01 처방전·일반(10/90)·링크페이</t>
         </is>
       </c>
-      <c r="C25" s="40" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>주문</t>
         </is>
       </c>
-      <c r="D25" s="41" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>주문 제품 등록</t>
         </is>
       </c>
-      <c r="E25" s="41" t="inlineStr">
-        <is>
-          <t>TC-011 완료 (검수 승인 + 동의 완료 필수)</t>
-        </is>
-      </c>
-      <c r="F25" s="41" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>TC-012 완료 (검수 승인 + 동의 완료 필수)</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
         <is>
           <t>주문 등록 › [주문 제품] 탭</t>
         </is>
       </c>
-      <c r="G25" s="41" t="inlineStr">
+      <c r="G24" s="23" t="inlineStr">
         <is>
           <t>/prescriptions/RX-20260907-005</t>
         </is>
       </c>
-      <c r="H25" s="42" t="n">
+      <c r="H24" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="41" t="inlineStr">
+      <c r="I24" s="23" t="inlineStr">
         <is>
           <t>제품 조회 팝업에서 처방 규격에 맞는 제품을 선택한다</t>
         </is>
       </c>
-      <c r="J25" s="41" t="inlineStr">
+      <c r="J24" s="23" t="inlineStr">
         <is>
           <t>검색어: CH14 Male
 선택: EasiCath Nalaton CH14 Male 40cm - Green</t>
         </is>
       </c>
-      <c r="K25" s="41" t="inlineStr">
+      <c r="K24" s="23" t="inlineStr">
         <is>
           <t>［주문 제품］ 탭 → 제품명 칸 ⌕ → 제품 선택</t>
         </is>
       </c>
-      <c r="L25" s="43" t="inlineStr">
+      <c r="L24" s="25" t="inlineStr">
         <is>
           <t>제품 선택 시 제품코드·소비자가가 자동 입력되고, 처방전 총계가 주문 수량으로 자동 반영된다</t>
         </is>
       </c>
-      <c r="M25" s="44" t="inlineStr">
+      <c r="M24" s="26" t="inlineStr">
         <is>
           <t>① 제품코드 5354 / 수량 540 / 소비자가 1,500
 ② 총 금액 810,000 · 기관 부담금 729,000(90%) · 본인 부담금 81,000(10%)</t>
         </is>
       </c>
-      <c r="N25" s="45" t="inlineStr">
+      <c r="N24" s="27" t="inlineStr">
         <is>
           <t>화면/26_주문제품-빈줄.png
 화면/27_제품조회-팝업.png
 화면/28_주문제품-채움.png</t>
         </is>
       </c>
-      <c r="O25" s="28" t="inlineStr"/>
-      <c r="P25" s="29" t="inlineStr"/>
-      <c r="Q25" s="29" t="inlineStr"/>
-      <c r="R25" s="29" t="inlineStr"/>
-      <c r="S25" s="29" t="inlineStr"/>
-      <c r="T25" s="28" t="inlineStr"/>
+      <c r="O24" s="28" t="inlineStr"/>
+      <c r="P24" s="29" t="inlineStr"/>
+      <c r="Q24" s="29" t="inlineStr"/>
+      <c r="R24" s="29" t="inlineStr"/>
+      <c r="S24" s="29" t="inlineStr"/>
+      <c r="T24" s="28" t="inlineStr"/>
+    </row>
+    <row r="25" ht="82" customHeight="1">
+      <c r="A25" s="30" t="n"/>
+      <c r="B25" s="30" t="n"/>
+      <c r="C25" s="30" t="n"/>
+      <c r="D25" s="30" t="n"/>
+      <c r="E25" s="30" t="n"/>
+      <c r="F25" s="30" t="n"/>
+      <c r="G25" s="30" t="n"/>
+      <c r="H25" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>주문 제품을 저장한다</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>［저장］</t>
+        </is>
+      </c>
+      <c r="L25" s="32" t="inlineStr">
+        <is>
+          <t>주문 품목 저장 및 청구전략별 금액 배분. 검수 승인과 동의가 모두 완료되어야 저장 가능하며 미완료 시 차단된다.</t>
+        </is>
+      </c>
+      <c r="M25" s="48" t="inlineStr">
+        <is>
+          <t>토스트 「저장되었습니다」</t>
+        </is>
+      </c>
+      <c r="N25" s="33" t="inlineStr">
+        <is>
+          <t>화면/29_주문제품-저장.png</t>
+        </is>
+      </c>
+      <c r="O25" s="34" t="inlineStr"/>
+      <c r="P25" s="35" t="inlineStr"/>
+      <c r="Q25" s="35" t="inlineStr"/>
+      <c r="R25" s="35" t="inlineStr"/>
+      <c r="S25" s="35" t="inlineStr"/>
+      <c r="T25" s="34" t="inlineStr"/>
     </row>
     <row r="26" ht="82" customHeight="1">
-      <c r="A26" s="37" t="n"/>
-      <c r="B26" s="37" t="n"/>
-      <c r="C26" s="37" t="n"/>
-      <c r="D26" s="37" t="n"/>
-      <c r="E26" s="37" t="n"/>
-      <c r="F26" s="37" t="n"/>
-      <c r="G26" s="37" t="n"/>
-      <c r="H26" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="I26" s="15" t="inlineStr">
-        <is>
-          <t>주문 제품을 저장한다</t>
-        </is>
-      </c>
-      <c r="J26" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K26" s="15" t="inlineStr">
-        <is>
-          <t>［저장］</t>
-        </is>
-      </c>
-      <c r="L26" s="47" t="inlineStr">
-        <is>
-          <t>주문 품목 저장 및 청구전략별 금액 배분. 검수 승인과 동의가 모두 완료되어야 저장 가능하며 미완료 시 차단된다.</t>
-        </is>
-      </c>
-      <c r="M26" s="48" t="inlineStr">
-        <is>
-          <t>토스트 「저장되었습니다」</t>
-        </is>
-      </c>
-      <c r="N26" s="49" t="inlineStr">
-        <is>
-          <t>화면/29_주문제품-저장.png</t>
-        </is>
-      </c>
-      <c r="O26" s="35" t="inlineStr"/>
-      <c r="P26" s="36" t="inlineStr"/>
-      <c r="Q26" s="36" t="inlineStr"/>
-      <c r="R26" s="36" t="inlineStr"/>
-      <c r="S26" s="36" t="inlineStr"/>
-      <c r="T26" s="35" t="inlineStr"/>
-    </row>
-    <row r="27" ht="82" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>TC-013</t>
-        </is>
-      </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="A26" s="36" t="inlineStr">
+        <is>
+          <t>TC-014</t>
+        </is>
+      </c>
+      <c r="B26" s="37" t="inlineStr">
         <is>
           <t>CASE-01 처방전·일반(10/90)·링크페이</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C26" s="38" t="inlineStr">
         <is>
           <t>연계</t>
         </is>
       </c>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="D26" s="39" t="inlineStr">
         <is>
           <t>주문 생성 및 위드웍스 연계</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
-        <is>
-          <t>TC-012 완료</t>
-        </is>
-      </c>
-      <c r="F27" s="23" t="inlineStr">
+      <c r="E26" s="39" t="inlineStr">
+        <is>
+          <t>TC-013 완료</t>
+        </is>
+      </c>
+      <c r="F26" s="39" t="inlineStr">
         <is>
           <t>주문 등록 › [주문 제품] 탭 하단</t>
         </is>
       </c>
-      <c r="G27" s="23" t="inlineStr">
+      <c r="G26" s="39" t="inlineStr">
         <is>
           <t>/prescriptions/RX-20260907-005</t>
         </is>
       </c>
-      <c r="H27" s="24" t="n">
+      <c r="H26" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="23" t="inlineStr">
+      <c r="I26" s="39" t="inlineStr">
         <is>
           <t>배송 정보를 확인하고 주문을 생성·연계한다</t>
         </is>
       </c>
-      <c r="J27" s="23" t="inlineStr">
+      <c r="J26" s="39" t="inlineStr">
         <is>
           <t>받는 사람: (E)(T3-5)김태오
 주소: 04524 서울특별시 중구 세종대로 110 / 테스트용 주소(3차 5회 김태오)</t>
         </is>
       </c>
-      <c r="K27" s="23" t="inlineStr">
+      <c r="K26" s="39" t="inlineStr">
         <is>
           <t>［주문 생성 및 연계］</t>
         </is>
       </c>
-      <c r="L27" s="25" t="inlineStr">
+      <c r="L26" s="41" t="inlineStr">
         <is>
           <t>POST /prescriptions/{rx}/withworks-order — ① 자사 주문(EUD…) 금액·품목 확정 ② 위드웍스 so_store 호출하여 판매주문(S…) 채번 및 저장 ③ 접수 안내·결제 안내 SMS 2건 발송 ④ 연계 내용을 확인 이메일로 발송 ⑤ 위드웍스가 so.created 웹훅을 회신하여 창고·판매현황 정보가 즉시 반영</t>
         </is>
       </c>
-      <c r="M27" s="26" t="inlineStr">
+      <c r="M26" s="42" t="inlineStr">
         <is>
           <t>① 창고 판매주문 S2609070004 채번
 ② 출고창고 「3PL Main 판매창고」 즉시 표시
 ③ 판매현황 항목 16건이 즉시 채워짐</t>
         </is>
       </c>
+      <c r="N26" s="43" t="inlineStr">
+        <is>
+          <t>화면/30_주문생성및연계.png</t>
+        </is>
+      </c>
+      <c r="O26" s="28" t="inlineStr"/>
+      <c r="P26" s="29" t="inlineStr"/>
+      <c r="Q26" s="29" t="inlineStr"/>
+      <c r="R26" s="29" t="inlineStr"/>
+      <c r="S26" s="29" t="inlineStr"/>
+      <c r="T26" s="28" t="inlineStr"/>
+    </row>
+    <row r="27" ht="82" customHeight="1">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>TC-015</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>CASE-01 처방전·일반(10/90)·링크페이</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>연계</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>위드웍스 판매주문 확인</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>TC-014 완료</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>[위드웍스] 주문 관리 › 판매 주문</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>https://www.demoworks.co.kr/salesorder</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="23" t="inlineStr">
+        <is>
+          <t>위드웍스에서 판매번호로 조회한다</t>
+        </is>
+      </c>
+      <c r="J27" s="23" t="inlineStr">
+        <is>
+          <t>판매번호: S2609070004</t>
+        </is>
+      </c>
+      <c r="K27" s="23" t="inlineStr">
+        <is>
+          <t>［검색］</t>
+        </is>
+      </c>
+      <c r="L27" s="25" t="inlineStr">
+        <is>
+          <t>위드웍스 판매주문 조회. CE Admin 주문번호는 etc SoNo 항목으로 연계된다.</t>
+        </is>
+      </c>
+      <c r="M27" s="26" t="inlineStr">
+        <is>
+          <t>① etc SoNo = EUD202609071734141 (CE 주문번호 일치)
+② 구매 거래처명 = (E)(T3-5)김태오
+③ 출고창고명 = 3PL Main 판매창고
+④ 판매금액 = 810,000
+⑤ 비고 = 업로드 시 입력한 메모 그대로</t>
+        </is>
+      </c>
       <c r="N27" s="27" t="inlineStr">
         <is>
-          <t>화면/30_주문생성및연계.png</t>
+          <t>화면/31_ww_판매주문-화면.png
+화면/32_ww_판매주문-조회결과.png</t>
         </is>
       </c>
       <c r="O27" s="28" t="inlineStr"/>
@@ -3202,77 +3265,77 @@
       <c r="T27" s="28" t="inlineStr"/>
     </row>
     <row r="28" ht="82" customHeight="1">
-      <c r="A28" s="38" t="inlineStr">
-        <is>
-          <t>TC-014</t>
-        </is>
-      </c>
-      <c r="B28" s="39" t="inlineStr">
+      <c r="A28" s="36" t="inlineStr">
+        <is>
+          <t>TC-016</t>
+        </is>
+      </c>
+      <c r="B28" s="37" t="inlineStr">
         <is>
           <t>CASE-01 처방전·일반(10/90)·링크페이</t>
         </is>
       </c>
-      <c r="C28" s="40" t="inlineStr">
-        <is>
-          <t>연계</t>
-        </is>
-      </c>
-      <c r="D28" s="41" t="inlineStr">
-        <is>
-          <t>위드웍스 판매주문 확인</t>
-        </is>
-      </c>
-      <c r="E28" s="41" t="inlineStr">
-        <is>
-          <t>TC-013 완료</t>
-        </is>
-      </c>
-      <c r="F28" s="41" t="inlineStr">
-        <is>
-          <t>[위드웍스] 주문 관리 › 판매 주문</t>
-        </is>
-      </c>
-      <c r="G28" s="41" t="inlineStr">
-        <is>
-          <t>https://www.demoworks.co.kr/salesorder</t>
-        </is>
-      </c>
-      <c r="H28" s="42" t="n">
+      <c r="C28" s="38" t="inlineStr">
+        <is>
+          <t>정산</t>
+        </is>
+      </c>
+      <c r="D28" s="39" t="inlineStr">
+        <is>
+          <t>입금 확인 (담당자 수동)</t>
+        </is>
+      </c>
+      <c r="E28" s="39" t="inlineStr">
+        <is>
+          <t>TC-014 완료</t>
+        </is>
+      </c>
+      <c r="F28" s="39" t="inlineStr">
+        <is>
+          <t>청구ㆍ회계 › 정산/회계</t>
+        </is>
+      </c>
+      <c r="G28" s="39" t="inlineStr">
+        <is>
+          <t>/settlement</t>
+        </is>
+      </c>
+      <c r="H28" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="I28" s="41" t="inlineStr">
-        <is>
-          <t>위드웍스에서 판매번호로 조회한다</t>
-        </is>
-      </c>
-      <c r="J28" s="41" t="inlineStr">
-        <is>
-          <t>판매번호: S2609070004</t>
-        </is>
-      </c>
-      <c r="K28" s="41" t="inlineStr">
-        <is>
-          <t>［검색］</t>
-        </is>
-      </c>
-      <c r="L28" s="43" t="inlineStr">
-        <is>
-          <t>위드웍스 판매주문 조회. CE Admin 주문번호는 etc SoNo 항목으로 연계된다.</t>
-        </is>
-      </c>
-      <c r="M28" s="44" t="inlineStr">
-        <is>
-          <t>① etc SoNo = EUD202609071734141 (CE 주문번호 일치)
-② 구매 거래처명 = (E)(T3-5)김태오
-③ 출고창고명 = 3PL Main 판매창고
-④ 판매금액 = 810,000
-⑤ 비고 = 업로드 시 입력한 메모 그대로</t>
-        </is>
-      </c>
-      <c r="N28" s="45" t="inlineStr">
-        <is>
-          <t>화면/31_ww_판매주문-화면.png
-화면/32_ww_판매주문-조회결과.png</t>
+      <c r="I28" s="39" t="inlineStr">
+        <is>
+          <t>해당 주문의 결제수단을 선택하여 입금을 확인한다</t>
+        </is>
+      </c>
+      <c r="J28" s="39" t="inlineStr">
+        <is>
+          <t>결제수단: 링크페이</t>
+        </is>
+      </c>
+      <c r="K28" s="39" t="inlineStr">
+        <is>
+          <t>결제수단 칸 → 링크페이 선택</t>
+        </is>
+      </c>
+      <c r="L28" s="41" t="inlineStr">
+        <is>
+          <t>POST /settlement/orders/{order}/pay-method — 결제수단 선택 시점이 곧 입금 확인이다. ① 입금 확인 처리 ② 세금계산서 발행 ③ 거래명세서 생성 ④ 위드웍스 판매주문 확정 ⑤ 청구전략상 대상이 아닌 증빙은 자동 제외</t>
+        </is>
+      </c>
+      <c r="M28" s="42" t="inlineStr">
+        <is>
+          <t>① 링크페이 · 81,000원 입금 확인
+② 세금계산서 TI20260907000243 발행
+③ 거래명세서 PDF 생성
+④ 위드웍스 S2609070004 확정
+⑤ 현금영수증은 「청구전략에 없음」으로 제외</t>
+        </is>
+      </c>
+      <c r="N28" s="43" t="inlineStr">
+        <is>
+          <t>화면/33_정산회계-목록.png
+화면/34_입금확인-뒤.png</t>
         </is>
       </c>
       <c r="O28" s="28" t="inlineStr"/>
@@ -3285,7 +3348,7 @@
     <row r="29" ht="82" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>TC-015</t>
+          <t>TC-017</t>
         </is>
       </c>
       <c r="B29" s="21" t="inlineStr">
@@ -3295,27 +3358,27 @@
       </c>
       <c r="C29" s="22" t="inlineStr">
         <is>
-          <t>정산</t>
+          <t>청구</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
         <is>
-          <t>입금 확인 (담당자 수동)</t>
+          <t>공단 등록 서류 팩스 발송</t>
         </is>
       </c>
       <c r="E29" s="23" t="inlineStr">
         <is>
-          <t>TC-013 완료</t>
+          <t>TC-012 완료 · 팩스 발송=우리에게만</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t>청구ㆍ회계 › 정산/회계</t>
+          <t>주문 등록 › 상단 [팩스 발송] 팝오버</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
         <is>
-          <t>/settlement</t>
+          <t>/prescriptions/RX-20260907-005</t>
         </is>
       </c>
       <c r="H29" s="24" t="n">
@@ -3323,37 +3386,34 @@
       </c>
       <c r="I29" s="23" t="inlineStr">
         <is>
-          <t>해당 주문의 결제수단을 선택하여 입금을 확인한다</t>
+          <t>수신처와 전송 서류를 확인한다</t>
         </is>
       </c>
       <c r="J29" s="23" t="inlineStr">
         <is>
-          <t>결제수단: 링크페이</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="23" t="inlineStr">
         <is>
-          <t>결제수단 칸 → 링크페이 선택</t>
+          <t>［팩스 발송］</t>
         </is>
       </c>
       <c r="L29" s="25" t="inlineStr">
         <is>
-          <t>POST /settlement/orders/{order}/pay-method — 결제수단 선택 시점이 곧 입금 확인. ① 입금 확인 처리 ② 세금계산서 발행 ③ 거래명세서 생성 ④ 위드웍스 판매주문 확정 ⑤ 청구전략상 대상이 아닌 증빙은 자동 제외</t>
+          <t>자격이 [일반]이므로 수신처가 건강보험공단으로 구성되고, 관할 청구처의 팩스번호가 자동 표시된다</t>
         </is>
       </c>
       <c r="M29" s="26" t="inlineStr">
         <is>
-          <t>① 링크페이 · 81,000원 입금 확인
-② 세금계산서 TI20260907000243 발행
-③ 거래명세서 PDF 생성
-④ 위드웍스 S2609070004 확정
-⑤ 현금영수증은 「청구전략에 없음」으로 제외</t>
+          <t>① 수신처 = 국민건강보험공단 · 공단 중구지사 · 보험급여부
+② 수신 팩스번호 = 02-0000-0000
+③ 신청 파일 11건 전체 선택 상태</t>
         </is>
       </c>
       <c r="N29" s="27" t="inlineStr">
         <is>
-          <t>화면/33_정산회계-목록.png
-화면/34_입금확인-뒤.png</t>
+          <t>화면/35_팩스발송-창.png</t>
         </is>
       </c>
       <c r="O29" s="28" t="inlineStr"/>
@@ -3364,199 +3424,199 @@
       <c r="T29" s="28" t="inlineStr"/>
     </row>
     <row r="30" ht="82" customHeight="1">
-      <c r="A30" s="38" t="inlineStr">
-        <is>
-          <t>TC-016</t>
-        </is>
-      </c>
-      <c r="B30" s="39" t="inlineStr">
-        <is>
-          <t>CASE-01 처방전·일반(10/90)·링크페이</t>
-        </is>
-      </c>
-      <c r="C30" s="40" t="inlineStr">
-        <is>
-          <t>청구</t>
-        </is>
-      </c>
-      <c r="D30" s="41" t="inlineStr">
-        <is>
-          <t>공단 등록 서류 팩스 발송</t>
-        </is>
-      </c>
-      <c r="E30" s="41" t="inlineStr">
-        <is>
-          <t>TC-011 완료 · 팩스 발송=우리에게만</t>
-        </is>
-      </c>
-      <c r="F30" s="41" t="inlineStr">
-        <is>
-          <t>주문 등록 › 상단 [팩스 발송] 팝오버</t>
-        </is>
-      </c>
-      <c r="G30" s="41" t="inlineStr">
-        <is>
-          <t>/prescriptions/RX-20260907-005</t>
-        </is>
-      </c>
-      <c r="H30" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="41" t="inlineStr">
-        <is>
-          <t>수신처와 전송 서류를 확인한다</t>
-        </is>
-      </c>
-      <c r="J30" s="41" t="inlineStr">
+      <c r="A30" s="30" t="n"/>
+      <c r="B30" s="30" t="n"/>
+      <c r="C30" s="30" t="n"/>
+      <c r="D30" s="30" t="n"/>
+      <c r="E30" s="30" t="n"/>
+      <c r="F30" s="30" t="n"/>
+      <c r="G30" s="30" t="n"/>
+      <c r="H30" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>팩스를 전송한다</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K30" s="41" t="inlineStr">
-        <is>
-          <t>［팩스 발송］</t>
-        </is>
-      </c>
-      <c r="L30" s="43" t="inlineStr">
-        <is>
-          <t>자격이 [일반]이므로 수신처가 건강보험공단으로 구성되고, 관할 청구처의 팩스번호가 자동 표시된다</t>
-        </is>
-      </c>
-      <c r="M30" s="44" t="inlineStr">
-        <is>
-          <t>① 수신처 = 국민건강보험공단 · 공단 중구지사 · 보험급여부
-② 수신 팩스번호 = 02-0000-0000
-③ 신청 파일 11건 전체 선택 상태</t>
-        </is>
-      </c>
-      <c r="N30" s="45" t="inlineStr">
-        <is>
-          <t>화면/35_팩스발송-창.png</t>
-        </is>
-      </c>
-      <c r="O30" s="28" t="inlineStr"/>
-      <c r="P30" s="29" t="inlineStr"/>
-      <c r="Q30" s="29" t="inlineStr"/>
-      <c r="R30" s="29" t="inlineStr"/>
-      <c r="S30" s="29" t="inlineStr"/>
-      <c r="T30" s="28" t="inlineStr"/>
-    </row>
-    <row r="31" ht="82" customHeight="1">
-      <c r="A31" s="37" t="n"/>
-      <c r="B31" s="37" t="n"/>
-      <c r="C31" s="37" t="n"/>
-      <c r="D31" s="37" t="n"/>
-      <c r="E31" s="37" t="n"/>
-      <c r="F31" s="37" t="n"/>
-      <c r="G31" s="37" t="n"/>
-      <c r="H31" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="I31" s="15" t="inlineStr">
-        <is>
-          <t>팩스를 전송한다</t>
-        </is>
-      </c>
-      <c r="J31" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K31" s="15" t="inlineStr">
+      <c r="K30" s="6" t="inlineStr">
         <is>
           <t>［팩스 전송］</t>
         </is>
       </c>
-      <c r="L31" s="47" t="inlineStr">
+      <c r="L30" s="32" t="inlineStr">
         <is>
           <t>POST /prescriptions/{rx}/fax — ① 선택 서류를 표지 포함 단일 PDF로 병합 ② 팝빌로 전송 ③ 접수번호를 발송 이력에 기록. [우리에게만]이면 수신번호만 테스트 팩스로 치환하고 수신처명은 유지한다.</t>
         </is>
       </c>
-      <c r="M31" s="48" t="inlineStr">
+      <c r="M30" s="48" t="inlineStr">
         <is>
           <t>① 팩스통합본 PDF 생성
 ② 로그: 국민건강보험공단 0200000000 → 05041341393 치환
 ③ 팝빌 접수번호 채번</t>
         </is>
       </c>
-      <c r="N31" s="49" t="inlineStr">
+      <c r="N30" s="33" t="inlineStr">
         <is>
           <t>화면/36_팩스발송-결과.png</t>
         </is>
       </c>
-      <c r="O31" s="35" t="inlineStr"/>
-      <c r="P31" s="36" t="inlineStr"/>
-      <c r="Q31" s="36" t="inlineStr"/>
-      <c r="R31" s="36" t="inlineStr"/>
-      <c r="S31" s="36" t="inlineStr"/>
-      <c r="T31" s="35" t="inlineStr"/>
-    </row>
-    <row r="32" ht="82" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>TC-017</t>
-        </is>
-      </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="O30" s="34" t="inlineStr"/>
+      <c r="P30" s="35" t="inlineStr"/>
+      <c r="Q30" s="35" t="inlineStr"/>
+      <c r="R30" s="35" t="inlineStr"/>
+      <c r="S30" s="35" t="inlineStr"/>
+      <c r="T30" s="34" t="inlineStr"/>
+    </row>
+    <row r="31" ht="82" customHeight="1">
+      <c r="A31" s="36" t="inlineStr">
+        <is>
+          <t>TC-018</t>
+        </is>
+      </c>
+      <c r="B31" s="37" t="inlineStr">
         <is>
           <t>CASE-01 처방전·일반(10/90)·링크페이</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C31" s="38" t="inlineStr">
         <is>
           <t>검증</t>
         </is>
       </c>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="D31" s="39" t="inlineStr">
         <is>
           <t>최종 상태 검증</t>
         </is>
       </c>
-      <c r="E32" s="23" t="inlineStr">
-        <is>
-          <t>TC-001 ~ TC-016 완료</t>
-        </is>
-      </c>
-      <c r="F32" s="23" t="inlineStr">
+      <c r="E31" s="39" t="inlineStr">
+        <is>
+          <t>TC-001 ~ TC-017 완료</t>
+        </is>
+      </c>
+      <c r="F31" s="39" t="inlineStr">
         <is>
           <t>주문ㆍ재구매 › 주문 관리 / Finance</t>
         </is>
       </c>
-      <c r="G32" s="23" t="inlineStr">
+      <c r="G31" s="39" t="inlineStr">
         <is>
           <t>/orders · /finance</t>
         </is>
       </c>
-      <c r="H32" s="24" t="n">
+      <c r="H31" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="I32" s="23" t="inlineStr">
+      <c r="I31" s="39" t="inlineStr">
         <is>
           <t>주문·창고·증빙 상태를 최종 확인한다</t>
         </is>
       </c>
-      <c r="J32" s="23" t="inlineStr">
+      <c r="J31" s="39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K32" s="23" t="inlineStr">
+      <c r="K31" s="39" t="inlineStr">
         <is>
           <t>목록 조회</t>
         </is>
       </c>
-      <c r="L32" s="25" t="inlineStr">
+      <c r="L31" s="41" t="inlineStr">
         <is>
           <t>전 구간 처리 결과 확인</t>
         </is>
       </c>
-      <c r="M32" s="26" t="inlineStr">
+      <c r="M31" s="42" t="inlineStr">
         <is>
           <t>① 처방전 RX-20260907-005 = 검수 완료
 ② 주문 EUD202609071734141 = confirmed
 ③ 창고 S2609070004 = 확정
 ④ 세금계산서 TI20260907000243 발행
 ⑤ 공단 팩스 발송 완료</t>
+        </is>
+      </c>
+      <c r="N31" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O31" s="28" t="inlineStr"/>
+      <c r="P31" s="29" t="inlineStr"/>
+      <c r="Q31" s="29" t="inlineStr"/>
+      <c r="R31" s="29" t="inlineStr"/>
+      <c r="S31" s="29" t="inlineStr"/>
+      <c r="T31" s="28" t="inlineStr"/>
+    </row>
+    <row r="32" ht="82" customHeight="1">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>TC-019</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>CASE-01 처방전·일반(10/90)·링크페이</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>검증</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>목록 항목 검증 (판매현황 연계)</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>TC-014 완료</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>Finance / 주문 관리</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>/finance</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="23" t="inlineStr">
+        <is>
+          <t>Finance 목록에서 위드웍스 판매현황 항목이 표시되는지 확인한다</t>
+        </is>
+      </c>
+      <c r="J32" s="23" t="inlineStr">
+        <is>
+          <t>조회 기간: 2026-09-01 ~ 2026-09-30</t>
+        </is>
+      </c>
+      <c r="K32" s="23" t="inlineStr">
+        <is>
+          <t>［검색］</t>
+        </is>
+      </c>
+      <c r="L32" s="25" t="inlineStr">
+        <is>
+          <t>ceWwCols() — Finance·주문 관리·입금 내역·현금영수증·청구 관리·교환/반품/취소 6개 화면이 동일한 위드웍스 판매현황 항목 순서를 공유한다</t>
+        </is>
+      </c>
+      <c r="M32" s="26" t="inlineStr">
+        <is>
+          <t>① 출고창고·납품창고 항목 표시
+② 유형·구매 거래처·매출 금액·제품그룹 등 판매현황 항목이 값과 함께 표시
+③ 구분(SB/SCI)·주민등록번호(마스킹)·상병코드·횟수는 자사 데이터로 표시</t>
         </is>
       </c>
       <c r="N32" s="27" t="inlineStr">
@@ -3571,149 +3631,78 @@
       <c r="S32" s="29" t="inlineStr"/>
       <c r="T32" s="28" t="inlineStr"/>
     </row>
-    <row r="33" ht="82" customHeight="1">
-      <c r="A33" s="38" t="inlineStr">
-        <is>
-          <t>TC-018</t>
-        </is>
-      </c>
-      <c r="B33" s="39" t="inlineStr">
-        <is>
-          <t>CASE-01 처방전·일반(10/90)·링크페이</t>
-        </is>
-      </c>
-      <c r="C33" s="40" t="inlineStr">
-        <is>
-          <t>검증</t>
-        </is>
-      </c>
-      <c r="D33" s="41" t="inlineStr">
-        <is>
-          <t>목록 항목 검증 (판매현황 연계)</t>
-        </is>
-      </c>
-      <c r="E33" s="41" t="inlineStr">
-        <is>
-          <t>TC-013 완료</t>
-        </is>
-      </c>
-      <c r="F33" s="41" t="inlineStr">
-        <is>
-          <t>Finance / 주문 관리</t>
-        </is>
-      </c>
-      <c r="G33" s="41" t="inlineStr">
-        <is>
-          <t>/finance</t>
-        </is>
-      </c>
-      <c r="H33" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" s="41" t="inlineStr">
-        <is>
-          <t>Finance 목록에서 위드웍스 판매현황 항목이 표시되는지 확인한다</t>
-        </is>
-      </c>
-      <c r="J33" s="41" t="inlineStr">
-        <is>
-          <t>조회 기간: 2026-09-01 ~ 2026-09-30</t>
-        </is>
-      </c>
-      <c r="K33" s="41" t="inlineStr">
-        <is>
-          <t>［검색］</t>
-        </is>
-      </c>
-      <c r="L33" s="43" t="inlineStr">
-        <is>
-          <t>ceWwCols() — Finance·주문 관리·입금 내역·현금영수증·청구 관리·교환/반품/취소 6개 화면이 동일한 위드웍스 판매현황 항목 순서를 공유한다</t>
-        </is>
-      </c>
-      <c r="M33" s="44" t="inlineStr">
-        <is>
-          <t>① 출고창고·납품창고 항목 표시
-② 유형·구매 거래처·매출 금액·제품그룹 등 판매현황 항목이 값과 함께 표시
-③ 구분(SB/SCI)·주민등록번호(마스킹)·상병코드·횟수는 자사 데이터로 표시</t>
-        </is>
-      </c>
-      <c r="N33" s="45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O33" s="28" t="inlineStr"/>
-      <c r="P33" s="29" t="inlineStr"/>
-      <c r="Q33" s="29" t="inlineStr"/>
-      <c r="R33" s="29" t="inlineStr"/>
-      <c r="S33" s="29" t="inlineStr"/>
-      <c r="T33" s="28" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:T33"/>
-  <mergeCells count="59">
-    <mergeCell ref="C30:C31"/>
+  <autoFilter ref="A2:T32"/>
+  <mergeCells count="66">
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="A24:A25"/>
     <mergeCell ref="O1:T1"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="D21:D24"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G21:G24"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="F3:F6"/>
-    <mergeCell ref="F21:F24"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="G3:G6"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="A21:A24"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="C21:C24"/>
-    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C20:C23"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="E20:E23"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="F20:F23"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="B24:B25"/>
     <mergeCell ref="H1:N1"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="G29:G30"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="D3:D6"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E3:E6"/>
-    <mergeCell ref="E21:E24"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="G20:G23"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="D20:D23"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="C5:C6"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="P3:P33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P3:P32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,N/A,Blocked"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3829,7 +3818,7 @@
       </c>
       <c r="B2" s="52" t="inlineStr">
         <is>
-          <t>TC-004</t>
+          <t>TC-005</t>
         </is>
       </c>
       <c r="C2" s="53" t="inlineStr">
@@ -3896,7 +3885,7 @@
       </c>
       <c r="B3" s="55" t="inlineStr">
         <is>
-          <t>TC-005</t>
+          <t>TC-006</t>
         </is>
       </c>
       <c r="C3" s="56" t="inlineStr">
@@ -3963,7 +3952,7 @@
       </c>
       <c r="B4" s="52" t="inlineStr">
         <is>
-          <t>TC-011</t>
+          <t>TC-012</t>
         </is>
       </c>
       <c r="C4" s="53" t="inlineStr">
@@ -4115,17 +4104,17 @@
       </c>
       <c r="C3" s="55" t="inlineStr">
         <is>
-          <t>TC-001</t>
-        </is>
-      </c>
-      <c r="D3" s="56" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+          <t>TC-002</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>팝업</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>거래처 관리 목록</t>
+          <t>거래처 조회 팝업 › [신규] 등록</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4129,7 @@
       </c>
       <c r="C4" s="52" t="inlineStr">
         <is>
-          <t>TC-001</t>
+          <t>TC-002</t>
         </is>
       </c>
       <c r="D4" s="57" t="inlineStr">
@@ -4165,7 +4154,7 @@
       </c>
       <c r="C5" s="55" t="inlineStr">
         <is>
-          <t>TC-001</t>
+          <t>TC-002</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -4190,7 +4179,7 @@
       </c>
       <c r="C6" s="52" t="inlineStr">
         <is>
-          <t>TC-001</t>
+          <t>TC-002</t>
         </is>
       </c>
       <c r="D6" s="53" t="inlineStr">
@@ -4215,7 +4204,7 @@
       </c>
       <c r="C7" s="55" t="inlineStr">
         <is>
-          <t>TC-002</t>
+          <t>TC-001</t>
         </is>
       </c>
       <c r="D7" s="56" t="inlineStr">
@@ -4240,7 +4229,7 @@
       </c>
       <c r="C8" s="52" t="inlineStr">
         <is>
-          <t>TC-002</t>
+          <t>TC-003</t>
         </is>
       </c>
       <c r="D8" s="53" t="inlineStr">
@@ -4265,7 +4254,7 @@
       </c>
       <c r="C9" s="55" t="inlineStr">
         <is>
-          <t>TC-002</t>
+          <t>TC-003</t>
         </is>
       </c>
       <c r="D9" s="56" t="inlineStr">
@@ -4290,7 +4279,7 @@
       </c>
       <c r="C10" s="52" t="inlineStr">
         <is>
-          <t>TC-003</t>
+          <t>TC-004</t>
         </is>
       </c>
       <c r="D10" s="53" t="inlineStr">
@@ -4315,7 +4304,7 @@
       </c>
       <c r="C11" s="55" t="inlineStr">
         <is>
-          <t>TC-004</t>
+          <t>TC-005</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -4340,7 +4329,7 @@
       </c>
       <c r="C12" s="52" t="inlineStr">
         <is>
-          <t>TC-005</t>
+          <t>TC-006</t>
         </is>
       </c>
       <c r="D12" s="57" t="inlineStr">
@@ -4365,7 +4354,7 @@
       </c>
       <c r="C13" s="55" t="inlineStr">
         <is>
-          <t>TC-005</t>
+          <t>TC-006</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -4390,7 +4379,7 @@
       </c>
       <c r="C14" s="52" t="inlineStr">
         <is>
-          <t>TC-005</t>
+          <t>TC-006</t>
         </is>
       </c>
       <c r="D14" s="53" t="inlineStr">
@@ -4415,7 +4404,7 @@
       </c>
       <c r="C15" s="55" t="inlineStr">
         <is>
-          <t>TC-006</t>
+          <t>TC-007</t>
         </is>
       </c>
       <c r="D15" s="56" t="inlineStr">
@@ -4440,7 +4429,7 @@
       </c>
       <c r="C16" s="52" t="inlineStr">
         <is>
-          <t>TC-007</t>
+          <t>TC-008</t>
         </is>
       </c>
       <c r="D16" s="57" t="inlineStr">
@@ -4465,7 +4454,7 @@
       </c>
       <c r="C17" s="55" t="inlineStr">
         <is>
-          <t>TC-007</t>
+          <t>TC-008</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -4490,7 +4479,7 @@
       </c>
       <c r="C18" s="52" t="inlineStr">
         <is>
-          <t>TC-007</t>
+          <t>TC-008</t>
         </is>
       </c>
       <c r="D18" s="53" t="inlineStr">
@@ -4515,7 +4504,7 @@
       </c>
       <c r="C19" s="55" t="inlineStr">
         <is>
-          <t>TC-008</t>
+          <t>TC-009</t>
         </is>
       </c>
       <c r="D19" s="56" t="inlineStr">
@@ -4540,7 +4529,7 @@
       </c>
       <c r="C20" s="52" t="inlineStr">
         <is>
-          <t>TC-009</t>
+          <t>TC-010</t>
         </is>
       </c>
       <c r="D20" s="57" t="inlineStr">
@@ -4565,7 +4554,7 @@
       </c>
       <c r="C21" s="55" t="inlineStr">
         <is>
-          <t>TC-009</t>
+          <t>TC-010</t>
         </is>
       </c>
       <c r="D21" s="56" t="inlineStr">
@@ -4590,7 +4579,7 @@
       </c>
       <c r="C22" s="52" t="inlineStr">
         <is>
-          <t>TC-010</t>
+          <t>TC-011</t>
         </is>
       </c>
       <c r="D22" s="57" t="inlineStr">
@@ -4615,7 +4604,7 @@
       </c>
       <c r="C23" s="55" t="inlineStr">
         <is>
-          <t>TC-010</t>
+          <t>TC-011</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -4640,7 +4629,7 @@
       </c>
       <c r="C24" s="52" t="inlineStr">
         <is>
-          <t>TC-011</t>
+          <t>TC-012</t>
         </is>
       </c>
       <c r="D24" s="58" t="inlineStr">
@@ -4665,7 +4654,7 @@
       </c>
       <c r="C25" s="55" t="inlineStr">
         <is>
-          <t>TC-011</t>
+          <t>TC-012</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
@@ -4690,7 +4679,7 @@
       </c>
       <c r="C26" s="52" t="inlineStr">
         <is>
-          <t>TC-011</t>
+          <t>TC-012</t>
         </is>
       </c>
       <c r="D26" s="58" t="inlineStr">
@@ -4715,7 +4704,7 @@
       </c>
       <c r="C27" s="55" t="inlineStr">
         <is>
-          <t>TC-011</t>
+          <t>TC-012</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
@@ -4740,7 +4729,7 @@
       </c>
       <c r="C28" s="52" t="inlineStr">
         <is>
-          <t>TC-011</t>
+          <t>TC-012</t>
         </is>
       </c>
       <c r="D28" s="58" t="inlineStr">
@@ -4765,7 +4754,7 @@
       </c>
       <c r="C29" s="55" t="inlineStr">
         <is>
-          <t>TC-012</t>
+          <t>TC-013</t>
         </is>
       </c>
       <c r="D29" s="56" t="inlineStr">
@@ -4790,7 +4779,7 @@
       </c>
       <c r="C30" s="52" t="inlineStr">
         <is>
-          <t>TC-012</t>
+          <t>TC-013</t>
         </is>
       </c>
       <c r="D30" s="57" t="inlineStr">
@@ -4815,7 +4804,7 @@
       </c>
       <c r="C31" s="55" t="inlineStr">
         <is>
-          <t>TC-012</t>
+          <t>TC-013</t>
         </is>
       </c>
       <c r="D31" s="56" t="inlineStr">
@@ -4840,7 +4829,7 @@
       </c>
       <c r="C32" s="52" t="inlineStr">
         <is>
-          <t>TC-012</t>
+          <t>TC-013</t>
         </is>
       </c>
       <c r="D32" s="53" t="inlineStr">
@@ -4865,7 +4854,7 @@
       </c>
       <c r="C33" s="55" t="inlineStr">
         <is>
-          <t>TC-013</t>
+          <t>TC-014</t>
         </is>
       </c>
       <c r="D33" s="56" t="inlineStr">
@@ -4890,7 +4879,7 @@
       </c>
       <c r="C34" s="52" t="inlineStr">
         <is>
-          <t>TC-014</t>
+          <t>TC-015</t>
         </is>
       </c>
       <c r="D34" s="59" t="inlineStr">
@@ -4915,7 +4904,7 @@
       </c>
       <c r="C35" s="55" t="inlineStr">
         <is>
-          <t>TC-014</t>
+          <t>TC-015</t>
         </is>
       </c>
       <c r="D35" s="60" t="inlineStr">
@@ -4940,7 +4929,7 @@
       </c>
       <c r="C36" s="52" t="inlineStr">
         <is>
-          <t>TC-015</t>
+          <t>TC-016</t>
         </is>
       </c>
       <c r="D36" s="53" t="inlineStr">
@@ -4965,7 +4954,7 @@
       </c>
       <c r="C37" s="55" t="inlineStr">
         <is>
-          <t>TC-015</t>
+          <t>TC-016</t>
         </is>
       </c>
       <c r="D37" s="56" t="inlineStr">
@@ -4990,7 +4979,7 @@
       </c>
       <c r="C38" s="52" t="inlineStr">
         <is>
-          <t>TC-016</t>
+          <t>TC-017</t>
         </is>
       </c>
       <c r="D38" s="57" t="inlineStr">
@@ -5015,7 +5004,7 @@
       </c>
       <c r="C39" s="55" t="inlineStr">
         <is>
-          <t>TC-016</t>
+          <t>TC-017</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">

--- a/테스트/테스트3차/5회/김태오/테스트시나리오_김태오.xlsx
+++ b/테스트/테스트3차/5회/김태오/테스트시나리오_김태오.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'환경설정'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'테스트시나리오'!$A$2:$T$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'테스트시나리오'!$A$2:$S$32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'테스트시나리오'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'결함관리'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'캡처목록'!$1:$1</definedName>
@@ -1415,7 +1415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T32"/>
+  <dimension ref="A1:S32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1423,21 +1423,20 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="52" customWidth="1" min="12" max="12"/>
-    <col width="46" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="52" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1451,28 +1450,27 @@
       <c r="D1" s="19" t="n"/>
       <c r="E1" s="19" t="n"/>
       <c r="F1" s="19" t="n"/>
-      <c r="G1" s="19" t="n"/>
-      <c r="H1" s="18" t="inlineStr">
+      <c r="G1" s="18" t="inlineStr">
         <is>
           <t>수행 절차</t>
         </is>
       </c>
+      <c r="H1" s="19" t="n"/>
       <c r="I1" s="19" t="n"/>
       <c r="J1" s="19" t="n"/>
       <c r="K1" s="19" t="n"/>
       <c r="L1" s="19" t="n"/>
       <c r="M1" s="19" t="n"/>
-      <c r="N1" s="19" t="n"/>
-      <c r="O1" s="18" t="inlineStr">
+      <c r="N1" s="18" t="inlineStr">
         <is>
           <t>수행 결과 (테스터 기입)</t>
         </is>
       </c>
+      <c r="O1" s="19" t="n"/>
       <c r="P1" s="19" t="n"/>
       <c r="Q1" s="19" t="n"/>
       <c r="R1" s="19" t="n"/>
       <c r="S1" s="19" t="n"/>
-      <c r="T1" s="19" t="n"/>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
@@ -1507,70 +1505,65 @@
       </c>
       <c r="G2" s="13" t="inlineStr">
         <is>
-          <t>URL</t>
+          <t>STEP</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
-          <t>STEP</t>
+          <t>수행 절차</t>
         </is>
       </c>
       <c r="I2" s="13" t="inlineStr">
         <is>
-          <t>수행 절차</t>
+          <t>입력 데이터</t>
         </is>
       </c>
       <c r="J2" s="13" t="inlineStr">
         <is>
-          <t>입력 데이터</t>
+          <t>클릭 대상 (탭/버튼)</t>
         </is>
       </c>
       <c r="K2" s="13" t="inlineStr">
         <is>
-          <t>클릭 대상 (탭/버튼)</t>
+          <t>트리거 / 연결 동작</t>
         </is>
       </c>
       <c r="L2" s="13" t="inlineStr">
         <is>
-          <t>트리거 / 연결 동작</t>
+          <t>기대 결과</t>
         </is>
       </c>
       <c r="M2" s="13" t="inlineStr">
         <is>
-          <t>기대 결과</t>
+          <t>캡처 파일</t>
         </is>
       </c>
       <c r="N2" s="13" t="inlineStr">
         <is>
-          <t>캡처 파일</t>
+          <t>실제 결과</t>
         </is>
       </c>
       <c r="O2" s="13" t="inlineStr">
         <is>
-          <t>실제 결과</t>
+          <t>판정</t>
         </is>
       </c>
       <c r="P2" s="13" t="inlineStr">
         <is>
-          <t>판정</t>
+          <t>결함번호</t>
         </is>
       </c>
       <c r="Q2" s="13" t="inlineStr">
         <is>
-          <t>결함번호</t>
+          <t>수행자</t>
         </is>
       </c>
       <c r="R2" s="13" t="inlineStr">
         <is>
-          <t>수행자</t>
+          <t>수행일</t>
         </is>
       </c>
       <c r="S2" s="13" t="inlineStr">
-        <is>
-          <t>수행일</t>
-        </is>
-      </c>
-      <c r="T2" s="13" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -1607,50 +1600,45 @@
           <t>환자ㆍ처방 › 처방자료 업로드</t>
         </is>
       </c>
-      <c r="G3" s="23" t="inlineStr">
-        <is>
-          <t>/prescriptions/upload</t>
-        </is>
-      </c>
-      <c r="H3" s="24" t="n">
+      <c r="G3" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="H3" s="23" t="inlineStr">
+        <is>
+          <t>처방자료 업로드 화면을 연다</t>
+        </is>
+      </c>
       <c r="I3" s="23" t="inlineStr">
         <is>
-          <t>처방자료 업로드 화면을 연다</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J3" s="23" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K3" s="23" t="inlineStr">
-        <is>
           <t>좌측 메뉴 ［처방자료 업로드］</t>
         </is>
       </c>
-      <c r="L3" s="25" t="inlineStr">
+      <c r="K3" s="25" t="inlineStr">
         <is>
           <t>업무 시작점. 처방전이 접수되면 이 화면에서 시작한다.</t>
         </is>
       </c>
-      <c r="M3" s="26" t="inlineStr">
+      <c r="L3" s="26" t="inlineStr">
         <is>
           <t>업로드 화면이 열리고 [이름 선택]이 비어 있다</t>
         </is>
       </c>
-      <c r="N3" s="27" t="inlineStr">
+      <c r="M3" s="27" t="inlineStr">
         <is>
           <t>화면/05_처방자료업로드-빈화면.png</t>
         </is>
       </c>
-      <c r="O3" s="28" t="inlineStr"/>
+      <c r="N3" s="28" t="inlineStr"/>
+      <c r="O3" s="29" t="inlineStr"/>
       <c r="P3" s="29" t="inlineStr"/>
       <c r="Q3" s="29" t="inlineStr"/>
       <c r="R3" s="29" t="inlineStr"/>
-      <c r="S3" s="29" t="inlineStr"/>
-      <c r="T3" s="28" t="inlineStr"/>
+      <c r="S3" s="28" t="inlineStr"/>
     </row>
     <row r="4" ht="82" customHeight="1">
       <c r="A4" s="30" t="n"/>
@@ -1659,46 +1647,45 @@
       <c r="D4" s="30" t="n"/>
       <c r="E4" s="30" t="n"/>
       <c r="F4" s="30" t="n"/>
-      <c r="G4" s="30" t="n"/>
-      <c r="H4" s="31" t="n">
+      <c r="G4" s="31" t="n">
         <v>2</v>
       </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>환자를 조회한다</t>
+        </is>
+      </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>환자를 조회한다</t>
+          <t>검색어: 김태오</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>검색어: 김태오</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
           <t>［조회］</t>
         </is>
       </c>
-      <c r="L4" s="32" t="inlineStr">
+      <c r="K4" s="32" t="inlineStr">
         <is>
           <t>pkOpen() — 거래처 조회 팝업. 이름 또는 연락처로 검색한다.</t>
         </is>
       </c>
-      <c r="M4" s="16" t="inlineStr">
+      <c r="L4" s="16" t="inlineStr">
         <is>
           <t>★ 검색 결과 0건 — 신규 환자이므로 미등록 상태 (기등록 환자면 TC-002 생략)</t>
         </is>
       </c>
-      <c r="N4" s="33" t="inlineStr">
+      <c r="M4" s="33" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O4" s="34" t="inlineStr"/>
+      <c r="N4" s="34" t="inlineStr"/>
+      <c r="O4" s="35" t="inlineStr"/>
       <c r="P4" s="35" t="inlineStr"/>
       <c r="Q4" s="35" t="inlineStr"/>
       <c r="R4" s="35" t="inlineStr"/>
-      <c r="S4" s="35" t="inlineStr"/>
-      <c r="T4" s="34" t="inlineStr"/>
+      <c r="S4" s="34" t="inlineStr"/>
     </row>
     <row r="5" ht="82" customHeight="1">
       <c r="A5" s="36" t="inlineStr">
@@ -1731,52 +1718,47 @@
           <t>처방자료 업로드 › [조회] 팝업</t>
         </is>
       </c>
-      <c r="G5" s="39" t="inlineStr">
-        <is>
-          <t>/prescriptions/upload</t>
-        </is>
-      </c>
-      <c r="H5" s="40" t="n">
+      <c r="G5" s="40" t="n">
         <v>1</v>
       </c>
+      <c r="H5" s="39" t="inlineStr">
+        <is>
+          <t>조회 결과가 없을 때 나타나는 [신규] 버튼을 누른다</t>
+        </is>
+      </c>
       <c r="I5" s="39" t="inlineStr">
-        <is>
-          <t>조회 결과가 없을 때 나타나는 [신규] 버튼을 누른다</t>
-        </is>
-      </c>
-      <c r="J5" s="39" t="inlineStr">
         <is>
           <t>이름: (T3-5)김태오
 주민등록번호: 850203-1000001</t>
         </is>
       </c>
-      <c r="K5" s="39" t="inlineStr">
+      <c r="J5" s="39" t="inlineStr">
         <is>
           <t>［신규］</t>
         </is>
       </c>
-      <c r="L5" s="41" t="inlineStr">
+      <c r="K5" s="41" t="inlineStr">
         <is>
           <t>pkCreate() — 조회 결과가 없을 때만 [신규] 버튼이 노출된다. 조회된 사람이 있으면 숨겨 동일인 중복 등록을 막는다. 등록 전 주민번호 앞자리로 중복 여부를 재확인한다.</t>
         </is>
       </c>
-      <c r="M5" s="42" t="inlineStr">
+      <c r="L5" s="42" t="inlineStr">
         <is>
           <t>① 거래처가 등록되고 [이름 선택]에 자동 반영
 ② 사업부 IC이면 이름 앞에 (E) 자동 부여</t>
         </is>
       </c>
-      <c r="N5" s="43" t="inlineStr">
+      <c r="M5" s="43" t="inlineStr">
         <is>
           <t>화면/01_거래처관리-목록.png</t>
         </is>
       </c>
-      <c r="O5" s="28" t="inlineStr"/>
+      <c r="N5" s="28" t="inlineStr"/>
+      <c r="O5" s="29" t="inlineStr"/>
       <c r="P5" s="29" t="inlineStr"/>
       <c r="Q5" s="29" t="inlineStr"/>
       <c r="R5" s="29" t="inlineStr"/>
-      <c r="S5" s="29" t="inlineStr"/>
-      <c r="T5" s="28" t="inlineStr"/>
+      <c r="S5" s="28" t="inlineStr"/>
     </row>
     <row r="6" ht="82" customHeight="1">
       <c r="A6" s="30" t="n"/>
@@ -1785,16 +1767,15 @@
       <c r="D6" s="30" t="n"/>
       <c r="E6" s="30" t="n"/>
       <c r="F6" s="30" t="n"/>
-      <c r="G6" s="30" t="n"/>
-      <c r="H6" s="44" t="n">
+      <c r="G6" s="44" t="n">
         <v>2</v>
       </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>거래처 상세 정보를 보완 입력한다</t>
+        </is>
+      </c>
       <c r="I6" s="15" t="inlineStr">
-        <is>
-          <t>거래처 상세 정보를 보완 입력한다</t>
-        </is>
-      </c>
-      <c r="J6" s="15" t="inlineStr">
         <is>
           <t>사업부: IC (카테터) / 성별: 남 / 환자구분: SB-N
 연락 상태: 정상 / 연락 선호: 업무폰2586 문자
@@ -1806,36 +1787,36 @@
 건보등록: 신규 등록 완료 · 2026-09-07</t>
         </is>
       </c>
-      <c r="K6" s="15" t="inlineStr">
+      <c r="J6" s="15" t="inlineStr">
         <is>
           <t>［거래처 수정］ 또는 환자ㆍ처방 › 거래처 관리</t>
         </is>
       </c>
-      <c r="L6" s="45" t="inlineStr">
+      <c r="K6" s="45" t="inlineStr">
         <is>
           <t>POST/PUT /patients — ① 주민번호 암호화 저장 + 마스킹값 별도 보관 ② 주민번호 입력 시 생년월일 자동 계산(peBirthFromRrn) ③ 만 19세 미만이면 [보호자] 입력 영역이 자동 노출</t>
         </is>
       </c>
-      <c r="M6" s="46" t="inlineStr">
+      <c r="L6" s="46" t="inlineStr">
         <is>
           <t>① 생년월일 1985-02-03 자동 입력
 ② 만 41세 성년이므로 [보호자] 영역 미노출
 ③ 거래처명 (E)(T3-5)김태오</t>
         </is>
       </c>
-      <c r="N6" s="47" t="inlineStr">
+      <c r="M6" s="47" t="inlineStr">
         <is>
           <t>화면/02_거래처등록-창.png
 화면/03_거래처등록-채움.png
 화면/04_거래처상세.png</t>
         </is>
       </c>
-      <c r="O6" s="34" t="inlineStr"/>
+      <c r="N6" s="34" t="inlineStr"/>
+      <c r="O6" s="35" t="inlineStr"/>
       <c r="P6" s="35" t="inlineStr"/>
       <c r="Q6" s="35" t="inlineStr"/>
       <c r="R6" s="35" t="inlineStr"/>
-      <c r="S6" s="35" t="inlineStr"/>
-      <c r="T6" s="34" t="inlineStr"/>
+      <c r="S6" s="34" t="inlineStr"/>
     </row>
     <row r="7" ht="82" customHeight="1">
       <c r="A7" s="20" t="inlineStr">
@@ -1868,20 +1849,15 @@
           <t>환자ㆍ처방 › 처방자료 업로드</t>
         </is>
       </c>
-      <c r="G7" s="23" t="inlineStr">
-        <is>
-          <t>/prescriptions/upload</t>
-        </is>
-      </c>
-      <c r="H7" s="24" t="n">
+      <c r="G7" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="H7" s="23" t="inlineStr">
+        <is>
+          <t>서류 유형을 바꿔가며 파일을 업로드한다</t>
+        </is>
+      </c>
       <c r="I7" s="23" t="inlineStr">
-        <is>
-          <t>서류 유형을 바꿔가며 파일을 업로드한다</t>
-        </is>
-      </c>
-      <c r="J7" s="23" t="inlineStr">
         <is>
           <t>처방전: 김태오_처방전.jpg (1건)
 신분증: 김태오_신분증_TEST.jpg (1건)
@@ -1889,32 +1865,32 @@
 결과지: 김태오_결과지_01~08_TEST.jpg (8건)</t>
         </is>
       </c>
-      <c r="K7" s="23" t="inlineStr">
+      <c r="J7" s="23" t="inlineStr">
         <is>
           <t>서류 유형 콤보 → 파일 선택 (유형별 4회 반복)</t>
         </is>
       </c>
-      <c r="L7" s="25" t="inlineStr">
+      <c r="K7" s="25" t="inlineStr">
         <is>
           <t>파일마다 업로드 시점의 [서류 유형]이 부여된다. 유형은 개별 타일에서 변경 가능.</t>
         </is>
       </c>
-      <c r="M7" s="26" t="inlineStr">
+      <c r="L7" s="26" t="inlineStr">
         <is>
           <t>총 11건이 유형별로 배치된다 (처방전1·신분증1·등록신청서1·결과지8)</t>
         </is>
       </c>
-      <c r="N7" s="27" t="inlineStr">
+      <c r="M7" s="27" t="inlineStr">
         <is>
           <t>화면/06_처방자료업로드-11건.png</t>
         </is>
       </c>
-      <c r="O7" s="28" t="inlineStr"/>
+      <c r="N7" s="28" t="inlineStr"/>
+      <c r="O7" s="29" t="inlineStr"/>
       <c r="P7" s="29" t="inlineStr"/>
       <c r="Q7" s="29" t="inlineStr"/>
       <c r="R7" s="29" t="inlineStr"/>
-      <c r="S7" s="29" t="inlineStr"/>
-      <c r="T7" s="28" t="inlineStr"/>
+      <c r="S7" s="28" t="inlineStr"/>
     </row>
     <row r="8" ht="82" customHeight="1">
       <c r="A8" s="30" t="n"/>
@@ -1923,48 +1899,47 @@
       <c r="D8" s="30" t="n"/>
       <c r="E8" s="30" t="n"/>
       <c r="F8" s="30" t="n"/>
-      <c r="G8" s="30" t="n"/>
-      <c r="H8" s="31" t="n">
+      <c r="G8" s="31" t="n">
         <v>2</v>
       </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>담당자와 메모를 입력하고 등록한다</t>
+        </is>
+      </c>
       <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>담당자와 메모를 입력하고 등록한다</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>담당자: 원동희
 메모: 3차 5회 · 1번 김태오 · 일반 10/90 · 링크페이 · 기준 한 바퀴</t>
         </is>
       </c>
-      <c r="K8" s="6" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>［등록］</t>
         </is>
       </c>
-      <c r="L8" s="32" t="inlineStr">
+      <c r="K8" s="32" t="inlineStr">
         <is>
           <t>POST /prescriptions — ① 처방전 1장은 처방전 이미지로, 나머지는 첨부문서로 저장 ② 처방번호 RX-YYYYMMDD-NNN 자동 채번(삭제분 포함 채번하여 번호 재사용 방지) ③ 상태=검수 필요 ④ 새 탭으로 주문 등록 화면 오픈</t>
         </is>
       </c>
-      <c r="M8" s="48" t="inlineStr">
+      <c r="L8" s="48" t="inlineStr">
         <is>
           <t>① RX-20260907-005 채번
 ② 새 탭에서 주문 등록 화면이 열림</t>
         </is>
       </c>
-      <c r="N8" s="33" t="inlineStr">
+      <c r="M8" s="33" t="inlineStr">
         <is>
           <t>화면/07_주문등록-열림.png</t>
         </is>
       </c>
-      <c r="O8" s="34" t="inlineStr"/>
+      <c r="N8" s="34" t="inlineStr"/>
+      <c r="O8" s="35" t="inlineStr"/>
       <c r="P8" s="35" t="inlineStr"/>
       <c r="Q8" s="35" t="inlineStr"/>
       <c r="R8" s="35" t="inlineStr"/>
-      <c r="S8" s="35" t="inlineStr"/>
-      <c r="T8" s="34" t="inlineStr"/>
+      <c r="S8" s="34" t="inlineStr"/>
     </row>
     <row r="9" ht="82" customHeight="1">
       <c r="A9" s="36" t="inlineStr">
@@ -1997,20 +1972,15 @@
           <t>주문ㆍ재구매 › 주문 등록 › [상세 목록] › 상담ㆍ환자 정보</t>
         </is>
       </c>
-      <c r="G9" s="39" t="inlineStr">
-        <is>
-          <t>/prescriptions/RX-20260907-005</t>
-        </is>
-      </c>
-      <c r="H9" s="40" t="n">
+      <c r="G9" s="40" t="n">
         <v>1</v>
       </c>
+      <c r="H9" s="39" t="inlineStr">
+        <is>
+          <t>상세 목록 탭 › 상담ㆍ환자 정보에서 환자 항목을 입력한다</t>
+        </is>
+      </c>
       <c r="I9" s="39" t="inlineStr">
-        <is>
-          <t>상세 목록 탭 › 상담ㆍ환자 정보에서 환자 항목을 입력한다</t>
-        </is>
-      </c>
-      <c r="J9" s="39" t="inlineStr">
         <is>
           <t>주민등록번호: 850203-1000001
 전화번호1: 관리자 · 01057990084 (선택)
@@ -2018,32 +1988,32 @@
 송금자명: 김태오</t>
         </is>
       </c>
-      <c r="K9" s="39" t="inlineStr">
+      <c r="J9" s="39" t="inlineStr">
         <is>
           <t>［상세 목록］ 탭 → ［상담ㆍ환자 정보］</t>
         </is>
       </c>
-      <c r="L9" s="41" t="inlineStr">
+      <c r="K9" s="41" t="inlineStr">
         <is>
           <t>[웹 화면=테스트]이면 전화번호가 콤보박스로 전환된다. 결제 방식도 이 탭에 위치한다(처방전 없이도 구매 가능하므로).</t>
         </is>
       </c>
-      <c r="M9" s="42" t="inlineStr">
+      <c r="L9" s="42" t="inlineStr">
         <is>
           <t>입력값이 반영되고 전화번호가 콤보박스로 표시된다</t>
         </is>
       </c>
-      <c r="N9" s="43" t="inlineStr">
+      <c r="M9" s="43" t="inlineStr">
         <is>
           <t>화면/08_상세목록-상담환자정보.png</t>
         </is>
       </c>
-      <c r="O9" s="28" t="inlineStr"/>
+      <c r="N9" s="28" t="inlineStr"/>
+      <c r="O9" s="29" t="inlineStr"/>
       <c r="P9" s="29" t="inlineStr"/>
       <c r="Q9" s="29" t="inlineStr"/>
       <c r="R9" s="29" t="inlineStr"/>
-      <c r="S9" s="29" t="inlineStr"/>
-      <c r="T9" s="28" t="inlineStr"/>
+      <c r="S9" s="28" t="inlineStr"/>
     </row>
     <row r="10" ht="82" customHeight="1">
       <c r="A10" s="20" t="inlineStr">
@@ -2076,50 +2046,45 @@
           <t>상세 목록 › 병원ㆍ처방 정보 › [병원 조회] 팝업</t>
         </is>
       </c>
-      <c r="G10" s="23" t="inlineStr">
-        <is>
-          <t>/prescriptions/RX-20260907-005</t>
-        </is>
-      </c>
-      <c r="H10" s="24" t="n">
+      <c r="G10" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t>병원 조회 팝업에서 병원명으로 검색한다</t>
+        </is>
+      </c>
       <c r="I10" s="23" t="inlineStr">
         <is>
-          <t>병원 조회 팝업에서 병원명으로 검색한다</t>
+          <t>검색어: 서울가온</t>
         </is>
       </c>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t>검색어: 서울가온</t>
-        </is>
-      </c>
-      <c r="K10" s="23" t="inlineStr">
-        <is>
           <t>［병원 조회］</t>
         </is>
       </c>
-      <c r="L10" s="25" t="inlineStr">
+      <c r="K10" s="25" t="inlineStr">
         <is>
           <t>hospitalSearch() — 병원 마스터에서 이름/요양기관기호로 조회</t>
         </is>
       </c>
-      <c r="M10" s="49" t="inlineStr">
+      <c r="L10" s="49" t="inlineStr">
         <is>
           <t>★ 검색 결과 0건 — 5회 테스트 자료의 가상 병원 8곳은 마스터에 미등록 상태</t>
         </is>
       </c>
-      <c r="N10" s="27" t="inlineStr">
+      <c r="M10" s="27" t="inlineStr">
         <is>
           <t>화면/09_병원조회-팝업.png</t>
         </is>
       </c>
-      <c r="O10" s="28" t="inlineStr"/>
+      <c r="N10" s="28" t="inlineStr"/>
+      <c r="O10" s="29" t="inlineStr"/>
       <c r="P10" s="29" t="inlineStr"/>
       <c r="Q10" s="29" t="inlineStr"/>
       <c r="R10" s="29" t="inlineStr"/>
-      <c r="S10" s="29" t="inlineStr"/>
-      <c r="T10" s="28" t="inlineStr"/>
+      <c r="S10" s="28" t="inlineStr"/>
     </row>
     <row r="11" ht="82" customHeight="1">
       <c r="A11" s="30" t="n"/>
@@ -2128,46 +2093,45 @@
       <c r="D11" s="30" t="n"/>
       <c r="E11" s="30" t="n"/>
       <c r="F11" s="30" t="n"/>
-      <c r="G11" s="30" t="n"/>
-      <c r="H11" s="31" t="n">
+      <c r="G11" s="31" t="n">
         <v>2</v>
       </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>요양기관기호로 재검색한다</t>
+        </is>
+      </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>요양기관기호로 재검색한다</t>
+          <t>검색어: 1231013</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>검색어: 1231013</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
           <t>［검색］</t>
         </is>
       </c>
-      <c r="L11" s="32" t="inlineStr">
+      <c r="K11" s="32" t="inlineStr">
         <is>
           <t>동일 함수 — 기호 부분일치 조회</t>
         </is>
       </c>
-      <c r="M11" s="48" t="inlineStr">
+      <c r="L11" s="48" t="inlineStr">
         <is>
           <t>무관한 「연세재활의학과의원(12310131)」만 조회된다</t>
         </is>
       </c>
-      <c r="N11" s="33" t="inlineStr">
+      <c r="M11" s="33" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O11" s="34" t="inlineStr"/>
+      <c r="N11" s="34" t="inlineStr"/>
+      <c r="O11" s="35" t="inlineStr"/>
       <c r="P11" s="35" t="inlineStr"/>
       <c r="Q11" s="35" t="inlineStr"/>
       <c r="R11" s="35" t="inlineStr"/>
-      <c r="S11" s="35" t="inlineStr"/>
-      <c r="T11" s="34" t="inlineStr"/>
+      <c r="S11" s="34" t="inlineStr"/>
     </row>
     <row r="12" ht="82" customHeight="1">
       <c r="A12" s="36" t="inlineStr">
@@ -2200,50 +2164,45 @@
           <t>병원 조회 팝업 › [새 병원 등록]</t>
         </is>
       </c>
-      <c r="G12" s="39" t="inlineStr">
-        <is>
-          <t>/prescriptions/RX-20260907-005</t>
-        </is>
-      </c>
-      <c r="H12" s="40" t="n">
+      <c r="G12" s="40" t="n">
         <v>1</v>
       </c>
+      <c r="H12" s="39" t="inlineStr">
+        <is>
+          <t>신규 병원 등록 창을 연다</t>
+        </is>
+      </c>
       <c r="I12" s="39" t="inlineStr">
         <is>
-          <t>신규 병원 등록 창을 연다</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J12" s="39" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K12" s="39" t="inlineStr">
-        <is>
           <t>［새 병원 등록］</t>
         </is>
       </c>
-      <c r="L12" s="41" t="inlineStr">
+      <c r="K12" s="41" t="inlineStr">
         <is>
           <t>hospitalNewOpen() — 병원 신규 등록 입력 영역 노출</t>
         </is>
       </c>
-      <c r="M12" s="42" t="inlineStr">
+      <c r="L12" s="42" t="inlineStr">
         <is>
           <t>병원명·요양기관기호·진료과목·전화번호·주소 입력칸이 표시된다</t>
         </is>
       </c>
-      <c r="N12" s="43" t="inlineStr">
+      <c r="M12" s="43" t="inlineStr">
         <is>
           <t>화면/10_새병원등록-팝업.png</t>
         </is>
       </c>
-      <c r="O12" s="28" t="inlineStr"/>
+      <c r="N12" s="28" t="inlineStr"/>
+      <c r="O12" s="29" t="inlineStr"/>
       <c r="P12" s="29" t="inlineStr"/>
       <c r="Q12" s="29" t="inlineStr"/>
       <c r="R12" s="29" t="inlineStr"/>
-      <c r="S12" s="29" t="inlineStr"/>
-      <c r="T12" s="28" t="inlineStr"/>
+      <c r="S12" s="28" t="inlineStr"/>
     </row>
     <row r="13" ht="82" customHeight="1">
       <c r="A13" s="30" t="n"/>
@@ -2252,16 +2211,15 @@
       <c r="D13" s="30" t="n"/>
       <c r="E13" s="30" t="n"/>
       <c r="F13" s="30" t="n"/>
-      <c r="G13" s="30" t="n"/>
-      <c r="H13" s="44" t="n">
+      <c r="G13" s="44" t="n">
         <v>2</v>
       </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>처방전에서 읽은 값으로 병원을 등록한다</t>
+        </is>
+      </c>
       <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>처방전에서 읽은 값으로 병원을 등록한다</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="inlineStr">
         <is>
           <t>병원명: 서울가온대학교병원
 요양기관 기호: 12310130
@@ -2270,34 +2228,34 @@
 주소: 서울특별시 광진구 구의동 631-1</t>
         </is>
       </c>
-      <c r="K13" s="15" t="inlineStr">
+      <c r="J13" s="15" t="inlineStr">
         <is>
           <t>［등록하고 고르기］</t>
         </is>
       </c>
-      <c r="L13" s="45" t="inlineStr">
+      <c r="K13" s="45" t="inlineStr">
         <is>
           <t>POST /hospitals — ① 병원 마스터에 신규 등록 ② 등록 즉시 해당 병원을 선택하여 병원명·요양병원 코드를 자동 채움</t>
         </is>
       </c>
-      <c r="M13" s="46" t="inlineStr">
+      <c r="L13" s="46" t="inlineStr">
         <is>
           <t>① 토스트 「서울가온대학교병원 · 12310130」
 ② 병원명·요양병원 코드가 자동 입력됨</t>
         </is>
       </c>
-      <c r="N13" s="47" t="inlineStr">
+      <c r="M13" s="47" t="inlineStr">
         <is>
           <t>화면/11_새병원등록-채움.png
 화면/12_병원채워짐.png</t>
         </is>
       </c>
-      <c r="O13" s="34" t="inlineStr"/>
+      <c r="N13" s="34" t="inlineStr"/>
+      <c r="O13" s="35" t="inlineStr"/>
       <c r="P13" s="35" t="inlineStr"/>
       <c r="Q13" s="35" t="inlineStr"/>
       <c r="R13" s="35" t="inlineStr"/>
-      <c r="S13" s="35" t="inlineStr"/>
-      <c r="T13" s="34" t="inlineStr"/>
+      <c r="S13" s="34" t="inlineStr"/>
     </row>
     <row r="14" ht="82" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
@@ -2330,20 +2288,15 @@
           <t>상세 목록 › 병원ㆍ처방 정보</t>
         </is>
       </c>
-      <c r="G14" s="23" t="inlineStr">
-        <is>
-          <t>/prescriptions/RX-20260907-005</t>
-        </is>
-      </c>
-      <c r="H14" s="24" t="n">
+      <c r="G14" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="H14" s="23" t="inlineStr">
+        <is>
+          <t>처방전 기재값과 시험값을 모두 입력한다</t>
+        </is>
+      </c>
       <c r="I14" s="23" t="inlineStr">
-        <is>
-          <t>처방전 기재값과 시험값을 모두 입력한다</t>
-        </is>
-      </c>
-      <c r="J14" s="23" t="inlineStr">
         <is>
           <t>[처방전 판독값]
 상병코드: Q05.9 / 상병명: 이분척추·신경인성 방광
@@ -2362,33 +2315,33 @@
 주문 담당자: 원동희</t>
         </is>
       </c>
-      <c r="K14" s="23" t="inlineStr">
+      <c r="J14" s="23" t="inlineStr">
         <is>
           <t>［병원ㆍ처방 정보］ 탭</t>
         </is>
       </c>
-      <c r="L14" s="25" t="inlineStr">
+      <c r="K14" s="25" t="inlineStr">
         <is>
           <t>자격을 [일반]으로 선택하면 청구전략이 본인 10% / 공단 90%로 확정된다</t>
         </is>
       </c>
-      <c r="M14" s="26" t="inlineStr">
+      <c r="L14" s="26" t="inlineStr">
         <is>
           <t>① 처방전종료일이 발행일+90일 = 2026-12-06 으로 자동 계산
 ② 일일 도뇨 횟수 선택지가 1~10, 10 이상으로 표시 (단위 「회」 미표기)</t>
         </is>
       </c>
-      <c r="N14" s="27" t="inlineStr">
+      <c r="M14" s="27" t="inlineStr">
         <is>
           <t>화면/13_상세목록-병원처방정보.png</t>
         </is>
       </c>
-      <c r="O14" s="28" t="inlineStr"/>
+      <c r="N14" s="28" t="inlineStr"/>
+      <c r="O14" s="29" t="inlineStr"/>
       <c r="P14" s="29" t="inlineStr"/>
       <c r="Q14" s="29" t="inlineStr"/>
       <c r="R14" s="29" t="inlineStr"/>
-      <c r="S14" s="29" t="inlineStr"/>
-      <c r="T14" s="28" t="inlineStr"/>
+      <c r="S14" s="28" t="inlineStr"/>
     </row>
     <row r="15" ht="82" customHeight="1">
       <c r="A15" s="36" t="inlineStr">
@@ -2421,52 +2374,47 @@
           <t>병원ㆍ처방 정보 › 관할 청구처 [찾기] 팝업</t>
         </is>
       </c>
-      <c r="G15" s="39" t="inlineStr">
-        <is>
-          <t>/prescriptions/RX-20260907-005</t>
-        </is>
-      </c>
-      <c r="H15" s="40" t="n">
+      <c r="G15" s="40" t="n">
         <v>1</v>
       </c>
+      <c r="H15" s="39" t="inlineStr">
+        <is>
+          <t>관할 청구처를 조회한다</t>
+        </is>
+      </c>
       <c r="I15" s="39" t="inlineStr">
-        <is>
-          <t>관할 청구처를 조회한다</t>
-        </is>
-      </c>
-      <c r="J15" s="39" t="inlineStr">
         <is>
           <t>읍ㆍ면ㆍ동: 소공동
 시ㆍ군ㆍ구: 중구(자동)</t>
         </is>
       </c>
-      <c r="K15" s="39" t="inlineStr">
+      <c r="J15" s="39" t="inlineStr">
         <is>
           <t>［찾기］</t>
         </is>
       </c>
-      <c r="L15" s="41" t="inlineStr">
+      <c r="K15" s="41" t="inlineStr">
         <is>
           <t>boFindRun() — ① 자사 청구처 마스터 우선 조회 ② 미존재 시 외부(공단·카카오)에 조회하여 후보 제시. ※ 기존 등록건을 선택해야 마스터 중복이 발생하지 않는다</t>
         </is>
       </c>
-      <c r="M15" s="42" t="inlineStr">
+      <c r="L15" s="42" t="inlineStr">
         <is>
           <t>「공단 중구지사 · 보험급여부」 1건이 조회된다 (기존 등록건)</t>
         </is>
       </c>
-      <c r="N15" s="43" t="inlineStr">
+      <c r="M15" s="43" t="inlineStr">
         <is>
           <t>화면/14_청구처찾기-팝업.png
 화면/15_청구처찾기-후보.png</t>
         </is>
       </c>
-      <c r="O15" s="28" t="inlineStr"/>
+      <c r="N15" s="28" t="inlineStr"/>
+      <c r="O15" s="29" t="inlineStr"/>
       <c r="P15" s="29" t="inlineStr"/>
       <c r="Q15" s="29" t="inlineStr"/>
       <c r="R15" s="29" t="inlineStr"/>
-      <c r="S15" s="29" t="inlineStr"/>
-      <c r="T15" s="28" t="inlineStr"/>
+      <c r="S15" s="28" t="inlineStr"/>
     </row>
     <row r="16" ht="82" customHeight="1">
       <c r="A16" s="30" t="n"/>
@@ -2475,47 +2423,46 @@
       <c r="D16" s="30" t="n"/>
       <c r="E16" s="30" t="n"/>
       <c r="F16" s="30" t="n"/>
-      <c r="G16" s="30" t="n"/>
-      <c r="H16" s="44" t="n">
+      <c r="G16" s="44" t="n">
         <v>2</v>
       </c>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>조회된 청구처를 선택하고 저장한다</t>
+        </is>
+      </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
-          <t>조회된 청구처를 선택하고 저장한다</t>
+          <t>청구처: 공단 중구지사</t>
         </is>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
-          <t>청구처: 공단 중구지사</t>
-        </is>
-      </c>
-      <c r="K16" s="15" t="inlineStr">
-        <is>
           <t>후보 클릭 → ［저장］</t>
         </is>
       </c>
-      <c r="L16" s="45" t="inlineStr">
+      <c r="K16" s="45" t="inlineStr">
         <is>
           <t>PUT /prescriptions/{rx}/ocr — ① 처방 항목 저장 ② 환자 귀속 항목(Email·전화2·건보등록 등)은 거래처로 승계 ③ 처방전을 환자에 연결 ④ 설정에 따라 접수 안내 문자 및 위임동의 링크 발송</t>
         </is>
       </c>
-      <c r="M16" s="46" t="inlineStr">
+      <c r="L16" s="46" t="inlineStr">
         <is>
           <t>① 토스트 「저장되었습니다」
 ② 관할 청구처에 공단 중구지사가 표시됨</t>
         </is>
       </c>
-      <c r="N16" s="47" t="inlineStr">
+      <c r="M16" s="47" t="inlineStr">
         <is>
           <t>화면/16_상세목록-저장.png</t>
         </is>
       </c>
-      <c r="O16" s="34" t="inlineStr"/>
+      <c r="N16" s="34" t="inlineStr"/>
+      <c r="O16" s="35" t="inlineStr"/>
       <c r="P16" s="35" t="inlineStr"/>
       <c r="Q16" s="35" t="inlineStr"/>
       <c r="R16" s="35" t="inlineStr"/>
-      <c r="S16" s="35" t="inlineStr"/>
-      <c r="T16" s="34" t="inlineStr"/>
+      <c r="S16" s="34" t="inlineStr"/>
     </row>
     <row r="17" ht="82" customHeight="1">
       <c r="A17" s="20" t="inlineStr">
@@ -2548,51 +2495,46 @@
           <t>주문 등록 › 상세 목록 상단</t>
         </is>
       </c>
-      <c r="G17" s="23" t="inlineStr">
-        <is>
-          <t>/prescriptions/RX-20260907-005</t>
-        </is>
-      </c>
-      <c r="H17" s="24" t="n">
+      <c r="G17" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="H17" s="23" t="inlineStr">
+        <is>
+          <t>검수를 요청한다</t>
+        </is>
+      </c>
       <c r="I17" s="23" t="inlineStr">
         <is>
-          <t>검수를 요청한다</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" s="23" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K17" s="23" t="inlineStr">
-        <is>
           <t>［검수 요청하기］ → 확인</t>
         </is>
       </c>
-      <c r="L17" s="25" t="inlineStr">
+      <c r="K17" s="25" t="inlineStr">
         <is>
           <t>POST /prescriptions/{rx}/request-review — ① 상태를 [검수 요청]으로 변경 ② 활동 이력 기록 ③ 검수 승인 권한 보유자 전원에게 알림 + 채팅 발송(「승인 요청」 방). 단, 요청자 본인은 수신 대상에서 제외</t>
         </is>
       </c>
-      <c r="M17" s="26" t="inlineStr">
+      <c r="L17" s="26" t="inlineStr">
         <is>
           <t>① 상태 = 검수 요청
 ② 승인 권한자 9명에게 알림 발송 (전체 10명 − 요청자 1명)</t>
         </is>
       </c>
-      <c r="N17" s="27" t="inlineStr">
+      <c r="M17" s="27" t="inlineStr">
         <is>
           <t>화면/17_검수요청.png</t>
         </is>
       </c>
-      <c r="O17" s="28" t="inlineStr"/>
+      <c r="N17" s="28" t="inlineStr"/>
+      <c r="O17" s="29" t="inlineStr"/>
       <c r="P17" s="29" t="inlineStr"/>
       <c r="Q17" s="29" t="inlineStr"/>
       <c r="R17" s="29" t="inlineStr"/>
-      <c r="S17" s="29" t="inlineStr"/>
-      <c r="T17" s="28" t="inlineStr"/>
+      <c r="S17" s="28" t="inlineStr"/>
     </row>
     <row r="18" ht="82" customHeight="1">
       <c r="A18" s="36" t="inlineStr">
@@ -2625,52 +2567,47 @@
           <t>주문 등록 › 상세 목록 상단</t>
         </is>
       </c>
-      <c r="G18" s="39" t="inlineStr">
-        <is>
-          <t>/prescriptions/RX-20260907-005</t>
-        </is>
-      </c>
-      <c r="H18" s="40" t="n">
+      <c r="G18" s="40" t="n">
         <v>1</v>
       </c>
+      <c r="H18" s="39" t="inlineStr">
+        <is>
+          <t>검수 승인 팝업에서 메모를 입력하고 승인한다</t>
+        </is>
+      </c>
       <c r="I18" s="39" t="inlineStr">
         <is>
-          <t>검수 승인 팝업에서 메모를 입력하고 승인한다</t>
+          <t>검수 메모: 3차 5회 · 1번 김태오 · 서류 11건 확인 · 일반 10/90</t>
         </is>
       </c>
       <c r="J18" s="39" t="inlineStr">
         <is>
-          <t>검수 메모: 3차 5회 · 1번 김태오 · 서류 11건 확인 · 일반 10/90</t>
-        </is>
-      </c>
-      <c r="K18" s="39" t="inlineStr">
-        <is>
           <t>［검수 승인하기］ → 팝업 ［검수 승인하기］</t>
         </is>
       </c>
-      <c r="L18" s="41" t="inlineStr">
+      <c r="K18" s="41" t="inlineStr">
         <is>
           <t>POST /prescriptions/{rx}/approve — ① 상태를 [검수 완료]로 변경, 검수자·검수일시 기록 ② 요청 담당자에게 승인 결과 회신 알림 ③ 이미 승인된 건은 재승인 차단(검수자·일시 덮어쓰기 방지)</t>
         </is>
       </c>
-      <c r="M18" s="42" t="inlineStr">
+      <c r="L18" s="42" t="inlineStr">
         <is>
           <t>① 상태 = 검수 완료, 검수자 = 관리자
 ② 담당자(원동희)에게 「검수가 승인되었습니다」 회신</t>
         </is>
       </c>
-      <c r="N18" s="43" t="inlineStr">
+      <c r="M18" s="43" t="inlineStr">
         <is>
           <t>화면/18_검수승인-팝업.png
 화면/19_검수완료.png</t>
         </is>
       </c>
-      <c r="O18" s="28" t="inlineStr"/>
+      <c r="N18" s="28" t="inlineStr"/>
+      <c r="O18" s="29" t="inlineStr"/>
       <c r="P18" s="29" t="inlineStr"/>
       <c r="Q18" s="29" t="inlineStr"/>
       <c r="R18" s="29" t="inlineStr"/>
-      <c r="S18" s="29" t="inlineStr"/>
-      <c r="T18" s="28" t="inlineStr"/>
+      <c r="S18" s="28" t="inlineStr"/>
     </row>
     <row r="19" ht="82" customHeight="1">
       <c r="A19" s="20" t="inlineStr">
@@ -2703,53 +2640,48 @@
           <t>주문 등록 › 상단 [위임동의] 팝오버</t>
         </is>
       </c>
-      <c r="G19" s="23" t="inlineStr">
-        <is>
-          <t>/prescriptions/RX-20260907-005</t>
-        </is>
-      </c>
-      <c r="H19" s="24" t="n">
+      <c r="G19" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="H19" s="23" t="inlineStr">
+        <is>
+          <t>위임동의 발송 창에서 수신번호를 확인하고 발송한다</t>
+        </is>
+      </c>
       <c r="I19" s="23" t="inlineStr">
         <is>
-          <t>위임동의 발송 창에서 수신번호를 확인하고 발송한다</t>
+          <t>수신 번호: 010-5799-0084 (거래처 전화번호1 자동 표시)</t>
         </is>
       </c>
       <c r="J19" s="23" t="inlineStr">
         <is>
-          <t>수신 번호: 010-5799-0084 (거래처 전화번호1 자동 표시)</t>
-        </is>
-      </c>
-      <c r="K19" s="23" t="inlineStr">
-        <is>
           <t>［위임동의］ → ［발송］</t>
         </is>
       </c>
-      <c r="L19" s="25" t="inlineStr">
+      <c r="K19" s="25" t="inlineStr">
         <is>
           <t>POST /prescriptions/{rx}/consent-sms — ① 30분 유효 1회용 토큰으로 동의 레코드 선생성 ② 서명 링크를 SMS 발송 ③ 마스킹 주민번호로 미성년 여부 판정(원문 미조회) ④ 미성년이면 거래처 보호자 정보를 동의 레코드에 선반영 ⑤ 발송 실패 시 생성한 동의 레코드를 삭제</t>
         </is>
       </c>
-      <c r="M19" s="26" t="inlineStr">
+      <c r="L19" s="26" t="inlineStr">
         <is>
           <t>① 발송 완료 · 팝빌 접수번호 채번
 ② [우리에게만] 설정에 의해 01057990084로 우회 발송
 ③ 성년이므로 is_minor = 0</t>
         </is>
       </c>
-      <c r="N19" s="27" t="inlineStr">
+      <c r="M19" s="27" t="inlineStr">
         <is>
           <t>화면/20_위임동의-발송창.png
 화면/21_위임동의-발송결과.png</t>
         </is>
       </c>
-      <c r="O19" s="28" t="inlineStr"/>
+      <c r="N19" s="28" t="inlineStr"/>
+      <c r="O19" s="29" t="inlineStr"/>
       <c r="P19" s="29" t="inlineStr"/>
       <c r="Q19" s="29" t="inlineStr"/>
       <c r="R19" s="29" t="inlineStr"/>
-      <c r="S19" s="29" t="inlineStr"/>
-      <c r="T19" s="28" t="inlineStr"/>
+      <c r="S19" s="28" t="inlineStr"/>
     </row>
     <row r="20" ht="82" customHeight="1">
       <c r="A20" s="36" t="inlineStr">
@@ -2782,51 +2714,46 @@
           <t>위임동의 서명 페이지 (비로그인 공개 화면)</t>
         </is>
       </c>
-      <c r="G20" s="39" t="inlineStr">
-        <is>
-          <t>/consent/{토큰}</t>
-        </is>
-      </c>
-      <c r="H20" s="40" t="n">
+      <c r="G20" s="40" t="n">
         <v>1</v>
       </c>
+      <c r="H20" s="39" t="inlineStr">
+        <is>
+          <t>서명 페이지를 열고 화면 구성을 확인한다</t>
+        </is>
+      </c>
       <c r="I20" s="39" t="inlineStr">
         <is>
-          <t>서명 페이지를 열고 화면 구성을 확인한다</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" s="39" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K20" s="39" t="inlineStr">
-        <is>
           <t>SMS 링크 클릭</t>
         </is>
       </c>
-      <c r="L20" s="41" t="inlineStr">
+      <c r="K20" s="41" t="inlineStr">
         <is>
           <t>토큰으로 동의 레코드를 조회하여 서명 화면을 구성한다. 미성년이면 보호자 입력·서명 영역이 추가로 노출된다.</t>
         </is>
       </c>
-      <c r="M20" s="42" t="inlineStr">
+      <c r="L20" s="42" t="inlineStr">
         <is>
           <t>① 본인 이름 확인·위임 내용·서명란 1개 표시
 ② 성년이므로 보호자 영역 미노출</t>
         </is>
       </c>
-      <c r="N20" s="43" t="inlineStr">
+      <c r="M20" s="43" t="inlineStr">
         <is>
           <t>화면/22_서명화면.png</t>
         </is>
       </c>
-      <c r="O20" s="28" t="inlineStr"/>
+      <c r="N20" s="28" t="inlineStr"/>
+      <c r="O20" s="29" t="inlineStr"/>
       <c r="P20" s="29" t="inlineStr"/>
       <c r="Q20" s="29" t="inlineStr"/>
       <c r="R20" s="29" t="inlineStr"/>
-      <c r="S20" s="29" t="inlineStr"/>
-      <c r="T20" s="28" t="inlineStr"/>
+      <c r="S20" s="28" t="inlineStr"/>
     </row>
     <row r="21" ht="82" customHeight="1">
       <c r="A21" s="50" t="n"/>
@@ -2835,47 +2762,46 @@
       <c r="D21" s="50" t="n"/>
       <c r="E21" s="50" t="n"/>
       <c r="F21" s="50" t="n"/>
-      <c r="G21" s="50" t="n"/>
-      <c r="H21" s="44" t="n">
+      <c r="G21" s="44" t="n">
         <v>2</v>
       </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>개인정보 수집·이용 동의를 선택한다</t>
+        </is>
+      </c>
       <c r="I21" s="15" t="inlineStr">
-        <is>
-          <t>개인정보 수집·이용 동의를 선택한다</t>
-        </is>
-      </c>
-      <c r="J21" s="15" t="inlineStr">
         <is>
           <t>신청 유형: 일반
 동의 항목: 일반·제3자·마케팅 모두 「동의함」</t>
         </is>
       </c>
-      <c r="K21" s="15" t="inlineStr">
+      <c r="J21" s="15" t="inlineStr">
         <is>
           <t>동의 항목 라디오 선택</t>
         </is>
       </c>
-      <c r="L21" s="45" t="inlineStr">
+      <c r="K21" s="45" t="inlineStr">
         <is>
           <t>privacyReady() — 신청 유형과 필수 동의 항목이 모두 충족되어야 서명 버튼이 활성화된다</t>
         </is>
       </c>
-      <c r="M21" s="46" t="inlineStr">
+      <c r="L21" s="46" t="inlineStr">
         <is>
           <t>필수 항목이 모두 선택된다</t>
         </is>
       </c>
-      <c r="N21" s="47" t="inlineStr">
+      <c r="M21" s="47" t="inlineStr">
         <is>
           <t>화면/23_개인정보동의.png</t>
         </is>
       </c>
-      <c r="O21" s="34" t="inlineStr"/>
+      <c r="N21" s="34" t="inlineStr"/>
+      <c r="O21" s="35" t="inlineStr"/>
       <c r="P21" s="35" t="inlineStr"/>
       <c r="Q21" s="35" t="inlineStr"/>
       <c r="R21" s="35" t="inlineStr"/>
-      <c r="S21" s="35" t="inlineStr"/>
-      <c r="T21" s="34" t="inlineStr"/>
+      <c r="S21" s="34" t="inlineStr"/>
     </row>
     <row r="22" ht="82" customHeight="1">
       <c r="A22" s="50" t="n"/>
@@ -2884,46 +2810,45 @@
       <c r="D22" s="50" t="n"/>
       <c r="E22" s="50" t="n"/>
       <c r="F22" s="50" t="n"/>
-      <c r="G22" s="50" t="n"/>
-      <c r="H22" s="44" t="n">
+      <c r="G22" s="44" t="n">
         <v>3</v>
       </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>휴대폰 본인확인을 수행한다</t>
+        </is>
+      </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
-          <t>휴대폰 본인확인을 수행한다</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J22" s="15" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K22" s="15" t="inlineStr">
-        <is>
           <t>［본인확인］</t>
         </is>
       </c>
-      <c r="L22" s="45" t="inlineStr">
+      <c r="K22" s="45" t="inlineStr">
         <is>
           <t>startNice() — NICE 본인확인. [본인확인 시늉=켬]이면 실제 호출 없이 통과 처리</t>
         </is>
       </c>
-      <c r="M22" s="46" t="inlineStr">
+      <c r="L22" s="46" t="inlineStr">
         <is>
           <t>「확인됨 (테스트)」로 표시된다</t>
         </is>
       </c>
-      <c r="N22" s="47" t="inlineStr">
+      <c r="M22" s="47" t="inlineStr">
         <is>
           <t>화면/24_본인확인.png</t>
         </is>
       </c>
-      <c r="O22" s="34" t="inlineStr"/>
+      <c r="N22" s="34" t="inlineStr"/>
+      <c r="O22" s="35" t="inlineStr"/>
       <c r="P22" s="35" t="inlineStr"/>
       <c r="Q22" s="35" t="inlineStr"/>
       <c r="R22" s="35" t="inlineStr"/>
-      <c r="S22" s="35" t="inlineStr"/>
-      <c r="T22" s="34" t="inlineStr"/>
+      <c r="S22" s="34" t="inlineStr"/>
     </row>
     <row r="23" ht="82" customHeight="1">
       <c r="A23" s="30" t="n"/>
@@ -2932,49 +2857,48 @@
       <c r="D23" s="30" t="n"/>
       <c r="E23" s="30" t="n"/>
       <c r="F23" s="30" t="n"/>
-      <c r="G23" s="30" t="n"/>
-      <c r="H23" s="44" t="n">
+      <c r="G23" s="44" t="n">
         <v>4</v>
       </c>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>서명 후 동의를 제출한다</t>
+        </is>
+      </c>
       <c r="I23" s="15" t="inlineStr">
         <is>
-          <t>서명 후 동의를 제출한다</t>
+          <t>서명란에 서명 입력</t>
         </is>
       </c>
       <c r="J23" s="15" t="inlineStr">
         <is>
-          <t>서명란에 서명 입력</t>
-        </is>
-      </c>
-      <c r="K23" s="15" t="inlineStr">
-        <is>
           <t>［동의 서명］</t>
         </is>
       </c>
-      <c r="L23" s="45" t="inlineStr">
+      <c r="K23" s="45" t="inlineStr">
         <is>
           <t>POST /consent/{토큰} — ① 서명 이미지·동의 항목 저장 ② 위임동의서 PDF 및 요양비위임장(원본 서식 오버레이) 생성하여 첨부문서 등록 ③ 주문 관리에 주문 레코드 생성 ④ 설정 시 공단 등록 서류 팩스 자동 발송</t>
         </is>
       </c>
-      <c r="M23" s="46" t="inlineStr">
+      <c r="L23" s="46" t="inlineStr">
         <is>
           <t>① 「동의가 완료되었습니다」 표시
 ② 주문 EUD202609071734141 생성
 ③ 위임동의서·요양비위임장 첨부문서 등록</t>
         </is>
       </c>
-      <c r="N23" s="47" t="inlineStr">
+      <c r="M23" s="47" t="inlineStr">
         <is>
           <t>화면/22b_서명함.png
 화면/25_동의완료.png</t>
         </is>
       </c>
-      <c r="O23" s="34" t="inlineStr"/>
+      <c r="N23" s="34" t="inlineStr"/>
+      <c r="O23" s="35" t="inlineStr"/>
       <c r="P23" s="35" t="inlineStr"/>
       <c r="Q23" s="35" t="inlineStr"/>
       <c r="R23" s="35" t="inlineStr"/>
-      <c r="S23" s="35" t="inlineStr"/>
-      <c r="T23" s="34" t="inlineStr"/>
+      <c r="S23" s="34" t="inlineStr"/>
     </row>
     <row r="24" ht="82" customHeight="1">
       <c r="A24" s="20" t="inlineStr">
@@ -3007,54 +2931,49 @@
           <t>주문 등록 › [주문 제품] 탭</t>
         </is>
       </c>
-      <c r="G24" s="23" t="inlineStr">
-        <is>
-          <t>/prescriptions/RX-20260907-005</t>
-        </is>
-      </c>
-      <c r="H24" s="24" t="n">
+      <c r="G24" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>제품 조회 팝업에서 처방 규격에 맞는 제품을 선택한다</t>
+        </is>
+      </c>
       <c r="I24" s="23" t="inlineStr">
-        <is>
-          <t>제품 조회 팝업에서 처방 규격에 맞는 제품을 선택한다</t>
-        </is>
-      </c>
-      <c r="J24" s="23" t="inlineStr">
         <is>
           <t>검색어: CH14 Male
 선택: EasiCath Nalaton CH14 Male 40cm - Green</t>
         </is>
       </c>
-      <c r="K24" s="23" t="inlineStr">
+      <c r="J24" s="23" t="inlineStr">
         <is>
           <t>［주문 제품］ 탭 → 제품명 칸 ⌕ → 제품 선택</t>
         </is>
       </c>
-      <c r="L24" s="25" t="inlineStr">
+      <c r="K24" s="25" t="inlineStr">
         <is>
           <t>제품 선택 시 제품코드·소비자가가 자동 입력되고, 처방전 총계가 주문 수량으로 자동 반영된다</t>
         </is>
       </c>
-      <c r="M24" s="26" t="inlineStr">
+      <c r="L24" s="26" t="inlineStr">
         <is>
           <t>① 제품코드 5354 / 수량 540 / 소비자가 1,500
 ② 총 금액 810,000 · 기관 부담금 729,000(90%) · 본인 부담금 81,000(10%)</t>
         </is>
       </c>
-      <c r="N24" s="27" t="inlineStr">
+      <c r="M24" s="27" t="inlineStr">
         <is>
           <t>화면/26_주문제품-빈줄.png
 화면/27_제품조회-팝업.png
 화면/28_주문제품-채움.png</t>
         </is>
       </c>
-      <c r="O24" s="28" t="inlineStr"/>
+      <c r="N24" s="28" t="inlineStr"/>
+      <c r="O24" s="29" t="inlineStr"/>
       <c r="P24" s="29" t="inlineStr"/>
       <c r="Q24" s="29" t="inlineStr"/>
       <c r="R24" s="29" t="inlineStr"/>
-      <c r="S24" s="29" t="inlineStr"/>
-      <c r="T24" s="28" t="inlineStr"/>
+      <c r="S24" s="28" t="inlineStr"/>
     </row>
     <row r="25" ht="82" customHeight="1">
       <c r="A25" s="30" t="n"/>
@@ -3063,46 +2982,45 @@
       <c r="D25" s="30" t="n"/>
       <c r="E25" s="30" t="n"/>
       <c r="F25" s="30" t="n"/>
-      <c r="G25" s="30" t="n"/>
-      <c r="H25" s="31" t="n">
+      <c r="G25" s="31" t="n">
         <v>2</v>
       </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>주문 제품을 저장한다</t>
+        </is>
+      </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>주문 제품을 저장한다</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K25" s="6" t="inlineStr">
-        <is>
           <t>［저장］</t>
         </is>
       </c>
-      <c r="L25" s="32" t="inlineStr">
+      <c r="K25" s="32" t="inlineStr">
         <is>
           <t>주문 품목 저장 및 청구전략별 금액 배분. 검수 승인과 동의가 모두 완료되어야 저장 가능하며 미완료 시 차단된다.</t>
         </is>
       </c>
-      <c r="M25" s="48" t="inlineStr">
+      <c r="L25" s="48" t="inlineStr">
         <is>
           <t>토스트 「저장되었습니다」</t>
         </is>
       </c>
-      <c r="N25" s="33" t="inlineStr">
+      <c r="M25" s="33" t="inlineStr">
         <is>
           <t>화면/29_주문제품-저장.png</t>
         </is>
       </c>
-      <c r="O25" s="34" t="inlineStr"/>
+      <c r="N25" s="34" t="inlineStr"/>
+      <c r="O25" s="35" t="inlineStr"/>
       <c r="P25" s="35" t="inlineStr"/>
       <c r="Q25" s="35" t="inlineStr"/>
       <c r="R25" s="35" t="inlineStr"/>
-      <c r="S25" s="35" t="inlineStr"/>
-      <c r="T25" s="34" t="inlineStr"/>
+      <c r="S25" s="34" t="inlineStr"/>
     </row>
     <row r="26" ht="82" customHeight="1">
       <c r="A26" s="36" t="inlineStr">
@@ -3135,53 +3053,48 @@
           <t>주문 등록 › [주문 제품] 탭 하단</t>
         </is>
       </c>
-      <c r="G26" s="39" t="inlineStr">
-        <is>
-          <t>/prescriptions/RX-20260907-005</t>
-        </is>
-      </c>
-      <c r="H26" s="40" t="n">
+      <c r="G26" s="40" t="n">
         <v>1</v>
       </c>
+      <c r="H26" s="39" t="inlineStr">
+        <is>
+          <t>배송 정보를 확인하고 주문을 생성·연계한다</t>
+        </is>
+      </c>
       <c r="I26" s="39" t="inlineStr">
-        <is>
-          <t>배송 정보를 확인하고 주문을 생성·연계한다</t>
-        </is>
-      </c>
-      <c r="J26" s="39" t="inlineStr">
         <is>
           <t>받는 사람: (E)(T3-5)김태오
 주소: 04524 서울특별시 중구 세종대로 110 / 테스트용 주소(3차 5회 김태오)</t>
         </is>
       </c>
-      <c r="K26" s="39" t="inlineStr">
+      <c r="J26" s="39" t="inlineStr">
         <is>
           <t>［주문 생성 및 연계］</t>
         </is>
       </c>
-      <c r="L26" s="41" t="inlineStr">
+      <c r="K26" s="41" t="inlineStr">
         <is>
           <t>POST /prescriptions/{rx}/withworks-order — ① 자사 주문(EUD…) 금액·품목 확정 ② 위드웍스 so_store 호출하여 판매주문(S…) 채번 및 저장 ③ 접수 안내·결제 안내 SMS 2건 발송 ④ 연계 내용을 확인 이메일로 발송 ⑤ 위드웍스가 so.created 웹훅을 회신하여 창고·판매현황 정보가 즉시 반영</t>
         </is>
       </c>
-      <c r="M26" s="42" t="inlineStr">
+      <c r="L26" s="42" t="inlineStr">
         <is>
           <t>① 창고 판매주문 S2609070004 채번
 ② 출고창고 「3PL Main 판매창고」 즉시 표시
 ③ 판매현황 항목 16건이 즉시 채워짐</t>
         </is>
       </c>
-      <c r="N26" s="43" t="inlineStr">
+      <c r="M26" s="43" t="inlineStr">
         <is>
           <t>화면/30_주문생성및연계.png</t>
         </is>
       </c>
-      <c r="O26" s="28" t="inlineStr"/>
+      <c r="N26" s="28" t="inlineStr"/>
+      <c r="O26" s="29" t="inlineStr"/>
       <c r="P26" s="29" t="inlineStr"/>
       <c r="Q26" s="29" t="inlineStr"/>
       <c r="R26" s="29" t="inlineStr"/>
-      <c r="S26" s="29" t="inlineStr"/>
-      <c r="T26" s="28" t="inlineStr"/>
+      <c r="S26" s="28" t="inlineStr"/>
     </row>
     <row r="27" ht="82" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
@@ -3214,35 +3127,30 @@
           <t>[위드웍스] 주문 관리 › 판매 주문</t>
         </is>
       </c>
-      <c r="G27" s="23" t="inlineStr">
-        <is>
-          <t>https://www.demoworks.co.kr/salesorder</t>
-        </is>
-      </c>
-      <c r="H27" s="24" t="n">
+      <c r="G27" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="H27" s="23" t="inlineStr">
+        <is>
+          <t>위드웍스에서 판매번호로 조회한다</t>
+        </is>
+      </c>
       <c r="I27" s="23" t="inlineStr">
         <is>
-          <t>위드웍스에서 판매번호로 조회한다</t>
+          <t>판매번호: S2609070004</t>
         </is>
       </c>
       <c r="J27" s="23" t="inlineStr">
         <is>
-          <t>판매번호: S2609070004</t>
-        </is>
-      </c>
-      <c r="K27" s="23" t="inlineStr">
-        <is>
           <t>［검색］</t>
         </is>
       </c>
-      <c r="L27" s="25" t="inlineStr">
+      <c r="K27" s="25" t="inlineStr">
         <is>
           <t>위드웍스 판매주문 조회. CE Admin 주문번호는 etc SoNo 항목으로 연계된다.</t>
         </is>
       </c>
-      <c r="M27" s="26" t="inlineStr">
+      <c r="L27" s="26" t="inlineStr">
         <is>
           <t>① etc SoNo = EUD202609071734141 (CE 주문번호 일치)
 ② 구매 거래처명 = (E)(T3-5)김태오
@@ -3251,18 +3159,18 @@
 ⑤ 비고 = 업로드 시 입력한 메모 그대로</t>
         </is>
       </c>
-      <c r="N27" s="27" t="inlineStr">
+      <c r="M27" s="27" t="inlineStr">
         <is>
           <t>화면/31_ww_판매주문-화면.png
 화면/32_ww_판매주문-조회결과.png</t>
         </is>
       </c>
-      <c r="O27" s="28" t="inlineStr"/>
+      <c r="N27" s="28" t="inlineStr"/>
+      <c r="O27" s="29" t="inlineStr"/>
       <c r="P27" s="29" t="inlineStr"/>
       <c r="Q27" s="29" t="inlineStr"/>
       <c r="R27" s="29" t="inlineStr"/>
-      <c r="S27" s="29" t="inlineStr"/>
-      <c r="T27" s="28" t="inlineStr"/>
+      <c r="S27" s="28" t="inlineStr"/>
     </row>
     <row r="28" ht="82" customHeight="1">
       <c r="A28" s="36" t="inlineStr">
@@ -3295,35 +3203,30 @@
           <t>청구ㆍ회계 › 정산/회계</t>
         </is>
       </c>
-      <c r="G28" s="39" t="inlineStr">
-        <is>
-          <t>/settlement</t>
-        </is>
-      </c>
-      <c r="H28" s="40" t="n">
+      <c r="G28" s="40" t="n">
         <v>1</v>
       </c>
+      <c r="H28" s="39" t="inlineStr">
+        <is>
+          <t>해당 주문의 결제수단을 선택하여 입금을 확인한다</t>
+        </is>
+      </c>
       <c r="I28" s="39" t="inlineStr">
         <is>
-          <t>해당 주문의 결제수단을 선택하여 입금을 확인한다</t>
+          <t>결제수단: 링크페이</t>
         </is>
       </c>
       <c r="J28" s="39" t="inlineStr">
         <is>
-          <t>결제수단: 링크페이</t>
-        </is>
-      </c>
-      <c r="K28" s="39" t="inlineStr">
-        <is>
           <t>결제수단 칸 → 링크페이 선택</t>
         </is>
       </c>
-      <c r="L28" s="41" t="inlineStr">
+      <c r="K28" s="41" t="inlineStr">
         <is>
           <t>POST /settlement/orders/{order}/pay-method — 결제수단 선택 시점이 곧 입금 확인이다. ① 입금 확인 처리 ② 세금계산서 발행 ③ 거래명세서 생성 ④ 위드웍스 판매주문 확정 ⑤ 청구전략상 대상이 아닌 증빙은 자동 제외</t>
         </is>
       </c>
-      <c r="M28" s="42" t="inlineStr">
+      <c r="L28" s="42" t="inlineStr">
         <is>
           <t>① 링크페이 · 81,000원 입금 확인
 ② 세금계산서 TI20260907000243 발행
@@ -3332,18 +3235,18 @@
 ⑤ 현금영수증은 「청구전략에 없음」으로 제외</t>
         </is>
       </c>
-      <c r="N28" s="43" t="inlineStr">
+      <c r="M28" s="43" t="inlineStr">
         <is>
           <t>화면/33_정산회계-목록.png
 화면/34_입금확인-뒤.png</t>
         </is>
       </c>
-      <c r="O28" s="28" t="inlineStr"/>
+      <c r="N28" s="28" t="inlineStr"/>
+      <c r="O28" s="29" t="inlineStr"/>
       <c r="P28" s="29" t="inlineStr"/>
       <c r="Q28" s="29" t="inlineStr"/>
       <c r="R28" s="29" t="inlineStr"/>
-      <c r="S28" s="29" t="inlineStr"/>
-      <c r="T28" s="28" t="inlineStr"/>
+      <c r="S28" s="28" t="inlineStr"/>
     </row>
     <row r="29" ht="82" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
@@ -3376,52 +3279,47 @@
           <t>주문 등록 › 상단 [팩스 발송] 팝오버</t>
         </is>
       </c>
-      <c r="G29" s="23" t="inlineStr">
-        <is>
-          <t>/prescriptions/RX-20260907-005</t>
-        </is>
-      </c>
-      <c r="H29" s="24" t="n">
+      <c r="G29" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="H29" s="23" t="inlineStr">
+        <is>
+          <t>수신처와 전송 서류를 확인한다</t>
+        </is>
+      </c>
       <c r="I29" s="23" t="inlineStr">
         <is>
-          <t>수신처와 전송 서류를 확인한다</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J29" s="23" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K29" s="23" t="inlineStr">
-        <is>
           <t>［팩스 발송］</t>
         </is>
       </c>
-      <c r="L29" s="25" t="inlineStr">
+      <c r="K29" s="25" t="inlineStr">
         <is>
           <t>자격이 [일반]이므로 수신처가 건강보험공단으로 구성되고, 관할 청구처의 팩스번호가 자동 표시된다</t>
         </is>
       </c>
-      <c r="M29" s="26" t="inlineStr">
+      <c r="L29" s="26" t="inlineStr">
         <is>
           <t>① 수신처 = 국민건강보험공단 · 공단 중구지사 · 보험급여부
 ② 수신 팩스번호 = 02-0000-0000
 ③ 신청 파일 11건 전체 선택 상태</t>
         </is>
       </c>
-      <c r="N29" s="27" t="inlineStr">
+      <c r="M29" s="27" t="inlineStr">
         <is>
           <t>화면/35_팩스발송-창.png</t>
         </is>
       </c>
-      <c r="O29" s="28" t="inlineStr"/>
+      <c r="N29" s="28" t="inlineStr"/>
+      <c r="O29" s="29" t="inlineStr"/>
       <c r="P29" s="29" t="inlineStr"/>
       <c r="Q29" s="29" t="inlineStr"/>
       <c r="R29" s="29" t="inlineStr"/>
-      <c r="S29" s="29" t="inlineStr"/>
-      <c r="T29" s="28" t="inlineStr"/>
+      <c r="S29" s="28" t="inlineStr"/>
     </row>
     <row r="30" ht="82" customHeight="1">
       <c r="A30" s="30" t="n"/>
@@ -3430,48 +3328,47 @@
       <c r="D30" s="30" t="n"/>
       <c r="E30" s="30" t="n"/>
       <c r="F30" s="30" t="n"/>
-      <c r="G30" s="30" t="n"/>
-      <c r="H30" s="31" t="n">
+      <c r="G30" s="31" t="n">
         <v>2</v>
       </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>팩스를 전송한다</t>
+        </is>
+      </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>팩스를 전송한다</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K30" s="6" t="inlineStr">
-        <is>
           <t>［팩스 전송］</t>
         </is>
       </c>
-      <c r="L30" s="32" t="inlineStr">
+      <c r="K30" s="32" t="inlineStr">
         <is>
           <t>POST /prescriptions/{rx}/fax — ① 선택 서류를 표지 포함 단일 PDF로 병합 ② 팝빌로 전송 ③ 접수번호를 발송 이력에 기록. [우리에게만]이면 수신번호만 테스트 팩스로 치환하고 수신처명은 유지한다.</t>
         </is>
       </c>
-      <c r="M30" s="48" t="inlineStr">
+      <c r="L30" s="48" t="inlineStr">
         <is>
           <t>① 팩스통합본 PDF 생성
 ② 로그: 국민건강보험공단 0200000000 → 05041341393 치환
 ③ 팝빌 접수번호 채번</t>
         </is>
       </c>
-      <c r="N30" s="33" t="inlineStr">
+      <c r="M30" s="33" t="inlineStr">
         <is>
           <t>화면/36_팩스발송-결과.png</t>
         </is>
       </c>
-      <c r="O30" s="34" t="inlineStr"/>
+      <c r="N30" s="34" t="inlineStr"/>
+      <c r="O30" s="35" t="inlineStr"/>
       <c r="P30" s="35" t="inlineStr"/>
       <c r="Q30" s="35" t="inlineStr"/>
       <c r="R30" s="35" t="inlineStr"/>
-      <c r="S30" s="35" t="inlineStr"/>
-      <c r="T30" s="34" t="inlineStr"/>
+      <c r="S30" s="34" t="inlineStr"/>
     </row>
     <row r="31" ht="82" customHeight="1">
       <c r="A31" s="36" t="inlineStr">
@@ -3504,35 +3401,30 @@
           <t>주문ㆍ재구매 › 주문 관리 / Finance</t>
         </is>
       </c>
-      <c r="G31" s="39" t="inlineStr">
-        <is>
-          <t>/orders · /finance</t>
-        </is>
-      </c>
-      <c r="H31" s="40" t="n">
+      <c r="G31" s="40" t="n">
         <v>1</v>
       </c>
+      <c r="H31" s="39" t="inlineStr">
+        <is>
+          <t>주문·창고·증빙 상태를 최종 확인한다</t>
+        </is>
+      </c>
       <c r="I31" s="39" t="inlineStr">
         <is>
-          <t>주문·창고·증빙 상태를 최종 확인한다</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J31" s="39" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K31" s="39" t="inlineStr">
-        <is>
           <t>목록 조회</t>
         </is>
       </c>
-      <c r="L31" s="41" t="inlineStr">
+      <c r="K31" s="41" t="inlineStr">
         <is>
           <t>전 구간 처리 결과 확인</t>
         </is>
       </c>
-      <c r="M31" s="42" t="inlineStr">
+      <c r="L31" s="42" t="inlineStr">
         <is>
           <t>① 처방전 RX-20260907-005 = 검수 완료
 ② 주문 EUD202609071734141 = confirmed
@@ -3541,17 +3433,17 @@
 ⑤ 공단 팩스 발송 완료</t>
         </is>
       </c>
-      <c r="N31" s="43" t="inlineStr">
+      <c r="M31" s="43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O31" s="28" t="inlineStr"/>
+      <c r="N31" s="28" t="inlineStr"/>
+      <c r="O31" s="29" t="inlineStr"/>
       <c r="P31" s="29" t="inlineStr"/>
       <c r="Q31" s="29" t="inlineStr"/>
       <c r="R31" s="29" t="inlineStr"/>
-      <c r="S31" s="29" t="inlineStr"/>
-      <c r="T31" s="28" t="inlineStr"/>
+      <c r="S31" s="28" t="inlineStr"/>
     </row>
     <row r="32" ht="82" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
@@ -3584,60 +3476,54 @@
           <t>Finance / 주문 관리</t>
         </is>
       </c>
-      <c r="G32" s="23" t="inlineStr">
-        <is>
-          <t>/finance</t>
-        </is>
-      </c>
-      <c r="H32" s="24" t="n">
+      <c r="G32" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="H32" s="23" t="inlineStr">
+        <is>
+          <t>Finance 목록에서 위드웍스 판매현황 항목이 표시되는지 확인한다</t>
+        </is>
+      </c>
       <c r="I32" s="23" t="inlineStr">
         <is>
-          <t>Finance 목록에서 위드웍스 판매현황 항목이 표시되는지 확인한다</t>
+          <t>조회 기간: 2026-09-01 ~ 2026-09-30</t>
         </is>
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>조회 기간: 2026-09-01 ~ 2026-09-30</t>
-        </is>
-      </c>
-      <c r="K32" s="23" t="inlineStr">
-        <is>
           <t>［검색］</t>
         </is>
       </c>
-      <c r="L32" s="25" t="inlineStr">
+      <c r="K32" s="25" t="inlineStr">
         <is>
           <t>ceWwCols() — Finance·주문 관리·입금 내역·현금영수증·청구 관리·교환/반품/취소 6개 화면이 동일한 위드웍스 판매현황 항목 순서를 공유한다</t>
         </is>
       </c>
-      <c r="M32" s="26" t="inlineStr">
+      <c r="L32" s="26" t="inlineStr">
         <is>
           <t>① 출고창고·납품창고 항목 표시
 ② 유형·구매 거래처·매출 금액·제품그룹 등 판매현황 항목이 값과 함께 표시
 ③ 구분(SB/SCI)·주민등록번호(마스킹)·상병코드·횟수는 자사 데이터로 표시</t>
         </is>
       </c>
-      <c r="N32" s="27" t="inlineStr">
+      <c r="M32" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O32" s="28" t="inlineStr"/>
+      <c r="N32" s="28" t="inlineStr"/>
+      <c r="O32" s="29" t="inlineStr"/>
       <c r="P32" s="29" t="inlineStr"/>
       <c r="Q32" s="29" t="inlineStr"/>
       <c r="R32" s="29" t="inlineStr"/>
-      <c r="S32" s="29" t="inlineStr"/>
-      <c r="T32" s="28" t="inlineStr"/>
+      <c r="S32" s="28" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:T32"/>
-  <mergeCells count="66">
+  <autoFilter ref="A2:S32"/>
+  <mergeCells count="57">
     <mergeCell ref="F15:F16"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="A24:A25"/>
-    <mergeCell ref="O1:T1"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="F12:F13"/>
@@ -3645,40 +3531,32 @@
     <mergeCell ref="C20:C23"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="A7:A8"/>
-    <mergeCell ref="G7:G8"/>
     <mergeCell ref="E20:E23"/>
     <mergeCell ref="E29:E30"/>
     <mergeCell ref="F5:F6"/>
+    <mergeCell ref="N1:S1"/>
     <mergeCell ref="C10:C11"/>
+    <mergeCell ref="G1:M1"/>
     <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G10:G11"/>
     <mergeCell ref="B29:B30"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="G3:G4"/>
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="F20:F23"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E15:E16"/>
-    <mergeCell ref="G15:G16"/>
     <mergeCell ref="D12:D13"/>
     <mergeCell ref="B10:B11"/>
-    <mergeCell ref="G24:G25"/>
     <mergeCell ref="B24:B25"/>
-    <mergeCell ref="H1:N1"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="D24:D25"/>
     <mergeCell ref="A5:A6"/>
-    <mergeCell ref="G5:G6"/>
     <mergeCell ref="D15:D16"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="A1:G1"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="A20:A23"/>
-    <mergeCell ref="G20:G23"/>
+    <mergeCell ref="A29:A30"/>
     <mergeCell ref="E7:E8"/>
-    <mergeCell ref="A29:A30"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D29:D30"/>
@@ -3687,10 +3565,10 @@
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="D10:D11"/>
     <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="E12:E13"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="B20:B23"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="G12:G13"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="D20:D23"/>
@@ -3702,7 +3580,7 @@
     <mergeCell ref="C5:C6"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="P3:P32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O3:O32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,N/A,Blocked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/테스트/테스트3차/5회/김태오/테스트시나리오_김태오.xlsx
+++ b/테스트/테스트3차/5회/김태오/테스트시나리오_김태오.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'환경설정'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'테스트시나리오'!$A$2:$S$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'테스트시나리오'!$A$2:$S$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'테스트시나리오'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'결함관리'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'캡처목록'!$1:$1</definedName>
@@ -834,7 +834,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CASE-01   |   End-to-End 통합 테스트   |   TC-001 ~ TC-019</t>
+          <t>CASE-01   |   End-to-End 통합 테스트   |   TC-001 ~ TC-020</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>19건 (TC-001 ~ TC-019)</t>
+          <t>21건 (TC-001 ~ TC-020, TC-013a 포함)</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S32"/>
+  <dimension ref="A1:S34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2913,22 +2913,22 @@
       </c>
       <c r="C24" s="22" t="inlineStr">
         <is>
-          <t>주문</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
         <is>
-          <t>주문 제품 등록</t>
+          <t>공단 신규/재등록 서류 팩스 — 자동 발송</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
-          <t>TC-012 완료 (검수 승인 + 동의 완료 필수)</t>
+          <t>TC-012 완료 · 설정 [동의 완료에 공단 팩스 발송] = 켬</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
         <is>
-          <t>주문 등록 › [주문 제품] 탭</t>
+          <t>(화면 조작 없음) 위임동의 서명 완료 시 서버가 자동 수행</t>
         </is>
       </c>
       <c r="G24" s="24" t="n">
@@ -2936,36 +2936,41 @@
       </c>
       <c r="H24" s="23" t="inlineStr">
         <is>
-          <t>제품 조회 팝업에서 처방 규격에 맞는 제품을 선택한다</t>
+          <t>위임동의 서명이 완료되면 자동 발송 여부를 확인한다</t>
         </is>
       </c>
       <c r="I24" s="23" t="inlineStr">
         <is>
-          <t>검색어: CH14 Male
-선택: EasiCath Nalaton CH14 Male 40cm - Green</t>
+          <t>(입력 없음)</t>
         </is>
       </c>
       <c r="J24" s="23" t="inlineStr">
         <is>
-          <t>［주문 제품］ 탭 → 제품명 칸 ⌕ → 제품 선택</t>
+          <t>(자동 — 클릭 대상 없음)</t>
         </is>
       </c>
       <c r="K24" s="25" t="inlineStr">
         <is>
-          <t>제품 선택 시 제품코드·소비자가가 자동 입력되고, 처방전 총계가 주문 수량으로 자동 반영된다</t>
+          <t>ConsentController → NhisFaxAuto::attempt(). [동의 서명] 요청 안에서 요양비위임장 PDF를 생성한 직후 호출된다(위임장이 있어야 보낼 수 있으므로 순서가 중요). 다음 5개 관문을 모두 통과해야 발송된다.
+① 설정 [동의 완료에 공단 팩스 발송]이 켜져 있을 것
+② 이미 발송한 이력이 없을 것 (중복 등록 방지)
+③ 공단 등록 대상일 것 — 위임이 필요한 자격(일반·차상위경감·기초)이면서 신구매이거나 재등록 대상
+   ※ 산재·자동차보험·처방외는 공단에 내지 않으므로 대상 아님
+④ 서류가 모두 있을 것 — 등록신청서·결과지·신분증·요양비위임장 (미성년이면 법정대리인 신분증 추가)
+⑤ 관할 청구처의 팩스번호가 있을 것
+④⑤에서 걸리면 발송하지 않고 담당자에게 알림을 보낸다. 여기서 오류가 나도 서명은 되돌리지 않는다.</t>
         </is>
       </c>
       <c r="L24" s="26" t="inlineStr">
         <is>
-          <t>① 제품코드 5354 / 수량 540 / 소비자가 1,500
-② 총 금액 810,000 · 기관 부담금 729,000(90%) · 본인 부담금 81,000(10%)</t>
+          <t>[설정 켬 + 조건 충족] 자동 발송되고 발송 이력에 접수번호가 남는다
+[설정 끔] 발송되지 않는다 → TC-013a 로 수동 발송
+[서류 누락] 발송하지 않고 담당자에게 「○○○ 이(가) 아직 없습니다」 알림</t>
         </is>
       </c>
       <c r="M24" s="27" t="inlineStr">
         <is>
-          <t>화면/26_주문제품-빈줄.png
-화면/27_제품조회-팝업.png
-화면/28_주문제품-채움.png</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="28" t="inlineStr"/>
@@ -2976,130 +2981,133 @@
       <c r="S24" s="28" t="inlineStr"/>
     </row>
     <row r="25" ht="82" customHeight="1">
-      <c r="A25" s="30" t="n"/>
-      <c r="B25" s="30" t="n"/>
-      <c r="C25" s="30" t="n"/>
-      <c r="D25" s="30" t="n"/>
-      <c r="E25" s="30" t="n"/>
-      <c r="F25" s="30" t="n"/>
-      <c r="G25" s="31" t="n">
+      <c r="A25" s="36" t="inlineStr">
+        <is>
+          <t>TC-013a</t>
+        </is>
+      </c>
+      <c r="B25" s="37" t="inlineStr">
+        <is>
+          <t>CASE-01 처방전·일반(10/90)·링크페이</t>
+        </is>
+      </c>
+      <c r="C25" s="38" t="inlineStr">
+        <is>
+          <t>등록</t>
+        </is>
+      </c>
+      <c r="D25" s="39" t="inlineStr">
+        <is>
+          <t>공단 신규/재등록 서류 팩스 — 수동 발송</t>
+        </is>
+      </c>
+      <c r="E25" s="39" t="inlineStr">
+        <is>
+          <t>TC-012 완료 · 자동 발송이 꺼져 있거나 관문에서 걸린 건</t>
+        </is>
+      </c>
+      <c r="F25" s="39" t="inlineStr">
+        <is>
+          <t>주문 등록 › 상단 [팩스 발송] 팝오버</t>
+        </is>
+      </c>
+      <c r="G25" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="39" t="inlineStr">
+        <is>
+          <t>수신처와 전송 서류를 확인한다</t>
+        </is>
+      </c>
+      <c r="I25" s="39" t="inlineStr">
+        <is>
+          <t>(입력 없음)</t>
+        </is>
+      </c>
+      <c r="J25" s="39" t="inlineStr">
+        <is>
+          <t>［팩스 발송］</t>
+        </is>
+      </c>
+      <c r="K25" s="41" t="inlineStr">
+        <is>
+          <t>자격이 공단 대상(일반·차상위경감·기초)이면 수신처가 건강보험공단으로 구성되고 관할 청구처의 팩스번호가 자동 표시된다. 신구매이거나 재등록 대상인데 아직 보내지 않은 건은 [팩스 발송] 버튼이 강조 표시된다(faxNudgeSync).</t>
+        </is>
+      </c>
+      <c r="L25" s="42" t="inlineStr">
+        <is>
+          <t>① 수신처 = 국민건강보험공단 · 공단 중구지사 · 보험급여부
+② 수신 팩스번호 = 관할 청구처 팩스 (02-0000-0000)
+③ 신청 파일 전체 선택 상태
+④ 안내문 「공단 팩스는 환자 등록·재등록용입니다 … 청구 자료는 팩스가 아니라 공단 사이트에 직접 업로드합니다」 표시</t>
+        </is>
+      </c>
+      <c r="M25" s="43" t="inlineStr">
+        <is>
+          <t>화면/35_팩스발송-창.png</t>
+        </is>
+      </c>
+      <c r="N25" s="28" t="inlineStr"/>
+      <c r="O25" s="29" t="inlineStr"/>
+      <c r="P25" s="29" t="inlineStr"/>
+      <c r="Q25" s="29" t="inlineStr"/>
+      <c r="R25" s="29" t="inlineStr"/>
+      <c r="S25" s="28" t="inlineStr"/>
+    </row>
+    <row r="26" ht="82" customHeight="1">
+      <c r="A26" s="30" t="n"/>
+      <c r="B26" s="30" t="n"/>
+      <c r="C26" s="30" t="n"/>
+      <c r="D26" s="30" t="n"/>
+      <c r="E26" s="30" t="n"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>주문 제품을 저장한다</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" s="6" t="inlineStr">
-        <is>
-          <t>［저장］</t>
-        </is>
-      </c>
-      <c r="K25" s="32" t="inlineStr">
-        <is>
-          <t>주문 품목 저장 및 청구전략별 금액 배분. 검수 승인과 동의가 모두 완료되어야 저장 가능하며 미완료 시 차단된다.</t>
-        </is>
-      </c>
-      <c r="L25" s="48" t="inlineStr">
-        <is>
-          <t>토스트 「저장되었습니다」</t>
-        </is>
-      </c>
-      <c r="M25" s="33" t="inlineStr">
-        <is>
-          <t>화면/29_주문제품-저장.png</t>
-        </is>
-      </c>
-      <c r="N25" s="34" t="inlineStr"/>
-      <c r="O25" s="35" t="inlineStr"/>
-      <c r="P25" s="35" t="inlineStr"/>
-      <c r="Q25" s="35" t="inlineStr"/>
-      <c r="R25" s="35" t="inlineStr"/>
-      <c r="S25" s="34" t="inlineStr"/>
-    </row>
-    <row r="26" ht="82" customHeight="1">
-      <c r="A26" s="36" t="inlineStr">
-        <is>
-          <t>TC-014</t>
-        </is>
-      </c>
-      <c r="B26" s="37" t="inlineStr">
-        <is>
-          <t>CASE-01 처방전·일반(10/90)·링크페이</t>
-        </is>
-      </c>
-      <c r="C26" s="38" t="inlineStr">
-        <is>
-          <t>연계</t>
-        </is>
-      </c>
-      <c r="D26" s="39" t="inlineStr">
-        <is>
-          <t>주문 생성 및 위드웍스 연계</t>
-        </is>
-      </c>
-      <c r="E26" s="39" t="inlineStr">
-        <is>
-          <t>TC-013 완료</t>
-        </is>
-      </c>
-      <c r="F26" s="39" t="inlineStr">
-        <is>
-          <t>주문 등록 › [주문 제품] 탭 하단</t>
-        </is>
-      </c>
-      <c r="G26" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="39" t="inlineStr">
-        <is>
-          <t>배송 정보를 확인하고 주문을 생성·연계한다</t>
-        </is>
-      </c>
-      <c r="I26" s="39" t="inlineStr">
-        <is>
-          <t>받는 사람: (E)(T3-5)김태오
-주소: 04524 서울특별시 중구 세종대로 110 / 테스트용 주소(3차 5회 김태오)</t>
-        </is>
-      </c>
-      <c r="J26" s="39" t="inlineStr">
-        <is>
-          <t>［주문 생성 및 연계］</t>
-        </is>
-      </c>
-      <c r="K26" s="41" t="inlineStr">
-        <is>
-          <t>POST /prescriptions/{rx}/withworks-order — ① 자사 주문(EUD…) 금액·품목 확정 ② 위드웍스 so_store 호출하여 판매주문(S…) 채번 및 저장 ③ 접수 안내·결제 안내 SMS 2건 발송 ④ 연계 내용을 확인 이메일로 발송 ⑤ 위드웍스가 so.created 웹훅을 회신하여 창고·판매현황 정보가 즉시 반영</t>
-        </is>
-      </c>
-      <c r="L26" s="42" t="inlineStr">
-        <is>
-          <t>① 창고 판매주문 S2609070004 채번
-② 출고창고 「3PL Main 판매창고」 즉시 표시
-③ 판매현황 항목 16건이 즉시 채워짐</t>
-        </is>
-      </c>
-      <c r="M26" s="43" t="inlineStr">
-        <is>
-          <t>화면/30_주문생성및연계.png</t>
-        </is>
-      </c>
-      <c r="N26" s="28" t="inlineStr"/>
-      <c r="O26" s="29" t="inlineStr"/>
-      <c r="P26" s="29" t="inlineStr"/>
-      <c r="Q26" s="29" t="inlineStr"/>
-      <c r="R26" s="29" t="inlineStr"/>
-      <c r="S26" s="28" t="inlineStr"/>
+      <c r="H26" s="15" t="inlineStr">
+        <is>
+          <t>팩스를 전송한다</t>
+        </is>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>(입력 없음)</t>
+        </is>
+      </c>
+      <c r="J26" s="15" t="inlineStr">
+        <is>
+          <t>［팩스 전송］</t>
+        </is>
+      </c>
+      <c r="K26" s="45" t="inlineStr">
+        <is>
+          <t>POST /prescriptions/{rx}/fax — ① 선택 서류를 표지 포함 단일 PDF로 병합 ② 팝빌로 전송 ③ 접수번호를 발송 이력에 기록. [팩스 발송=우리에게만]이면 수신번호만 테스트 팩스로 치환하고 수신처명은 유지한다.
+※ 이 팩스는 급여대상자 등록·재등록 신청이다. 요양비 청구가 아니다 — 청구는 별도로 공단 사이트에 직접 업로드한다.</t>
+        </is>
+      </c>
+      <c r="L26" s="46" t="inlineStr">
+        <is>
+          <t>① 팩스통합본 PDF 생성
+② 로그: 국민건강보험공단 0200000000 → 05041341393 치환
+③ 팝빌 접수번호 채번</t>
+        </is>
+      </c>
+      <c r="M26" s="47" t="inlineStr">
+        <is>
+          <t>화면/36_팩스발송-결과.png</t>
+        </is>
+      </c>
+      <c r="N26" s="34" t="inlineStr"/>
+      <c r="O26" s="35" t="inlineStr"/>
+      <c r="P26" s="35" t="inlineStr"/>
+      <c r="Q26" s="35" t="inlineStr"/>
+      <c r="R26" s="35" t="inlineStr"/>
+      <c r="S26" s="34" t="inlineStr"/>
     </row>
     <row r="27" ht="82" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>TC-015</t>
+          <t>TC-014</t>
         </is>
       </c>
       <c r="B27" s="21" t="inlineStr">
@@ -3109,22 +3117,22 @@
       </c>
       <c r="C27" s="22" t="inlineStr">
         <is>
-          <t>연계</t>
+          <t>주문</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
         <is>
-          <t>위드웍스 판매주문 확인</t>
+          <t>주문 제품 등록</t>
         </is>
       </c>
       <c r="E27" s="23" t="inlineStr">
         <is>
-          <t>TC-014 완료</t>
+          <t>TC-012 완료 (검수 승인 + 동의 완료 필수)</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t>[위드웍스] 주문 관리 › 판매 주문</t>
+          <t>주문 등록 › [주문 제품] 탭</t>
         </is>
       </c>
       <c r="G27" s="24" t="n">
@@ -3132,37 +3140,36 @@
       </c>
       <c r="H27" s="23" t="inlineStr">
         <is>
-          <t>위드웍스에서 판매번호로 조회한다</t>
+          <t>제품 조회 팝업에서 처방 규격에 맞는 제품을 선택한다</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
         <is>
-          <t>판매번호: S2609070004</t>
+          <t>검색어: CH14 Male
+선택: EasiCath Nalaton CH14 Male 40cm - Green</t>
         </is>
       </c>
       <c r="J27" s="23" t="inlineStr">
         <is>
-          <t>［검색］</t>
+          <t>［주문 제품］ 탭 → 제품명 칸 ⌕ → 제품 선택</t>
         </is>
       </c>
       <c r="K27" s="25" t="inlineStr">
         <is>
-          <t>위드웍스 판매주문 조회. CE Admin 주문번호는 etc SoNo 항목으로 연계된다.</t>
+          <t>제품 선택 시 제품코드·소비자가가 자동 입력되고, 처방전 총계가 주문 수량으로 자동 반영된다. 금액은 자격별 청구전략에 따라 배분된다.</t>
         </is>
       </c>
       <c r="L27" s="26" t="inlineStr">
         <is>
-          <t>① etc SoNo = EUD202609071734141 (CE 주문번호 일치)
-② 구매 거래처명 = (E)(T3-5)김태오
-③ 출고창고명 = 3PL Main 판매창고
-④ 판매금액 = 810,000
-⑤ 비고 = 업로드 시 입력한 메모 그대로</t>
+          <t>① 제품코드 5354 / 수량 540 / 소비자가 1,500
+② 총 금액 810,000 · 기관 부담금 729,000(90%) · 본인 부담금 81,000(10%)</t>
         </is>
       </c>
       <c r="M27" s="27" t="inlineStr">
         <is>
-          <t>화면/31_ww_판매주문-화면.png
-화면/32_ww_판매주문-조회결과.png</t>
+          <t>화면/26_주문제품-빈줄.png
+화면/27_제품조회-팝업.png
+화면/28_주문제품-채움.png</t>
         </is>
       </c>
       <c r="N27" s="28" t="inlineStr"/>
@@ -3173,145 +3180,117 @@
       <c r="S27" s="28" t="inlineStr"/>
     </row>
     <row r="28" ht="82" customHeight="1">
-      <c r="A28" s="36" t="inlineStr">
-        <is>
-          <t>TC-016</t>
-        </is>
-      </c>
-      <c r="B28" s="37" t="inlineStr">
+      <c r="A28" s="30" t="n"/>
+      <c r="B28" s="30" t="n"/>
+      <c r="C28" s="30" t="n"/>
+      <c r="D28" s="30" t="n"/>
+      <c r="E28" s="30" t="n"/>
+      <c r="F28" s="30" t="n"/>
+      <c r="G28" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>주문 제품을 저장한다</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>(입력 없음)</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>［저장］</t>
+        </is>
+      </c>
+      <c r="K28" s="32" t="inlineStr">
+        <is>
+          <t>주문 품목 저장 및 청구전략별 금액 배분. 검수 승인과 동의가 모두 완료되어야 저장 가능하며 미완료 시 차단된다.</t>
+        </is>
+      </c>
+      <c r="L28" s="48" t="inlineStr">
+        <is>
+          <t>토스트 「저장되었습니다」</t>
+        </is>
+      </c>
+      <c r="M28" s="33" t="inlineStr">
+        <is>
+          <t>화면/29_주문제품-저장.png</t>
+        </is>
+      </c>
+      <c r="N28" s="34" t="inlineStr"/>
+      <c r="O28" s="35" t="inlineStr"/>
+      <c r="P28" s="35" t="inlineStr"/>
+      <c r="Q28" s="35" t="inlineStr"/>
+      <c r="R28" s="35" t="inlineStr"/>
+      <c r="S28" s="34" t="inlineStr"/>
+    </row>
+    <row r="29" ht="82" customHeight="1">
+      <c r="A29" s="36" t="inlineStr">
+        <is>
+          <t>TC-015</t>
+        </is>
+      </c>
+      <c r="B29" s="37" t="inlineStr">
         <is>
           <t>CASE-01 처방전·일반(10/90)·링크페이</t>
         </is>
       </c>
-      <c r="C28" s="38" t="inlineStr">
-        <is>
-          <t>정산</t>
-        </is>
-      </c>
-      <c r="D28" s="39" t="inlineStr">
-        <is>
-          <t>입금 확인 (담당자 수동)</t>
-        </is>
-      </c>
-      <c r="E28" s="39" t="inlineStr">
+      <c r="C29" s="38" t="inlineStr">
+        <is>
+          <t>연계</t>
+        </is>
+      </c>
+      <c r="D29" s="39" t="inlineStr">
+        <is>
+          <t>주문 생성 및 위드웍스 연계</t>
+        </is>
+      </c>
+      <c r="E29" s="39" t="inlineStr">
         <is>
           <t>TC-014 완료</t>
         </is>
       </c>
-      <c r="F28" s="39" t="inlineStr">
-        <is>
-          <t>청구ㆍ회계 › 정산/회계</t>
-        </is>
-      </c>
-      <c r="G28" s="40" t="n">
+      <c r="F29" s="39" t="inlineStr">
+        <is>
+          <t>주문 등록 › [주문 제품] 탭 하단</t>
+        </is>
+      </c>
+      <c r="G29" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="H28" s="39" t="inlineStr">
-        <is>
-          <t>해당 주문의 결제수단을 선택하여 입금을 확인한다</t>
-        </is>
-      </c>
-      <c r="I28" s="39" t="inlineStr">
-        <is>
-          <t>결제수단: 링크페이</t>
-        </is>
-      </c>
-      <c r="J28" s="39" t="inlineStr">
-        <is>
-          <t>결제수단 칸 → 링크페이 선택</t>
-        </is>
-      </c>
-      <c r="K28" s="41" t="inlineStr">
-        <is>
-          <t>POST /settlement/orders/{order}/pay-method — 결제수단 선택 시점이 곧 입금 확인이다. ① 입금 확인 처리 ② 세금계산서 발행 ③ 거래명세서 생성 ④ 위드웍스 판매주문 확정 ⑤ 청구전략상 대상이 아닌 증빙은 자동 제외</t>
-        </is>
-      </c>
-      <c r="L28" s="42" t="inlineStr">
-        <is>
-          <t>① 링크페이 · 81,000원 입금 확인
-② 세금계산서 TI20260907000243 발행
-③ 거래명세서 PDF 생성
-④ 위드웍스 S2609070004 확정
-⑤ 현금영수증은 「청구전략에 없음」으로 제외</t>
-        </is>
-      </c>
-      <c r="M28" s="43" t="inlineStr">
-        <is>
-          <t>화면/33_정산회계-목록.png
-화면/34_입금확인-뒤.png</t>
-        </is>
-      </c>
-      <c r="N28" s="28" t="inlineStr"/>
-      <c r="O28" s="29" t="inlineStr"/>
-      <c r="P28" s="29" t="inlineStr"/>
-      <c r="Q28" s="29" t="inlineStr"/>
-      <c r="R28" s="29" t="inlineStr"/>
-      <c r="S28" s="28" t="inlineStr"/>
-    </row>
-    <row r="29" ht="82" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>TC-017</t>
-        </is>
-      </c>
-      <c r="B29" s="21" t="inlineStr">
-        <is>
-          <t>CASE-01 처방전·일반(10/90)·링크페이</t>
-        </is>
-      </c>
-      <c r="C29" s="22" t="inlineStr">
-        <is>
-          <t>청구</t>
-        </is>
-      </c>
-      <c r="D29" s="23" t="inlineStr">
-        <is>
-          <t>공단 등록 서류 팩스 발송</t>
-        </is>
-      </c>
-      <c r="E29" s="23" t="inlineStr">
-        <is>
-          <t>TC-012 완료 · 팩스 발송=우리에게만</t>
-        </is>
-      </c>
-      <c r="F29" s="23" t="inlineStr">
-        <is>
-          <t>주문 등록 › 상단 [팩스 발송] 팝오버</t>
-        </is>
-      </c>
-      <c r="G29" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="23" t="inlineStr">
-        <is>
-          <t>수신처와 전송 서류를 확인한다</t>
-        </is>
-      </c>
-      <c r="I29" s="23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J29" s="23" t="inlineStr">
-        <is>
-          <t>［팩스 발송］</t>
-        </is>
-      </c>
-      <c r="K29" s="25" t="inlineStr">
-        <is>
-          <t>자격이 [일반]이므로 수신처가 건강보험공단으로 구성되고, 관할 청구처의 팩스번호가 자동 표시된다</t>
-        </is>
-      </c>
-      <c r="L29" s="26" t="inlineStr">
-        <is>
-          <t>① 수신처 = 국민건강보험공단 · 공단 중구지사 · 보험급여부
-② 수신 팩스번호 = 02-0000-0000
-③ 신청 파일 11건 전체 선택 상태</t>
-        </is>
-      </c>
-      <c r="M29" s="27" t="inlineStr">
-        <is>
-          <t>화면/35_팩스발송-창.png</t>
+      <c r="H29" s="39" t="inlineStr">
+        <is>
+          <t>배송 정보를 확인하고 주문을 생성·연계한다</t>
+        </is>
+      </c>
+      <c r="I29" s="39" t="inlineStr">
+        <is>
+          <t>받는 사람: (E)(T3-5)김태오
+주소: 04524 서울특별시 중구 세종대로 110 / 테스트용 주소(3차 5회 김태오)</t>
+        </is>
+      </c>
+      <c r="J29" s="39" t="inlineStr">
+        <is>
+          <t>［주문 생성 및 연계］</t>
+        </is>
+      </c>
+      <c r="K29" s="41" t="inlineStr">
+        <is>
+          <t>POST /prescriptions/{rx}/withworks-order — ① 자사 주문(EUD…) 금액·품목 확정 ② 위드웍스 so_store 호출하여 판매주문(S…) 채번 및 저장 ③ 접수 안내·결제 안내 SMS 2건 발송 ④ 연계 내용을 확인 이메일로 발송 ⑤ 위드웍스가 so.created 웹훅을 회신하여 창고·판매현황 정보가 즉시 반영</t>
+        </is>
+      </c>
+      <c r="L29" s="42" t="inlineStr">
+        <is>
+          <t>① 창고 판매주문 S2609070004 채번
+② 출고창고 「3PL Main 판매창고」 즉시 표시
+③ 판매현황 항목 16건이 즉시 채워짐</t>
+        </is>
+      </c>
+      <c r="M29" s="43" t="inlineStr">
+        <is>
+          <t>화면/30_주문생성및연계.png</t>
         </is>
       </c>
       <c r="N29" s="28" t="inlineStr"/>
@@ -3322,58 +3301,85 @@
       <c r="S29" s="28" t="inlineStr"/>
     </row>
     <row r="30" ht="82" customHeight="1">
-      <c r="A30" s="30" t="n"/>
-      <c r="B30" s="30" t="n"/>
-      <c r="C30" s="30" t="n"/>
-      <c r="D30" s="30" t="n"/>
-      <c r="E30" s="30" t="n"/>
-      <c r="F30" s="30" t="n"/>
-      <c r="G30" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>팩스를 전송한다</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J30" s="6" t="inlineStr">
-        <is>
-          <t>［팩스 전송］</t>
-        </is>
-      </c>
-      <c r="K30" s="32" t="inlineStr">
-        <is>
-          <t>POST /prescriptions/{rx}/fax — ① 선택 서류를 표지 포함 단일 PDF로 병합 ② 팝빌로 전송 ③ 접수번호를 발송 이력에 기록. [우리에게만]이면 수신번호만 테스트 팩스로 치환하고 수신처명은 유지한다.</t>
-        </is>
-      </c>
-      <c r="L30" s="48" t="inlineStr">
-        <is>
-          <t>① 팩스통합본 PDF 생성
-② 로그: 국민건강보험공단 0200000000 → 05041341393 치환
-③ 팝빌 접수번호 채번</t>
-        </is>
-      </c>
-      <c r="M30" s="33" t="inlineStr">
-        <is>
-          <t>화면/36_팩스발송-결과.png</t>
-        </is>
-      </c>
-      <c r="N30" s="34" t="inlineStr"/>
-      <c r="O30" s="35" t="inlineStr"/>
-      <c r="P30" s="35" t="inlineStr"/>
-      <c r="Q30" s="35" t="inlineStr"/>
-      <c r="R30" s="35" t="inlineStr"/>
-      <c r="S30" s="34" t="inlineStr"/>
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>TC-016</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>CASE-01 처방전·일반(10/90)·링크페이</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>연계</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>위드웍스 판매주문 확인</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>TC-015 완료</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>[위드웍스] 주문 관리 › 판매 주문</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="23" t="inlineStr">
+        <is>
+          <t>위드웍스에서 판매번호로 조회한다</t>
+        </is>
+      </c>
+      <c r="I30" s="23" t="inlineStr">
+        <is>
+          <t>판매번호: S2609070004</t>
+        </is>
+      </c>
+      <c r="J30" s="23" t="inlineStr">
+        <is>
+          <t>［검색］</t>
+        </is>
+      </c>
+      <c r="K30" s="25" t="inlineStr">
+        <is>
+          <t>위드웍스 판매주문 조회. CE Admin 주문번호는 etc SoNo 항목으로 연계된다.</t>
+        </is>
+      </c>
+      <c r="L30" s="26" t="inlineStr">
+        <is>
+          <t>① etc SoNo = EUD202609071734141 (CE 주문번호 일치)
+② 구매 거래처명 = (E)(T3-5)김태오
+③ 출고창고명 = 3PL Main 판매창고
+④ 판매금액 = 810,000
+⑤ 비고 = 업로드 시 입력한 메모 그대로</t>
+        </is>
+      </c>
+      <c r="M30" s="27" t="inlineStr">
+        <is>
+          <t>화면/31_ww_판매주문-화면.png
+화면/32_ww_판매주문-조회결과.png</t>
+        </is>
+      </c>
+      <c r="N30" s="28" t="inlineStr"/>
+      <c r="O30" s="29" t="inlineStr"/>
+      <c r="P30" s="29" t="inlineStr"/>
+      <c r="Q30" s="29" t="inlineStr"/>
+      <c r="R30" s="29" t="inlineStr"/>
+      <c r="S30" s="28" t="inlineStr"/>
     </row>
     <row r="31" ht="82" customHeight="1">
       <c r="A31" s="36" t="inlineStr">
         <is>
-          <t>TC-018</t>
+          <t>TC-017</t>
         </is>
       </c>
       <c r="B31" s="37" t="inlineStr">
@@ -3383,22 +3389,22 @@
       </c>
       <c r="C31" s="38" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>정산</t>
         </is>
       </c>
       <c r="D31" s="39" t="inlineStr">
         <is>
-          <t>최종 상태 검증</t>
+          <t>주문 확정 / 입금 확인</t>
         </is>
       </c>
       <c r="E31" s="39" t="inlineStr">
         <is>
-          <t>TC-001 ~ TC-017 완료</t>
+          <t>TC-015 완료</t>
         </is>
       </c>
       <c r="F31" s="39" t="inlineStr">
         <is>
-          <t>주문ㆍ재구매 › 주문 관리 / Finance</t>
+          <t>청구ㆍ회계 › 정산/회계</t>
         </is>
       </c>
       <c r="G31" s="40" t="n">
@@ -3406,36 +3412,37 @@
       </c>
       <c r="H31" s="39" t="inlineStr">
         <is>
-          <t>주문·창고·증빙 상태를 최종 확인한다</t>
+          <t>해당 주문의 결제수단을 선택한다</t>
         </is>
       </c>
       <c r="I31" s="39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>결제수단: 링크페이</t>
         </is>
       </c>
       <c r="J31" s="39" t="inlineStr">
         <is>
-          <t>목록 조회</t>
+          <t>결제수단 칸 → 링크페이 선택</t>
         </is>
       </c>
       <c r="K31" s="41" t="inlineStr">
         <is>
-          <t>전 구간 처리 결과 확인</t>
+          <t>POST /settlement/orders/{order}/pay-method — 결제수단 선택 시점이 곧 확정 시점이다. ① 입금 확인(또는 주문 확정) 처리 ② 세금계산서 발행 ③ 거래명세서 생성 ④ 위드웍스 판매주문 확정 ⑤ 청구전략상 대상이 아닌 증빙은 자동 제외
+④는 DepositAutoIssue 끝에서 WithworksConfirm 이 so_confirm 을 호출하는 것으로, 여태 담당자가 위드웍스 화면에서 손으로 눌러야 출고가 시작되던 일을 대신한다. 재고가 모자라 확정되지 않아도 입금 확인은 되돌리지 않고 까닭만 남긴다 → TC-018 에서 확인
+※ 본인부담금이 0원인 건(차상위경감·기초)은 받을 돈이 없으므로 「주문 확정」으로 처리되고 메시지도 그렇게 표시된다.</t>
         </is>
       </c>
       <c r="L31" s="42" t="inlineStr">
         <is>
-          <t>① 처방전 RX-20260907-005 = 검수 완료
-② 주문 EUD202609071734141 = confirmed
-③ 창고 S2609070004 = 확정
-④ 세금계산서 TI20260907000243 발행
-⑤ 공단 팩스 발송 완료</t>
+          <t>[본인부담 있음] 「링크페이으로 81,000원 입금 확인했습니다」
+[본인부담 0원] 「본인부담금이 없는 건입니다 — 주문을 확정했습니다」
+공통: ① 세금계산서 TI20260907000243 발행 ② 거래명세서 PDF 생성 ③ 위드웍스 S2609070004 확정 ④ 현금영수증은 「청구전략에 없음」으로 제외</t>
         </is>
       </c>
       <c r="M31" s="43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>화면/33_정산회계-목록.png
+화면/34_입금확인-뒤.png</t>
         </is>
       </c>
       <c r="N31" s="28" t="inlineStr"/>
@@ -3448,7 +3455,7 @@
     <row r="32" ht="82" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>TC-019</t>
+          <t>TC-018</t>
         </is>
       </c>
       <c r="B32" s="21" t="inlineStr">
@@ -3458,22 +3465,22 @@
       </c>
       <c r="C32" s="22" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>연계</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
         <is>
-          <t>목록 항목 검증 (판매현황 연계)</t>
+          <t>위드웍스 판매주문 확정 확인</t>
         </is>
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
-          <t>TC-014 완료</t>
+          <t>TC-017 완료</t>
         </is>
       </c>
       <c r="F32" s="23" t="inlineStr">
         <is>
-          <t>Finance / 주문 관리</t>
+          <t>[위드웍스] 주문 관리 › 판매 주문</t>
         </is>
       </c>
       <c r="G32" s="24" t="n">
@@ -3481,34 +3488,38 @@
       </c>
       <c r="H32" s="23" t="inlineStr">
         <is>
-          <t>Finance 목록에서 위드웍스 판매현황 항목이 표시되는지 확인한다</t>
+          <t>입금 확인(주문 확정)이 창고까지 닿았는지 확인한다</t>
         </is>
       </c>
       <c r="I32" s="23" t="inlineStr">
         <is>
-          <t>조회 기간: 2026-09-01 ~ 2026-09-30</t>
+          <t>판매번호: S2609070004
+판매상태: 등록·승인·확정·거절 모두 선택</t>
         </is>
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>［검색］</t>
+          <t>［검색］ → 행 더블클릭 → [상세 목록] 탭</t>
         </is>
       </c>
       <c r="K32" s="25" t="inlineStr">
         <is>
-          <t>ceWwCols() — Finance·주문 관리·입금 내역·현금영수증·청구 관리·교환/반품/취소 6개 화면이 동일한 위드웍스 판매현황 항목 순서를 공유한다</t>
+          <t>TC-017 에서 보낸 so_confirm 의 결과를 창고 쪽에서 확인한다. so_store 시점에는 confirm=0(등록)으로 서 있다가, 입금 확인 시점에 확정으로 옮겨지며 이때 가용재고가 잡힌다. 확정이 되어야 우리 쪽 주문 상태도 pending → confirmed 로 바뀐다.</t>
         </is>
       </c>
       <c r="L32" s="26" t="inlineStr">
         <is>
-          <t>① 출고창고·납품창고 항목 표시
-② 유형·구매 거래처·매출 금액·제품그룹 등 판매현황 항목이 값과 함께 표시
-③ 구분(SB/SCI)·주민등록번호(마스킹)·상병코드·횟수는 자사 데이터로 표시</t>
+          <t>① 판매상태 = 확정 (등록 아님)
+② 확정판매금액 810,000 · 확정일자 2026-09-07 채워짐
+③ 화면 단추가 [마감 확정] 에서 [확정 취소]·[반품] 으로 바뀜
+④ 출고창고 = Main / 3PL Main 판매창고
+⑤ CE Admin 주문 상태 = confirmed · 활동 기록에 「위드웍스 판매주문 S2609070004 확정」
+[재고 부족 시] 확정되지 않고 까닭만 기록된다 — 입금 확인은 되돌리지 않고 담당자가 재고를 채운 뒤 다시 확정</t>
         </is>
       </c>
       <c r="M32" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>화면/37_ww_판매주문-확정.png</t>
         </is>
       </c>
       <c r="N32" s="28" t="inlineStr"/>
@@ -3518,52 +3529,201 @@
       <c r="R32" s="29" t="inlineStr"/>
       <c r="S32" s="28" t="inlineStr"/>
     </row>
+    <row r="33" ht="82" customHeight="1">
+      <c r="A33" s="36" t="inlineStr">
+        <is>
+          <t>TC-019</t>
+        </is>
+      </c>
+      <c r="B33" s="37" t="inlineStr">
+        <is>
+          <t>CASE-01 처방전·일반(10/90)·링크페이</t>
+        </is>
+      </c>
+      <c r="C33" s="38" t="inlineStr">
+        <is>
+          <t>검증</t>
+        </is>
+      </c>
+      <c r="D33" s="39" t="inlineStr">
+        <is>
+          <t>최종 상태 검증</t>
+        </is>
+      </c>
+      <c r="E33" s="39" t="inlineStr">
+        <is>
+          <t>TC-001 ~ TC-018 완료</t>
+        </is>
+      </c>
+      <c r="F33" s="39" t="inlineStr">
+        <is>
+          <t>주문ㆍ재구매 › 주문 관리 / Finance</t>
+        </is>
+      </c>
+      <c r="G33" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="39" t="inlineStr">
+        <is>
+          <t>주문·창고·증빙 상태를 최종 확인한다</t>
+        </is>
+      </c>
+      <c r="I33" s="39" t="inlineStr">
+        <is>
+          <t>(입력 없음)</t>
+        </is>
+      </c>
+      <c r="J33" s="39" t="inlineStr">
+        <is>
+          <t>목록 조회</t>
+        </is>
+      </c>
+      <c r="K33" s="41" t="inlineStr">
+        <is>
+          <t>전 구간 처리 결과 확인</t>
+        </is>
+      </c>
+      <c r="L33" s="42" t="inlineStr">
+        <is>
+          <t>① 처방전 RX-20260907-005 = 검수 완료
+② 주문 EUD202609071734141 = confirmed
+③ 창고 S2609070004 = 확정
+④ 세금계산서 TI20260907000243 발행
+⑤ 공단 등록 서류 팩스 발송 완료</t>
+        </is>
+      </c>
+      <c r="M33" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="28" t="inlineStr"/>
+      <c r="O33" s="29" t="inlineStr"/>
+      <c r="P33" s="29" t="inlineStr"/>
+      <c r="Q33" s="29" t="inlineStr"/>
+      <c r="R33" s="29" t="inlineStr"/>
+      <c r="S33" s="28" t="inlineStr"/>
+    </row>
+    <row r="34" ht="82" customHeight="1">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>TC-020</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>CASE-01 처방전·일반(10/90)·링크페이</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>검증</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>목록 항목 검증 (판매현황 연계)</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="inlineStr">
+        <is>
+          <t>TC-015 완료</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>Finance / 주문 관리</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="23" t="inlineStr">
+        <is>
+          <t>Finance 목록에서 위드웍스 판매현황 항목이 표시되는지 확인한다</t>
+        </is>
+      </c>
+      <c r="I34" s="23" t="inlineStr">
+        <is>
+          <t>조회 기간: 2026-09-01 ~ 2026-09-30</t>
+        </is>
+      </c>
+      <c r="J34" s="23" t="inlineStr">
+        <is>
+          <t>［검색］</t>
+        </is>
+      </c>
+      <c r="K34" s="25" t="inlineStr">
+        <is>
+          <t>ceWwCols() — Finance·주문 관리·입금 내역·현금영수증·청구 관리·교환/반품/취소 6개 화면이 동일한 위드웍스 판매현황 항목 순서를 공유한다</t>
+        </is>
+      </c>
+      <c r="L34" s="26" t="inlineStr">
+        <is>
+          <t>① 출고창고·납품창고 항목 표시
+② 유형·구매 거래처·매출 금액·제품그룹 등 판매현황 항목이 값과 함께 표시
+③ 구분(SB/SCI)·주민등록번호(마스킹)·상병코드·횟수는 자사 데이터로 표시</t>
+        </is>
+      </c>
+      <c r="M34" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="28" t="inlineStr"/>
+      <c r="O34" s="29" t="inlineStr"/>
+      <c r="P34" s="29" t="inlineStr"/>
+      <c r="Q34" s="29" t="inlineStr"/>
+      <c r="R34" s="29" t="inlineStr"/>
+      <c r="S34" s="28" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:S32"/>
+  <autoFilter ref="A2:S34"/>
   <mergeCells count="57">
     <mergeCell ref="F15:F16"/>
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="F25:F26"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="F12:F13"/>
-    <mergeCell ref="C29:C30"/>
     <mergeCell ref="C20:C23"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="E20:E23"/>
-    <mergeCell ref="E29:E30"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="N1:S1"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="G1:M1"/>
     <mergeCell ref="E10:E11"/>
-    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="A27:A28"/>
     <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A25:A26"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C25:C26"/>
     <mergeCell ref="F20:F23"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E15:E16"/>
     <mergeCell ref="D12:D13"/>
     <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B24:B25"/>
     <mergeCell ref="B15:B16"/>
-    <mergeCell ref="D24:D25"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="C27:C28"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="D25:D26"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D29:D30"/>
     <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="E24:E25"/>
     <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E25:E26"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E12:E13"/>
@@ -3573,14 +3733,13 @@
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="D20:D23"/>
     <mergeCell ref="C15:C16"/>
+    <mergeCell ref="B25:B26"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="C24:C25"/>
     <mergeCell ref="F10:F11"/>
-    <mergeCell ref="F24:F25"/>
     <mergeCell ref="C5:C6"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="O3:O32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O3:O34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,N/A,Blocked"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3603,7 +3762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3884,6 +4043,140 @@
         </is>
       </c>
       <c r="M4" s="52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="64" customHeight="1">
+      <c r="A5" s="54" t="inlineStr">
+        <is>
+          <t>OBS-04</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>TC-013</t>
+        </is>
+      </c>
+      <c r="C5" s="56" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="D5" s="55" t="inlineStr">
+        <is>
+          <t>환경</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>동의 완료 시 공단 등록 서류 팩스가 자동 발송되지 않음</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>위임동의 서명 완료 → 발송 이력 확인</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>설정에 따라 자동 발송</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>자동 발송되지 않음</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>[동의 완료에 공단 팩스 발송] 설정이 꺼져 있는 상태. 설정값대로 동작한 것이며 결함 아님. TC-013a 수동 발송으로 진행</t>
+        </is>
+      </c>
+      <c r="J5" s="55" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="K5" s="55" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="L5" s="55" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="M5" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="64" customHeight="1">
+      <c r="A6" s="51" t="inlineStr">
+        <is>
+          <t>OBS-05</t>
+        </is>
+      </c>
+      <c r="B6" s="52" t="inlineStr">
+        <is>
+          <t>TC-018</t>
+        </is>
+      </c>
+      <c r="C6" s="57" t="inlineStr">
+        <is>
+          <t>경미</t>
+        </is>
+      </c>
+      <c r="D6" s="52" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>위드웍스 판매주문 확정자 칸이 비어 있음</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>입금 확인(주문 확정) → 위드웍스 판매 주문 상세 목록 확인</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>확정을 수행한 주체가 남는다</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>확정자 칸이 빈 상태 (판매상태·확정판매금액·확정일자는 정상)</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>so_confirm API 로 확정하면 화면 사용자가 없어 확정자가 남지 않음. 누가 확정했는지 추적하려면 연동 계정명을 남기도록 위드웍스 쪽 보완 필요 — CE Admin 활동 기록에는 남으므로 급하지 않음</t>
+        </is>
+      </c>
+      <c r="J6" s="52" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="K6" s="52" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="L6" s="52" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="M6" s="52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3909,7 +4202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4627,22 +4920,22 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>26_주문제품-빈줄.png</t>
+          <t>35_팩스발송-창.png</t>
         </is>
       </c>
       <c r="C29" s="55" t="inlineStr">
         <is>
-          <t>TC-013</t>
-        </is>
-      </c>
-      <c r="D29" s="56" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+          <t>TC-013a</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>팝오버</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>주문 제품 탭 초기 상태</t>
+          <t>공단 신규/재등록 서류 팩스 — 수신처·전송 서류</t>
         </is>
       </c>
     </row>
@@ -4652,22 +4945,22 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>27_제품조회-팝업.png</t>
+          <t>36_팩스발송-결과.png</t>
         </is>
       </c>
       <c r="C30" s="52" t="inlineStr">
         <is>
-          <t>TC-013</t>
+          <t>TC-013a</t>
         </is>
       </c>
       <c r="D30" s="57" t="inlineStr">
         <is>
-          <t>팝업</t>
+          <t>팝오버</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>제품 조회 — CH14 Male</t>
+          <t>공단 신규/재등록 서류 팩스 — 발송 결과</t>
         </is>
       </c>
     </row>
@@ -4677,12 +4970,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>28_주문제품-채움.png</t>
+          <t>26_주문제품-빈줄.png</t>
         </is>
       </c>
       <c r="C31" s="55" t="inlineStr">
         <is>
-          <t>TC-013</t>
+          <t>TC-014</t>
         </is>
       </c>
       <c r="D31" s="56" t="inlineStr">
@@ -4692,7 +4985,7 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>제품 선택 후 금액 자동 배분</t>
+          <t>주문 제품 탭 초기 상태</t>
         </is>
       </c>
     </row>
@@ -4702,22 +4995,22 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>29_주문제품-저장.png</t>
+          <t>27_제품조회-팝업.png</t>
         </is>
       </c>
       <c r="C32" s="52" t="inlineStr">
         <is>
-          <t>TC-013</t>
-        </is>
-      </c>
-      <c r="D32" s="53" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+          <t>TC-014</t>
+        </is>
+      </c>
+      <c r="D32" s="57" t="inlineStr">
+        <is>
+          <t>팝업</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>주문 제품 저장 완료</t>
+          <t>제품 조회 — CH14 Male</t>
         </is>
       </c>
     </row>
@@ -4727,7 +5020,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>30_주문생성및연계.png</t>
+          <t>28_주문제품-채움.png</t>
         </is>
       </c>
       <c r="C33" s="55" t="inlineStr">
@@ -4742,7 +5035,7 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>주문 생성 및 위드웍스 연계 결과</t>
+          <t>제품 선택 후 금액 자동 배분</t>
         </is>
       </c>
     </row>
@@ -4752,22 +5045,22 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>31_ww_판매주문-화면.png</t>
+          <t>29_주문제품-저장.png</t>
         </is>
       </c>
       <c r="C34" s="52" t="inlineStr">
         <is>
-          <t>TC-015</t>
-        </is>
-      </c>
-      <c r="D34" s="59" t="inlineStr">
-        <is>
-          <t>위드웍스</t>
+          <t>TC-014</t>
+        </is>
+      </c>
+      <c r="D34" s="53" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
         </is>
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>판매 주문 조회 화면</t>
+          <t>주문 제품 저장 완료</t>
         </is>
       </c>
     </row>
@@ -4777,7 +5070,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>32_ww_판매주문-조회결과.png</t>
+          <t>30_주문생성및연계.png</t>
         </is>
       </c>
       <c r="C35" s="55" t="inlineStr">
@@ -4785,14 +5078,14 @@
           <t>TC-015</t>
         </is>
       </c>
-      <c r="D35" s="60" t="inlineStr">
-        <is>
-          <t>위드웍스</t>
+      <c r="D35" s="56" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>판매주문 S2609070004 조회 결과</t>
+          <t>주문 생성 및 위드웍스 연계 결과</t>
         </is>
       </c>
     </row>
@@ -4802,7 +5095,7 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>33_정산회계-목록.png</t>
+          <t>31_ww_판매주문-화면.png</t>
         </is>
       </c>
       <c r="C36" s="52" t="inlineStr">
@@ -4810,14 +5103,14 @@
           <t>TC-016</t>
         </is>
       </c>
-      <c r="D36" s="53" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+      <c r="D36" s="59" t="inlineStr">
+        <is>
+          <t>위드웍스</t>
         </is>
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>정산/회계 목록</t>
+          <t>판매 주문 조회 화면</t>
         </is>
       </c>
     </row>
@@ -4827,7 +5120,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>34_입금확인-뒤.png</t>
+          <t>32_ww_판매주문-조회결과.png</t>
         </is>
       </c>
       <c r="C37" s="55" t="inlineStr">
@@ -4835,14 +5128,14 @@
           <t>TC-016</t>
         </is>
       </c>
-      <c r="D37" s="56" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+      <c r="D37" s="60" t="inlineStr">
+        <is>
+          <t>위드웍스</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>입금 확인 후 상태</t>
+          <t>판매주문 S2609070004 조회 결과</t>
         </is>
       </c>
     </row>
@@ -4852,7 +5145,7 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>35_팩스발송-창.png</t>
+          <t>33_정산회계-목록.png</t>
         </is>
       </c>
       <c r="C38" s="52" t="inlineStr">
@@ -4860,14 +5153,14 @@
           <t>TC-017</t>
         </is>
       </c>
-      <c r="D38" s="57" t="inlineStr">
-        <is>
-          <t>팝오버</t>
+      <c r="D38" s="53" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
         </is>
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t>팩스 발송 — 수신처·전송 서류</t>
+          <t>정산/회계 목록</t>
         </is>
       </c>
     </row>
@@ -4877,7 +5170,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>36_팩스발송-결과.png</t>
+          <t>34_입금확인-뒤.png</t>
         </is>
       </c>
       <c r="C39" s="55" t="inlineStr">
@@ -4885,14 +5178,39 @@
           <t>TC-017</t>
         </is>
       </c>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>팝오버</t>
+      <c r="D39" s="56" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>팩스 발송 결과</t>
+          <t>주문 확정 / 입금 확인 후 상태</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="52" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>37_ww_판매주문-확정.png</t>
+        </is>
+      </c>
+      <c r="C40" s="52" t="inlineStr">
+        <is>
+          <t>TC-018</t>
+        </is>
+      </c>
+      <c r="D40" s="59" t="inlineStr">
+        <is>
+          <t>위드웍스</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>판매주문 상세 — 판매상태 확정</t>
         </is>
       </c>
     </row>

--- a/테스트/테스트3차/5회/김태오/테스트시나리오_김태오.xlsx
+++ b/테스트/테스트3차/5회/김태오/테스트시나리오_김태오.xlsx
@@ -432,10 +432,10 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1780,10 +1780,10 @@
           <t>사업부: IC (카테터) / 성별: 남 / 환자구분: SB-N
 연락 상태: 정상 / 연락 선호: 업무폰2586 문자
 전화번호1: 관리자·010-5799-0084 (선택)
-전화번호2: 010-8716-0133
+전화번호2: 정희경·010-8716-0133
 Email: test-kto@example.com / Fax: 02-0000-0000
 주소: 04524 서울특별시 중구 세종대로 110 / 테스트용 주소(3차 5회 김태오)
-송금자명: 김태오 / 현금영수증: 소득공제·010-5799-0084
+송금자명: 김태오 / 현금영수증: 소득공제·관리자·010-5799-0084
 건보등록: 신규 등록 완료 · 2026-09-07</t>
         </is>
       </c>
@@ -1862,7 +1862,7 @@
           <t>처방전: 김태오_처방전.jpg (1건)
 신분증: 김태오_신분증_TEST.jpg (1건)
 등록신청서: 김태오_자가도뇨소모성재료_등록신청서_TEST.jpg (1건)
-결과지: 김태오_결과지_01~08_TEST.jpg (8건)</t>
+결과지: 김태오_결과지_01~8_TEST.jpg (8건)</t>
         </is>
       </c>
       <c r="J7" s="23" t="inlineStr">
@@ -1983,8 +1983,8 @@
       <c r="I9" s="39" t="inlineStr">
         <is>
           <t>주민등록번호: 850203-1000001
-전화번호1: 관리자 · 01057990084 (선택)
-전화번호2: 정희경 · 01087160133 (선택)
+전화번호1: 관리자·010-5799-0084 (선택)
+전화번호2: 정희경·010-8716-0133 (선택)
 송금자명: 김태오</t>
         </is>
       </c>
@@ -3285,7 +3285,8 @@
         <is>
           <t>① 창고 판매주문 S2609070004 채번
 ② 출고창고 「3PL Main 판매창고」 즉시 표시
-③ 판매현황 항목 16건이 즉시 채워짐</t>
+③ 판매현황 항목 16건이 즉시 채워짐
+④ 접수 안내·결제 안내 SMS 2건 발송</t>
         </is>
       </c>
       <c r="M29" s="43" t="inlineStr">
@@ -3434,8 +3435,7 @@
       </c>
       <c r="L31" s="42" t="inlineStr">
         <is>
-          <t>[본인부담 있음] 「링크페이으로 81,000원 입금 확인했습니다」
-[본인부담 0원] 「본인부담금이 없는 건입니다 — 주문을 확정했습니다」
+          <t>「링크페이으로 81,000원 입금 확인했습니다」
 공통: ① 세금계산서 TI20260907000243 발행 ② 거래명세서 PDF 생성 ③ 위드웍스 S2609070004 확정 ④ 현금영수증은 「청구전략에 없음」으로 제외</t>
         </is>
       </c>
@@ -3855,7 +3855,7 @@
       </c>
       <c r="B2" s="52" t="inlineStr">
         <is>
-          <t>TC-005</t>
+          <t>TC-006</t>
         </is>
       </c>
       <c r="C2" s="53" t="inlineStr">
@@ -3865,32 +3865,32 @@
       </c>
       <c r="D2" s="52" t="inlineStr">
         <is>
-          <t>데이터</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="E2" s="15" t="inlineStr">
         <is>
-          <t>5회 테스트 자료의 가상 병원 8곳이 병원 마스터에 미등록</t>
+          <t>hospitalCreate() 를 콘솔에서 인자 없이 호출 시 오류</t>
         </is>
       </c>
       <c r="F2" s="15" t="inlineStr">
         <is>
-          <t>병원 조회에서 「서울가온」 검색</t>
+          <t>개발자도구에서 hospitalCreate() 직접 호출</t>
         </is>
       </c>
       <c r="G2" s="15" t="inlineStr">
         <is>
-          <t>조회 결과 표시</t>
+          <t>정상 등록</t>
         </is>
       </c>
       <c r="H2" s="15" t="inlineStr">
         <is>
-          <t>조회 결과 0건</t>
+          <t>Cannot set properties of undefined (setting disabled)</t>
         </is>
       </c>
       <c r="I2" s="15" t="inlineStr">
         <is>
-          <t>화면의 [새 병원 등록]으로 등록 후 진행 (TC-005). 시스템 결함 아님 — 8명 모두 동일 절차 필요</t>
+          <t>해당 함수는 클릭된 버튼 객체를 인자로 받아 비활성화 처리함. 화면 버튼을 직접 클릭해야 함. 실사용에는 영향 없음</t>
         </is>
       </c>
       <c r="J2" s="52" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B3" s="55" t="inlineStr">
         <is>
-          <t>TC-006</t>
+          <t>TC-005</t>
         </is>
       </c>
       <c r="C3" s="56" t="inlineStr">
@@ -3932,32 +3932,32 @@
       </c>
       <c r="D3" s="55" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>데이터</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>hospitalCreate() 를 콘솔에서 인자 없이 호출 시 오류</t>
+          <t>5회 테스트 자료의 가상 병원 8곳이 병원 마스터에 미등록</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>개발자도구에서 hospitalCreate() 직접 호출</t>
+          <t>병원 조회에서 「서울가온」 검색</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>정상 등록</t>
+          <t>조회 결과 표시</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>Cannot set properties of undefined (setting disabled)</t>
+          <t>조회 결과 0건</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>해당 함수는 클릭된 버튼 객체를 인자로 받아 비활성화 처리함. 화면 버튼을 직접 클릭해야 함. 실사용에는 영향 없음</t>
+          <t>화면의 [새 병원 등록]으로 등록 후 진행 (TC-006). 시스템 결함 아님 — 8명 모두 동일 절차 필요</t>
         </is>
       </c>
       <c r="J3" s="55" t="inlineStr">
@@ -4202,7 +4202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4212,7 +4212,7 @@
     <col width="56" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
           <t>No</t>
@@ -4245,12 +4245,12 @@
       </c>
       <c r="B2" s="15" t="inlineStr">
         <is>
-          <t>00_테스트설정.png</t>
+          <t>01_거래처관리-목록.png</t>
         </is>
       </c>
       <c r="C2" s="52" t="inlineStr">
         <is>
-          <t>사전</t>
+          <t>TC-002</t>
         </is>
       </c>
       <c r="D2" s="53" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="E2" s="15" t="inlineStr">
         <is>
-          <t>설정 › 서비스 연동 설정 › 테스트 설정 (_계획 폴더)</t>
+          <t>거래처 관리 목록 — 신규 등록 진입</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>01_거래처관리-목록.png</t>
+          <t>02_거래처등록-창.png</t>
         </is>
       </c>
       <c r="C3" s="55" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>거래처 조회 팝업 › [신규] 등록</t>
+          <t>거래처 등록 창 초기 상태</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>02_거래처등록-창.png</t>
+          <t>03_거래처등록-채움.png</t>
         </is>
       </c>
       <c r="C4" s="52" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>거래처 등록 창 — 주민번호 입력 직후 생년월일 자동 계산</t>
+          <t>거래처 정보 입력 완료</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>03_거래처등록-채움.png</t>
+          <t>04_거래처상세.png</t>
         </is>
       </c>
       <c r="C5" s="55" t="inlineStr">
@@ -4328,14 +4328,14 @@
           <t>TC-002</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>팝업</t>
+      <c r="D5" s="56" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>거래처 등록 창 — 전 항목 입력 완료</t>
+          <t>거래처 #178 상세 — 생년월일 자동 입력 확인</t>
         </is>
       </c>
     </row>
@@ -4345,12 +4345,12 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>04_거래처상세.png</t>
+          <t>05_처방자료업로드-빈화면.png</t>
         </is>
       </c>
       <c r="C6" s="52" t="inlineStr">
         <is>
-          <t>TC-002</t>
+          <t>TC-001</t>
         </is>
       </c>
       <c r="D6" s="53" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>거래처 상세 — (E) 접두 부여 확인</t>
+          <t>처방자료 업로드 초기 화면</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>05_처방자료업로드-빈화면.png</t>
+          <t>06_처방자료업로드-11건.png</t>
         </is>
       </c>
       <c r="C7" s="55" t="inlineStr">
         <is>
-          <t>TC-001</t>
+          <t>TC-003</t>
         </is>
       </c>
       <c r="D7" s="56" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>처방자료 업로드 초기 화면</t>
+          <t>서류 11건 업로드 및 유형 지정 완료</t>
         </is>
       </c>
     </row>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>06_처방자료업로드-11건.png</t>
+          <t>07_주문등록-열림.png</t>
         </is>
       </c>
       <c r="C8" s="52" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>서류 11건 유형별 배치 완료</t>
+          <t>RX-20260907-005 주문 등록 화면</t>
         </is>
       </c>
     </row>
@@ -4420,12 +4420,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>07_주문등록-열림.png</t>
+          <t>08_상세목록-상담환자정보.png</t>
         </is>
       </c>
       <c r="C9" s="55" t="inlineStr">
         <is>
-          <t>TC-003</t>
+          <t>TC-004</t>
         </is>
       </c>
       <c r="D9" s="56" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>등록 후 새 탭으로 열린 주문 등록 화면</t>
+          <t>상세 목록 › 상담ㆍ환자 정보</t>
         </is>
       </c>
     </row>
@@ -4445,22 +4445,22 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>08_상세목록-상담환자정보.png</t>
+          <t>09_병원조회-팝업.png</t>
         </is>
       </c>
       <c r="C10" s="52" t="inlineStr">
         <is>
-          <t>TC-004</t>
-        </is>
-      </c>
-      <c r="D10" s="53" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+          <t>TC-005</t>
+        </is>
+      </c>
+      <c r="D10" s="57" t="inlineStr">
+        <is>
+          <t>팝업</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>상세 목록 › 상담ㆍ환자 정보</t>
+          <t>병원 조회 — 마스터 미등록 확인</t>
         </is>
       </c>
     </row>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>09_병원조회-팝업.png</t>
+          <t>10_새병원등록-팝업.png</t>
         </is>
       </c>
       <c r="C11" s="55" t="inlineStr">
         <is>
-          <t>TC-005</t>
+          <t>TC-006</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>병원 조회 — 검색 결과 0건</t>
+          <t>새 병원 등록 폼 열림</t>
         </is>
       </c>
     </row>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>10_새병원등록-팝업.png</t>
+          <t>11_새병원등록-채움.png</t>
         </is>
       </c>
       <c r="C12" s="52" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>새 병원 등록 입력 영역</t>
+          <t>새 병원 정보 입력 완료</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>11_새병원등록-채움.png</t>
+          <t>12_병원채워짐.png</t>
         </is>
       </c>
       <c r="C13" s="55" t="inlineStr">
@@ -4528,14 +4528,14 @@
           <t>TC-006</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>팝업</t>
+      <c r="D13" s="56" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>새 병원 등록 — 입력 완료</t>
+          <t>병원명·요양병원 코드 자동 입력</t>
         </is>
       </c>
     </row>
@@ -4545,12 +4545,12 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>12_병원채워짐.png</t>
+          <t>13_상세목록-병원처방정보.png</t>
         </is>
       </c>
       <c r="C14" s="52" t="inlineStr">
         <is>
-          <t>TC-006</t>
+          <t>TC-007</t>
         </is>
       </c>
       <c r="D14" s="53" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>병원명·요양병원 코드 자동 입력 결과</t>
+          <t>상세 목록 › 병원ㆍ처방 정보 입력 완료</t>
         </is>
       </c>
     </row>
@@ -4570,22 +4570,22 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>13_상세목록-병원처방정보.png</t>
+          <t>14_청구처찾기-팝업.png</t>
         </is>
       </c>
       <c r="C15" s="55" t="inlineStr">
         <is>
-          <t>TC-007</t>
-        </is>
-      </c>
-      <c r="D15" s="56" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+          <t>TC-008</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>팝업</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>상세 목록 › 병원ㆍ처방 정보 전 항목</t>
+          <t>관할 청구처 찾기</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>14_청구처찾기-팝업.png</t>
+          <t>15_청구처찾기-후보.png</t>
         </is>
       </c>
       <c r="C16" s="52" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>관할 청구처 찾기</t>
+          <t>배송지 기준 후보 목록</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>15_청구처찾기-후보.png</t>
+          <t>16_상세목록-저장.png</t>
         </is>
       </c>
       <c r="C17" s="55" t="inlineStr">
@@ -4628,14 +4628,14 @@
           <t>TC-008</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>팝업</t>
+      <c r="D17" s="56" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>청구처 조회 결과 — 공단 중구지사</t>
+          <t>상세 목록 저장 완료</t>
         </is>
       </c>
     </row>
@@ -4645,12 +4645,12 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>16_상세목록-저장.png</t>
+          <t>17_검수요청.png</t>
         </is>
       </c>
       <c r="C18" s="52" t="inlineStr">
         <is>
-          <t>TC-008</t>
+          <t>TC-009</t>
         </is>
       </c>
       <c r="D18" s="53" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>상세 목록 저장 완료</t>
+          <t>검수 요청 완료 — 승인자 알림 발송</t>
         </is>
       </c>
     </row>
@@ -4670,22 +4670,22 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>17_검수요청.png</t>
+          <t>18_검수승인-팝업.png</t>
         </is>
       </c>
       <c r="C19" s="55" t="inlineStr">
         <is>
-          <t>TC-009</t>
-        </is>
-      </c>
-      <c r="D19" s="56" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+          <t>TC-010</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>팝업</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>검수 요청 완료 — 상태 변경</t>
+          <t>검수 승인 확인 창</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>18_검수승인-팝업.png</t>
+          <t>19_검수완료.png</t>
         </is>
       </c>
       <c r="C20" s="52" t="inlineStr">
@@ -4703,14 +4703,14 @@
           <t>TC-010</t>
         </is>
       </c>
-      <c r="D20" s="57" t="inlineStr">
-        <is>
-          <t>팝업</t>
+      <c r="D20" s="53" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
         </is>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>검수 승인 — 메모 입력</t>
+          <t>검수 완료 상태</t>
         </is>
       </c>
     </row>
@@ -4720,22 +4720,22 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>19_검수완료.png</t>
+          <t>20_위임동의-발송창.png</t>
         </is>
       </c>
       <c r="C21" s="55" t="inlineStr">
         <is>
-          <t>TC-010</t>
-        </is>
-      </c>
-      <c r="D21" s="56" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+          <t>TC-011</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>팝오버</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>검수 완료 상태</t>
+          <t>위임동의 SMS 발송 창 — 수신번호·미리보기</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>20_위임동의-발송창.png</t>
+          <t>21_위임동의-발송결과.png</t>
         </is>
       </c>
       <c r="C22" s="52" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>위임동의 SMS 발송 창 — 수신번호·미리보기</t>
+          <t>위임동의 발송 결과</t>
         </is>
       </c>
     </row>
@@ -4770,22 +4770,22 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>21_위임동의-발송결과.png</t>
+          <t>22_서명화면.png</t>
         </is>
       </c>
       <c r="C23" s="55" t="inlineStr">
         <is>
-          <t>TC-011</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>팝오버</t>
+          <t>TC-012</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>공개화면</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>위임동의 발송 결과</t>
+          <t>위임동의 서명 페이지 (비로그인)</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>22_서명화면.png</t>
+          <t>22b_서명함.png</t>
         </is>
       </c>
       <c r="C24" s="52" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>위임동의 서명 페이지 (비로그인)</t>
+          <t>서명 입력 완료</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>22b_서명함.png</t>
+          <t>23_개인정보동의.png</t>
         </is>
       </c>
       <c r="C25" s="55" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>서명 입력 완료</t>
+          <t>개인정보 수집·이용 동의 선택</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>23_개인정보동의.png</t>
+          <t>24_본인확인.png</t>
         </is>
       </c>
       <c r="C26" s="52" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>개인정보 수집·이용 동의 선택</t>
+          <t>NICE 본인확인 — 확인됨(테스트)</t>
         </is>
       </c>
     </row>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>24_본인확인.png</t>
+          <t>25_동의완료.png</t>
         </is>
       </c>
       <c r="C27" s="55" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>NICE 본인확인 — 확인됨(테스트)</t>
+          <t>동의 완료 화면</t>
         </is>
       </c>
     </row>
@@ -4895,22 +4895,22 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>25_동의완료.png</t>
+          <t>35_팩스발송-창.png</t>
         </is>
       </c>
       <c r="C28" s="52" t="inlineStr">
         <is>
-          <t>TC-012</t>
-        </is>
-      </c>
-      <c r="D28" s="58" t="inlineStr">
-        <is>
-          <t>공개화면</t>
+          <t>TC-013a</t>
+        </is>
+      </c>
+      <c r="D28" s="57" t="inlineStr">
+        <is>
+          <t>팝오버</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>동의 완료 화면</t>
+          <t>공단 신규/재등록 서류 팩스 — 수신처·전송 서류</t>
         </is>
       </c>
     </row>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>35_팩스발송-창.png</t>
+          <t>36_팩스발송-결과.png</t>
         </is>
       </c>
       <c r="C29" s="55" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>공단 신규/재등록 서류 팩스 — 수신처·전송 서류</t>
+          <t>공단 신규/재등록 서류 팩스 — 발송 결과</t>
         </is>
       </c>
     </row>
@@ -4945,22 +4945,22 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>36_팩스발송-결과.png</t>
+          <t>26_주문제품-빈줄.png</t>
         </is>
       </c>
       <c r="C30" s="52" t="inlineStr">
         <is>
-          <t>TC-013a</t>
-        </is>
-      </c>
-      <c r="D30" s="57" t="inlineStr">
-        <is>
-          <t>팝오버</t>
+          <t>TC-014</t>
+        </is>
+      </c>
+      <c r="D30" s="53" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>공단 신규/재등록 서류 팩스 — 발송 결과</t>
+          <t>주문 제품 탭 초기 상태</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>26_주문제품-빈줄.png</t>
+          <t>27_제품조회-팝업.png</t>
         </is>
       </c>
       <c r="C31" s="55" t="inlineStr">
@@ -4978,14 +4978,14 @@
           <t>TC-014</t>
         </is>
       </c>
-      <c r="D31" s="56" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>팝업</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>주문 제품 탭 초기 상태</t>
+          <t>제품 조회 — CH14 Male</t>
         </is>
       </c>
     </row>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>27_제품조회-팝업.png</t>
+          <t>28_주문제품-채움.png</t>
         </is>
       </c>
       <c r="C32" s="52" t="inlineStr">
@@ -5003,14 +5003,14 @@
           <t>TC-014</t>
         </is>
       </c>
-      <c r="D32" s="57" t="inlineStr">
-        <is>
-          <t>팝업</t>
+      <c r="D32" s="53" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>제품 조회 — CH14 Male</t>
+          <t>제품 선택 후 금액 자동 배분</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>28_주문제품-채움.png</t>
+          <t>29_주문제품-저장.png</t>
         </is>
       </c>
       <c r="C33" s="55" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>제품 선택 후 금액 자동 배분</t>
+          <t>주문 제품 저장 완료</t>
         </is>
       </c>
     </row>
@@ -5045,12 +5045,12 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>29_주문제품-저장.png</t>
+          <t>30_주문생성및연계.png</t>
         </is>
       </c>
       <c r="C34" s="52" t="inlineStr">
         <is>
-          <t>TC-014</t>
+          <t>TC-015</t>
         </is>
       </c>
       <c r="D34" s="53" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>주문 제품 저장 완료</t>
+          <t>주문 생성 및 위드웍스 연계 결과</t>
         </is>
       </c>
     </row>
@@ -5070,22 +5070,22 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>30_주문생성및연계.png</t>
+          <t>31_ww_판매주문-화면.png</t>
         </is>
       </c>
       <c r="C35" s="55" t="inlineStr">
         <is>
-          <t>TC-015</t>
-        </is>
-      </c>
-      <c r="D35" s="56" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+          <t>TC-016</t>
+        </is>
+      </c>
+      <c r="D35" s="59" t="inlineStr">
+        <is>
+          <t>위드웍스</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>주문 생성 및 위드웍스 연계 결과</t>
+          <t>판매 주문 조회 화면</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>31_ww_판매주문-화면.png</t>
+          <t>32_ww_판매주문-조회결과.png</t>
         </is>
       </c>
       <c r="C36" s="52" t="inlineStr">
@@ -5103,14 +5103,14 @@
           <t>TC-016</t>
         </is>
       </c>
-      <c r="D36" s="59" t="inlineStr">
+      <c r="D36" s="60" t="inlineStr">
         <is>
           <t>위드웍스</t>
         </is>
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>판매 주문 조회 화면</t>
+          <t>판매주문 S2609070004 조회 결과</t>
         </is>
       </c>
     </row>
@@ -5120,22 +5120,22 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>32_ww_판매주문-조회결과.png</t>
+          <t>33_정산회계-목록.png</t>
         </is>
       </c>
       <c r="C37" s="55" t="inlineStr">
         <is>
-          <t>TC-016</t>
-        </is>
-      </c>
-      <c r="D37" s="60" t="inlineStr">
-        <is>
-          <t>위드웍스</t>
+          <t>TC-017</t>
+        </is>
+      </c>
+      <c r="D37" s="56" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>판매주문 S2609070004 조회 결과</t>
+          <t>정산/회계 목록</t>
         </is>
       </c>
     </row>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>33_정산회계-목록.png</t>
+          <t>34_입금확인-뒤.png</t>
         </is>
       </c>
       <c r="C38" s="52" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t>정산/회계 목록</t>
+          <t>주문 확정 / 입금 확인 후 상태</t>
         </is>
       </c>
     </row>
@@ -5170,45 +5170,20 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>34_입금확인-뒤.png</t>
+          <t>37_ww_판매주문-확정.png</t>
         </is>
       </c>
       <c r="C39" s="55" t="inlineStr">
         <is>
-          <t>TC-017</t>
-        </is>
-      </c>
-      <c r="D39" s="56" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+          <t>TC-018</t>
+        </is>
+      </c>
+      <c r="D39" s="59" t="inlineStr">
+        <is>
+          <t>위드웍스</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>주문 확정 / 입금 확인 후 상태</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="52" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="15" t="inlineStr">
-        <is>
-          <t>37_ww_판매주문-확정.png</t>
-        </is>
-      </c>
-      <c r="C40" s="52" t="inlineStr">
-        <is>
-          <t>TC-018</t>
-        </is>
-      </c>
-      <c r="D40" s="59" t="inlineStr">
-        <is>
-          <t>위드웍스</t>
-        </is>
-      </c>
-      <c r="E40" s="15" t="inlineStr">
         <is>
           <t>판매주문 상세 — 판매상태 확정</t>
         </is>

--- a/테스트/테스트3차/5회/김태오/테스트시나리오_김태오.xlsx
+++ b/테스트/테스트3차/5회/김태오/테스트시나리오_김태오.xlsx
@@ -432,10 +432,10 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1783,7 +1783,7 @@
 전화번호2: 정희경·010-8716-0133
 Email: test-kto@example.com / Fax: 02-0000-0000
 주소: 04524 서울특별시 중구 세종대로 110 / 테스트용 주소(3차 5회 김태오)
-송금자명: 김태오 / 현금영수증: 소득공제·관리자·010-5799-0084
+송금자명: 김태오 / 현금영수증: 소득공제·010-5799-0084
 건보등록: 신규 등록 완료 · 2026-09-07</t>
         </is>
       </c>
@@ -1862,7 +1862,7 @@
           <t>처방전: 김태오_처방전.jpg (1건)
 신분증: 김태오_신분증_TEST.jpg (1건)
 등록신청서: 김태오_자가도뇨소모성재료_등록신청서_TEST.jpg (1건)
-결과지: 김태오_결과지_01~8_TEST.jpg (8건)</t>
+결과지: 김태오_결과지_01~08_TEST.jpg (8건)</t>
         </is>
       </c>
       <c r="J7" s="23" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="B2" s="52" t="inlineStr">
         <is>
-          <t>TC-006</t>
+          <t>TC-005</t>
         </is>
       </c>
       <c r="C2" s="53" t="inlineStr">
@@ -3865,32 +3865,32 @@
       </c>
       <c r="D2" s="52" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>데이터</t>
         </is>
       </c>
       <c r="E2" s="15" t="inlineStr">
         <is>
-          <t>hospitalCreate() 를 콘솔에서 인자 없이 호출 시 오류</t>
+          <t>5회 테스트 자료의 가상 병원 8곳이 병원 마스터에 미등록</t>
         </is>
       </c>
       <c r="F2" s="15" t="inlineStr">
         <is>
-          <t>개발자도구에서 hospitalCreate() 직접 호출</t>
+          <t>병원 조회에서 「서울가온」 검색</t>
         </is>
       </c>
       <c r="G2" s="15" t="inlineStr">
         <is>
-          <t>정상 등록</t>
+          <t>조회 결과 표시</t>
         </is>
       </c>
       <c r="H2" s="15" t="inlineStr">
         <is>
-          <t>Cannot set properties of undefined (setting disabled)</t>
+          <t>조회 결과 0건</t>
         </is>
       </c>
       <c r="I2" s="15" t="inlineStr">
         <is>
-          <t>해당 함수는 클릭된 버튼 객체를 인자로 받아 비활성화 처리함. 화면 버튼을 직접 클릭해야 함. 실사용에는 영향 없음</t>
+          <t>화면의 [새 병원 등록]으로 등록 후 진행 (TC-006). 시스템 결함 아님 — 8명 모두 동일 절차 필요</t>
         </is>
       </c>
       <c r="J2" s="52" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B3" s="55" t="inlineStr">
         <is>
-          <t>TC-005</t>
+          <t>TC-006</t>
         </is>
       </c>
       <c r="C3" s="56" t="inlineStr">
@@ -3932,32 +3932,32 @@
       </c>
       <c r="D3" s="55" t="inlineStr">
         <is>
-          <t>데이터</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>5회 테스트 자료의 가상 병원 8곳이 병원 마스터에 미등록</t>
+          <t>hospitalCreate() 를 콘솔에서 인자 없이 호출 시 오류</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>병원 조회에서 「서울가온」 검색</t>
+          <t>개발자도구에서 hospitalCreate() 직접 호출</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>조회 결과 표시</t>
+          <t>정상 등록</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>조회 결과 0건</t>
+          <t>Cannot set properties of undefined (setting disabled)</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>화면의 [새 병원 등록]으로 등록 후 진행 (TC-006). 시스템 결함 아님 — 8명 모두 동일 절차 필요</t>
+          <t>해당 함수는 클릭된 버튼 객체를 인자로 받아 비활성화 처리함. 화면 버튼을 직접 클릭해야 함. 실사용에는 영향 없음</t>
         </is>
       </c>
       <c r="J3" s="55" t="inlineStr">
@@ -4202,7 +4202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4245,12 +4245,12 @@
       </c>
       <c r="B2" s="15" t="inlineStr">
         <is>
-          <t>01_거래처관리-목록.png</t>
+          <t>00_테스트설정.png</t>
         </is>
       </c>
       <c r="C2" s="52" t="inlineStr">
         <is>
-          <t>TC-002</t>
+          <t>사전</t>
         </is>
       </c>
       <c r="D2" s="53" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="E2" s="15" t="inlineStr">
         <is>
-          <t>거래처 관리 목록 — 신규 등록 진입</t>
+          <t>설정 › 서비스 연동 설정 › 테스트 설정 (_계획 폴더)</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>02_거래처등록-창.png</t>
+          <t>01_거래처관리-목록.png</t>
         </is>
       </c>
       <c r="C3" s="55" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>거래처 등록 창 초기 상태</t>
+          <t>거래처 조회 팝업 › [신규] 등록</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>03_거래처등록-채움.png</t>
+          <t>02_거래처등록-창.png</t>
         </is>
       </c>
       <c r="C4" s="52" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>거래처 정보 입력 완료</t>
+          <t>거래처 등록 창 — 주민번호 입력 직후 생년월일 자동 계산</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>04_거래처상세.png</t>
+          <t>03_거래처등록-채움.png</t>
         </is>
       </c>
       <c r="C5" s="55" t="inlineStr">
@@ -4328,14 +4328,14 @@
           <t>TC-002</t>
         </is>
       </c>
-      <c r="D5" s="56" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>팝업</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>거래처 #178 상세 — 생년월일 자동 입력 확인</t>
+          <t>거래처 등록 창 — 전 항목 입력 완료</t>
         </is>
       </c>
     </row>
@@ -4345,12 +4345,12 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>05_처방자료업로드-빈화면.png</t>
+          <t>04_거래처상세.png</t>
         </is>
       </c>
       <c r="C6" s="52" t="inlineStr">
         <is>
-          <t>TC-001</t>
+          <t>TC-002</t>
         </is>
       </c>
       <c r="D6" s="53" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>처방자료 업로드 초기 화면</t>
+          <t>거래처 상세 — (E) 접두 부여 확인</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>06_처방자료업로드-11건.png</t>
+          <t>05_처방자료업로드-빈화면.png</t>
         </is>
       </c>
       <c r="C7" s="55" t="inlineStr">
         <is>
-          <t>TC-003</t>
+          <t>TC-001</t>
         </is>
       </c>
       <c r="D7" s="56" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>서류 11건 업로드 및 유형 지정 완료</t>
+          <t>처방자료 업로드 초기 화면</t>
         </is>
       </c>
     </row>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>07_주문등록-열림.png</t>
+          <t>06_처방자료업로드-11건.png</t>
         </is>
       </c>
       <c r="C8" s="52" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>RX-20260907-005 주문 등록 화면</t>
+          <t>서류 11건 유형별 배치 완료</t>
         </is>
       </c>
     </row>
@@ -4420,12 +4420,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>08_상세목록-상담환자정보.png</t>
+          <t>07_주문등록-열림.png</t>
         </is>
       </c>
       <c r="C9" s="55" t="inlineStr">
         <is>
-          <t>TC-004</t>
+          <t>TC-003</t>
         </is>
       </c>
       <c r="D9" s="56" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>상세 목록 › 상담ㆍ환자 정보</t>
+          <t>등록 후 새 탭으로 열린 주문 등록 화면</t>
         </is>
       </c>
     </row>
@@ -4445,22 +4445,22 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>09_병원조회-팝업.png</t>
+          <t>08_상세목록-상담환자정보.png</t>
         </is>
       </c>
       <c r="C10" s="52" t="inlineStr">
         <is>
-          <t>TC-005</t>
-        </is>
-      </c>
-      <c r="D10" s="57" t="inlineStr">
-        <is>
-          <t>팝업</t>
+          <t>TC-004</t>
+        </is>
+      </c>
+      <c r="D10" s="53" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>병원 조회 — 마스터 미등록 확인</t>
+          <t>상세 목록 › 상담ㆍ환자 정보</t>
         </is>
       </c>
     </row>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>10_새병원등록-팝업.png</t>
+          <t>09_병원조회-팝업.png</t>
         </is>
       </c>
       <c r="C11" s="55" t="inlineStr">
         <is>
-          <t>TC-006</t>
+          <t>TC-005</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>새 병원 등록 폼 열림</t>
+          <t>병원 조회 — 검색 결과 0건</t>
         </is>
       </c>
     </row>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>11_새병원등록-채움.png</t>
+          <t>10_새병원등록-팝업.png</t>
         </is>
       </c>
       <c r="C12" s="52" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>새 병원 정보 입력 완료</t>
+          <t>새 병원 등록 입력 영역</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>12_병원채워짐.png</t>
+          <t>11_새병원등록-채움.png</t>
         </is>
       </c>
       <c r="C13" s="55" t="inlineStr">
@@ -4528,14 +4528,14 @@
           <t>TC-006</t>
         </is>
       </c>
-      <c r="D13" s="56" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>팝업</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>병원명·요양병원 코드 자동 입력</t>
+          <t>새 병원 등록 — 입력 완료</t>
         </is>
       </c>
     </row>
@@ -4545,12 +4545,12 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>13_상세목록-병원처방정보.png</t>
+          <t>12_병원채워짐.png</t>
         </is>
       </c>
       <c r="C14" s="52" t="inlineStr">
         <is>
-          <t>TC-007</t>
+          <t>TC-006</t>
         </is>
       </c>
       <c r="D14" s="53" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>상세 목록 › 병원ㆍ처방 정보 입력 완료</t>
+          <t>병원명·요양병원 코드 자동 입력 결과</t>
         </is>
       </c>
     </row>
@@ -4570,22 +4570,22 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>14_청구처찾기-팝업.png</t>
+          <t>13_상세목록-병원처방정보.png</t>
         </is>
       </c>
       <c r="C15" s="55" t="inlineStr">
         <is>
-          <t>TC-008</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>팝업</t>
+          <t>TC-007</t>
+        </is>
+      </c>
+      <c r="D15" s="56" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>관할 청구처 찾기</t>
+          <t>상세 목록 › 병원ㆍ처방 정보 전 항목</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>15_청구처찾기-후보.png</t>
+          <t>14_청구처찾기-팝업.png</t>
         </is>
       </c>
       <c r="C16" s="52" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>배송지 기준 후보 목록</t>
+          <t>관할 청구처 찾기</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>16_상세목록-저장.png</t>
+          <t>15_청구처찾기-후보.png</t>
         </is>
       </c>
       <c r="C17" s="55" t="inlineStr">
@@ -4628,14 +4628,14 @@
           <t>TC-008</t>
         </is>
       </c>
-      <c r="D17" s="56" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>팝업</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>상세 목록 저장 완료</t>
+          <t>청구처 조회 결과 — 공단 중구지사</t>
         </is>
       </c>
     </row>
@@ -4645,12 +4645,12 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>17_검수요청.png</t>
+          <t>16_상세목록-저장.png</t>
         </is>
       </c>
       <c r="C18" s="52" t="inlineStr">
         <is>
-          <t>TC-009</t>
+          <t>TC-008</t>
         </is>
       </c>
       <c r="D18" s="53" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>검수 요청 완료 — 승인자 알림 발송</t>
+          <t>상세 목록 저장 완료</t>
         </is>
       </c>
     </row>
@@ -4670,22 +4670,22 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>18_검수승인-팝업.png</t>
+          <t>17_검수요청.png</t>
         </is>
       </c>
       <c r="C19" s="55" t="inlineStr">
         <is>
-          <t>TC-010</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>팝업</t>
+          <t>TC-009</t>
+        </is>
+      </c>
+      <c r="D19" s="56" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>검수 승인 확인 창</t>
+          <t>검수 요청 완료 — 상태 변경</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>19_검수완료.png</t>
+          <t>18_검수승인-팝업.png</t>
         </is>
       </c>
       <c r="C20" s="52" t="inlineStr">
@@ -4703,14 +4703,14 @@
           <t>TC-010</t>
         </is>
       </c>
-      <c r="D20" s="53" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+      <c r="D20" s="57" t="inlineStr">
+        <is>
+          <t>팝업</t>
         </is>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>검수 완료 상태</t>
+          <t>검수 승인 — 메모 입력</t>
         </is>
       </c>
     </row>
@@ -4720,22 +4720,22 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>20_위임동의-발송창.png</t>
+          <t>19_검수완료.png</t>
         </is>
       </c>
       <c r="C21" s="55" t="inlineStr">
         <is>
-          <t>TC-011</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>팝오버</t>
+          <t>TC-010</t>
+        </is>
+      </c>
+      <c r="D21" s="56" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>위임동의 SMS 발송 창 — 수신번호·미리보기</t>
+          <t>검수 완료 상태</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>21_위임동의-발송결과.png</t>
+          <t>20_위임동의-발송창.png</t>
         </is>
       </c>
       <c r="C22" s="52" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>위임동의 발송 결과</t>
+          <t>위임동의 SMS 발송 창 — 수신번호·미리보기</t>
         </is>
       </c>
     </row>
@@ -4770,22 +4770,22 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>22_서명화면.png</t>
+          <t>21_위임동의-발송결과.png</t>
         </is>
       </c>
       <c r="C23" s="55" t="inlineStr">
         <is>
-          <t>TC-012</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>공개화면</t>
+          <t>TC-011</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>팝오버</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>위임동의 서명 페이지 (비로그인)</t>
+          <t>위임동의 발송 결과</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>22b_서명함.png</t>
+          <t>22_서명화면.png</t>
         </is>
       </c>
       <c r="C24" s="52" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>서명 입력 완료</t>
+          <t>위임동의 서명 페이지 (비로그인)</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>23_개인정보동의.png</t>
+          <t>22b_서명함.png</t>
         </is>
       </c>
       <c r="C25" s="55" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>개인정보 수집·이용 동의 선택</t>
+          <t>서명 입력 완료</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>24_본인확인.png</t>
+          <t>23_개인정보동의.png</t>
         </is>
       </c>
       <c r="C26" s="52" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>NICE 본인확인 — 확인됨(테스트)</t>
+          <t>개인정보 수집·이용 동의 선택</t>
         </is>
       </c>
     </row>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>25_동의완료.png</t>
+          <t>24_본인확인.png</t>
         </is>
       </c>
       <c r="C27" s="55" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>동의 완료 화면</t>
+          <t>NICE 본인확인 — 확인됨(테스트)</t>
         </is>
       </c>
     </row>
@@ -4895,22 +4895,22 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>35_팩스발송-창.png</t>
+          <t>25_동의완료.png</t>
         </is>
       </c>
       <c r="C28" s="52" t="inlineStr">
         <is>
-          <t>TC-013a</t>
-        </is>
-      </c>
-      <c r="D28" s="57" t="inlineStr">
-        <is>
-          <t>팝오버</t>
+          <t>TC-012</t>
+        </is>
+      </c>
+      <c r="D28" s="58" t="inlineStr">
+        <is>
+          <t>공개화면</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>공단 신규/재등록 서류 팩스 — 수신처·전송 서류</t>
+          <t>동의 완료 화면</t>
         </is>
       </c>
     </row>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>36_팩스발송-결과.png</t>
+          <t>35_팩스발송-창.png</t>
         </is>
       </c>
       <c r="C29" s="55" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>공단 신규/재등록 서류 팩스 — 발송 결과</t>
+          <t>공단 신규/재등록 서류 팩스 — 수신처·전송 서류</t>
         </is>
       </c>
     </row>
@@ -4945,22 +4945,22 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>26_주문제품-빈줄.png</t>
+          <t>36_팩스발송-결과.png</t>
         </is>
       </c>
       <c r="C30" s="52" t="inlineStr">
         <is>
-          <t>TC-014</t>
-        </is>
-      </c>
-      <c r="D30" s="53" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+          <t>TC-013a</t>
+        </is>
+      </c>
+      <c r="D30" s="57" t="inlineStr">
+        <is>
+          <t>팝오버</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>주문 제품 탭 초기 상태</t>
+          <t>공단 신규/재등록 서류 팩스 — 발송 결과</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>27_제품조회-팝업.png</t>
+          <t>26_주문제품-빈줄.png</t>
         </is>
       </c>
       <c r="C31" s="55" t="inlineStr">
@@ -4978,14 +4978,14 @@
           <t>TC-014</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>팝업</t>
+      <c r="D31" s="56" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>제품 조회 — CH14 Male</t>
+          <t>주문 제품 탭 초기 상태</t>
         </is>
       </c>
     </row>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>28_주문제품-채움.png</t>
+          <t>27_제품조회-팝업.png</t>
         </is>
       </c>
       <c r="C32" s="52" t="inlineStr">
@@ -5003,14 +5003,14 @@
           <t>TC-014</t>
         </is>
       </c>
-      <c r="D32" s="53" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+      <c r="D32" s="57" t="inlineStr">
+        <is>
+          <t>팝업</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>제품 선택 후 금액 자동 배분</t>
+          <t>제품 조회 — CH14 Male</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>29_주문제품-저장.png</t>
+          <t>28_주문제품-채움.png</t>
         </is>
       </c>
       <c r="C33" s="55" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>주문 제품 저장 완료</t>
+          <t>제품 선택 후 금액 자동 배분</t>
         </is>
       </c>
     </row>
@@ -5045,12 +5045,12 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>30_주문생성및연계.png</t>
+          <t>29_주문제품-저장.png</t>
         </is>
       </c>
       <c r="C34" s="52" t="inlineStr">
         <is>
-          <t>TC-015</t>
+          <t>TC-014</t>
         </is>
       </c>
       <c r="D34" s="53" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>주문 생성 및 위드웍스 연계 결과</t>
+          <t>주문 제품 저장 완료</t>
         </is>
       </c>
     </row>
@@ -5070,22 +5070,22 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>31_ww_판매주문-화면.png</t>
+          <t>30_주문생성및연계.png</t>
         </is>
       </c>
       <c r="C35" s="55" t="inlineStr">
         <is>
-          <t>TC-016</t>
-        </is>
-      </c>
-      <c r="D35" s="59" t="inlineStr">
-        <is>
-          <t>위드웍스</t>
+          <t>TC-015</t>
+        </is>
+      </c>
+      <c r="D35" s="56" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>판매 주문 조회 화면</t>
+          <t>주문 생성 및 위드웍스 연계 결과</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>32_ww_판매주문-조회결과.png</t>
+          <t>31_ww_판매주문-화면.png</t>
         </is>
       </c>
       <c r="C36" s="52" t="inlineStr">
@@ -5103,14 +5103,14 @@
           <t>TC-016</t>
         </is>
       </c>
-      <c r="D36" s="60" t="inlineStr">
+      <c r="D36" s="59" t="inlineStr">
         <is>
           <t>위드웍스</t>
         </is>
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>판매주문 S2609070004 조회 결과</t>
+          <t>판매 주문 조회 화면</t>
         </is>
       </c>
     </row>
@@ -5120,22 +5120,22 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>33_정산회계-목록.png</t>
+          <t>32_ww_판매주문-조회결과.png</t>
         </is>
       </c>
       <c r="C37" s="55" t="inlineStr">
         <is>
-          <t>TC-017</t>
-        </is>
-      </c>
-      <c r="D37" s="56" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+          <t>TC-016</t>
+        </is>
+      </c>
+      <c r="D37" s="60" t="inlineStr">
+        <is>
+          <t>위드웍스</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>정산/회계 목록</t>
+          <t>판매주문 S2609070004 조회 결과</t>
         </is>
       </c>
     </row>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>34_입금확인-뒤.png</t>
+          <t>33_정산회계-목록.png</t>
         </is>
       </c>
       <c r="C38" s="52" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t>주문 확정 / 입금 확인 후 상태</t>
+          <t>정산/회계 목록</t>
         </is>
       </c>
     </row>
@@ -5170,20 +5170,45 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
+          <t>34_입금확인-뒤.png</t>
+        </is>
+      </c>
+      <c r="C39" s="55" t="inlineStr">
+        <is>
+          <t>TC-017</t>
+        </is>
+      </c>
+      <c r="D39" s="56" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>주문 확정 / 입금 확인 후 상태</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="52" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
           <t>37_ww_판매주문-확정.png</t>
         </is>
       </c>
-      <c r="C39" s="55" t="inlineStr">
+      <c r="C40" s="52" t="inlineStr">
         <is>
           <t>TC-018</t>
         </is>
       </c>
-      <c r="D39" s="59" t="inlineStr">
+      <c r="D40" s="59" t="inlineStr">
         <is>
           <t>위드웍스</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E40" s="15" t="inlineStr">
         <is>
           <t>판매주문 상세 — 판매상태 확정</t>
         </is>

--- a/테스트/테스트3차/5회/김태오/테스트시나리오_김태오.xlsx
+++ b/테스트/테스트3차/5회/김태오/테스트시나리오_김태오.xlsx
@@ -4270,22 +4270,22 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>01_거래처관리-목록.png</t>
+          <t>05_처방자료업로드-빈화면.png</t>
         </is>
       </c>
       <c r="C3" s="55" t="inlineStr">
         <is>
-          <t>TC-002</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>팝업</t>
+          <t>TC-001</t>
+        </is>
+      </c>
+      <c r="D3" s="56" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>거래처 조회 팝업 › [신규] 등록</t>
+          <t>처방자료 업로드 초기 화면</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>02_거래처등록-창.png</t>
+          <t>01_거래처관리-목록.png</t>
         </is>
       </c>
       <c r="C4" s="52" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>거래처 등록 창 — 주민번호 입력 직후 생년월일 자동 계산</t>
+          <t>거래처 조회 팝업 › [신규] 등록</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>03_거래처등록-채움.png</t>
+          <t>02_거래처등록-창.png</t>
         </is>
       </c>
       <c r="C5" s="55" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>거래처 등록 창 — 전 항목 입력 완료</t>
+          <t>거래처 등록 창 — 주민번호 입력 직후 생년월일 자동 계산</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>04_거래처상세.png</t>
+          <t>03_거래처등록-채움.png</t>
         </is>
       </c>
       <c r="C6" s="52" t="inlineStr">
@@ -4353,14 +4353,14 @@
           <t>TC-002</t>
         </is>
       </c>
-      <c r="D6" s="53" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+      <c r="D6" s="57" t="inlineStr">
+        <is>
+          <t>팝업</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>거래처 상세 — (E) 접두 부여 확인</t>
+          <t>거래처 등록 창 — 전 항목 입력 완료</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>05_처방자료업로드-빈화면.png</t>
+          <t>04_거래처상세.png</t>
         </is>
       </c>
       <c r="C7" s="55" t="inlineStr">
         <is>
-          <t>TC-001</t>
+          <t>TC-002</t>
         </is>
       </c>
       <c r="D7" s="56" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>처방자료 업로드 초기 화면</t>
+          <t>거래처 상세 — (E) 접두 부여 확인</t>
         </is>
       </c>
     </row>

--- a/테스트/테스트3차/5회/김태오/테스트시나리오_김태오.xlsx
+++ b/테스트/테스트3차/5회/김태오/테스트시나리오_김태오.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'환경설정'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'테스트시나리오'!$A$2:$S$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'테스트시나리오'!$A$2:$S$36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'테스트시나리오'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'결함관리'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'캡처목록'!$1:$1</definedName>
@@ -834,7 +834,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CASE-01   |   End-to-End 통합 테스트   |   TC-001 ~ TC-020</t>
+          <t>CASE-01   |   End-to-End 통합 테스트   |   TC-001 ~ TC-021</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>21건 (TC-001 ~ TC-020, TC-013a 포함)</t>
+          <t>22건 (TC-001 ~ TC-021, TC-013a 포함)</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:S36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C33" s="38" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>청구</t>
         </is>
       </c>
       <c r="D33" s="39" t="inlineStr">
         <is>
-          <t>최종 상태 검증</t>
+          <t>지자체 청구 — 등기 발송</t>
         </is>
       </c>
       <c r="E33" s="39" t="inlineStr">
         <is>
-          <t>TC-001 ~ TC-018 완료</t>
+          <t>TC-017 완료 · 청구처 = 지자체(시군구청)인 건만 해당</t>
         </is>
       </c>
       <c r="F33" s="39" t="inlineStr">
         <is>
-          <t>주문ㆍ재구매 › 주문 관리 / Finance</t>
+          <t>청구ㆍ회계 › 청구 관리</t>
         </is>
       </c>
       <c r="G33" s="40" t="n">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="H33" s="39" t="inlineStr">
         <is>
-          <t>주문·창고·증빙 상태를 최종 확인한다</t>
+          <t>해당 건의 청구처ㆍ관할이 바르게 서는지 확인한다</t>
         </is>
       </c>
       <c r="I33" s="39" t="inlineStr">
@@ -3580,16 +3580,14 @@
       </c>
       <c r="K33" s="41" t="inlineStr">
         <is>
-          <t>전 구간 처리 결과 확인</t>
+          <t>청구처는 자격이 정한다 — 기초(의료급여)는 지자체, 일반·차상위경감은 공단이다. 그 아래 줄에 어디로 보내는지(공단은 지사·부서, 지자체는 시군구)가 함께 서야 한다. 서지 않으면 건마다 다시 찾아야 한다.</t>
         </is>
       </c>
       <c r="L33" s="42" t="inlineStr">
         <is>
-          <t>① 처방전 RX-20260907-005 = 검수 완료
-② 주문 EUD202609071734141 = confirmed
-③ 창고 S2609070004 = 확정
-④ 세금계산서 TI20260907000243 발행
-⑤ 공단 등록 서류 팩스 발송 완료</t>
+          <t>① 청구처 = 지자체(시군구청)
+② 관할 = 상세 목록에서 지정한 시군구 (예: 서울특별시 중구)
+[공단 건] 청구처 = 건강보험공단 · 관할 = 지사ㆍ부서명</t>
         </is>
       </c>
       <c r="M33" s="43" t="inlineStr">
@@ -3605,81 +3603,209 @@
       <c r="S33" s="28" t="inlineStr"/>
     </row>
     <row r="34" ht="82" customHeight="1">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="30" t="n"/>
+      <c r="B34" s="30" t="n"/>
+      <c r="C34" s="30" t="n"/>
+      <c r="D34" s="30" t="n"/>
+      <c r="E34" s="30" t="n"/>
+      <c r="F34" s="30" t="n"/>
+      <c r="G34" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="15" t="inlineStr">
+        <is>
+          <t>등기로 부친 것을 적는다</t>
+        </is>
+      </c>
+      <c r="I34" s="15" t="inlineStr">
+        <is>
+          <t>발송일: 2026-09-07
+등기번호: (우체국 등기번호)
+발송 영수증: (스캔 파일)
+메모: 보낸 곳·담은 서류</t>
+        </is>
+      </c>
+      <c r="J34" s="15" t="inlineStr">
+        <is>
+          <t>［등기 발송］ → ［저장］</t>
+        </is>
+      </c>
+      <c r="K34" s="45" t="inlineStr">
+        <is>
+          <t>POST /nhis/assist/claim/{order}/local-dispatch — 등기로 부친 자취를 LocalClaimDispatch 에 남긴다. 공단은 사이트에 옮겨 적고 지자체는 등기로 부치므로 단추도 서식도 다르다.
+※ 이 걸음은 지자체 건에만 있다. 공단 건은 [청구] 단추로 사이트 입력을 마친 뒤 「청구함」을 남긴다.</t>
+        </is>
+      </c>
+      <c r="L34" s="46" t="inlineStr">
+        <is>
+          <t>① 청구상태 = 청구 완료 · 청구일시 기록
+② 단추가 [등기 발송] 에서 [등기 영수증] 으로 바뀜
+③ 등기번호·영수증을 다시 꺼내 볼 수 있다</t>
+        </is>
+      </c>
+      <c r="M34" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="34" t="inlineStr"/>
+      <c r="O34" s="35" t="inlineStr"/>
+      <c r="P34" s="35" t="inlineStr"/>
+      <c r="Q34" s="35" t="inlineStr"/>
+      <c r="R34" s="35" t="inlineStr"/>
+      <c r="S34" s="34" t="inlineStr"/>
+    </row>
+    <row r="35" ht="82" customHeight="1">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>TC-020</t>
         </is>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>CASE-01 처방전·일반(10/90)·링크페이</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>검증</t>
         </is>
       </c>
-      <c r="D34" s="23" t="inlineStr">
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>최종 상태 검증</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
+        <is>
+          <t>TC-001 ~ TC-019 완료</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>주문ㆍ재구매 › 주문 관리 / Finance</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="23" t="inlineStr">
+        <is>
+          <t>주문·창고·증빙 상태를 최종 확인한다</t>
+        </is>
+      </c>
+      <c r="I35" s="23" t="inlineStr">
+        <is>
+          <t>(입력 없음)</t>
+        </is>
+      </c>
+      <c r="J35" s="23" t="inlineStr">
+        <is>
+          <t>목록 조회</t>
+        </is>
+      </c>
+      <c r="K35" s="25" t="inlineStr">
+        <is>
+          <t>전 구간 처리 결과 확인</t>
+        </is>
+      </c>
+      <c r="L35" s="26" t="inlineStr">
+        <is>
+          <t>① 처방전 RX-20260907-005 = 검수 완료
+② 주문 EUD202609071734141 = confirmed
+③ 창고 S2609070004 = 확정
+④ 세금계산서 TI20260907000243 발행
+⑤ 공단 등록 서류 팩스 발송 완료</t>
+        </is>
+      </c>
+      <c r="M35" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="28" t="inlineStr"/>
+      <c r="O35" s="29" t="inlineStr"/>
+      <c r="P35" s="29" t="inlineStr"/>
+      <c r="Q35" s="29" t="inlineStr"/>
+      <c r="R35" s="29" t="inlineStr"/>
+      <c r="S35" s="28" t="inlineStr"/>
+    </row>
+    <row r="36" ht="82" customHeight="1">
+      <c r="A36" s="36" t="inlineStr">
+        <is>
+          <t>TC-021</t>
+        </is>
+      </c>
+      <c r="B36" s="37" t="inlineStr">
+        <is>
+          <t>CASE-01 처방전·일반(10/90)·링크페이</t>
+        </is>
+      </c>
+      <c r="C36" s="38" t="inlineStr">
+        <is>
+          <t>검증</t>
+        </is>
+      </c>
+      <c r="D36" s="39" t="inlineStr">
         <is>
           <t>목록 항목 검증 (판매현황 연계)</t>
         </is>
       </c>
-      <c r="E34" s="23" t="inlineStr">
+      <c r="E36" s="39" t="inlineStr">
         <is>
           <t>TC-015 완료</t>
         </is>
       </c>
-      <c r="F34" s="23" t="inlineStr">
+      <c r="F36" s="39" t="inlineStr">
         <is>
           <t>Finance / 주문 관리</t>
         </is>
       </c>
-      <c r="G34" s="24" t="n">
+      <c r="G36" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="23" t="inlineStr">
+      <c r="H36" s="39" t="inlineStr">
         <is>
           <t>Finance 목록에서 위드웍스 판매현황 항목이 표시되는지 확인한다</t>
         </is>
       </c>
-      <c r="I34" s="23" t="inlineStr">
+      <c r="I36" s="39" t="inlineStr">
         <is>
           <t>조회 기간: 2026-09-01 ~ 2026-09-30</t>
         </is>
       </c>
-      <c r="J34" s="23" t="inlineStr">
+      <c r="J36" s="39" t="inlineStr">
         <is>
           <t>［검색］</t>
         </is>
       </c>
-      <c r="K34" s="25" t="inlineStr">
+      <c r="K36" s="41" t="inlineStr">
         <is>
           <t>ceWwCols() — Finance·주문 관리·입금 내역·현금영수증·청구 관리·교환/반품/취소 6개 화면이 동일한 위드웍스 판매현황 항목 순서를 공유한다</t>
         </is>
       </c>
-      <c r="L34" s="26" t="inlineStr">
+      <c r="L36" s="42" t="inlineStr">
         <is>
           <t>① 출고창고·납품창고 항목 표시
 ② 유형·구매 거래처·매출 금액·제품그룹 등 판매현황 항목이 값과 함께 표시
 ③ 구분(SB/SCI)·주민등록번호(마스킹)·상병코드·횟수는 자사 데이터로 표시</t>
         </is>
       </c>
-      <c r="M34" s="27" t="inlineStr">
+      <c r="M36" s="43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N34" s="28" t="inlineStr"/>
-      <c r="O34" s="29" t="inlineStr"/>
-      <c r="P34" s="29" t="inlineStr"/>
-      <c r="Q34" s="29" t="inlineStr"/>
-      <c r="R34" s="29" t="inlineStr"/>
-      <c r="S34" s="28" t="inlineStr"/>
+      <c r="N36" s="28" t="inlineStr"/>
+      <c r="O36" s="29" t="inlineStr"/>
+      <c r="P36" s="29" t="inlineStr"/>
+      <c r="Q36" s="29" t="inlineStr"/>
+      <c r="R36" s="29" t="inlineStr"/>
+      <c r="S36" s="28" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S34"/>
-  <mergeCells count="57">
+  <autoFilter ref="A2:S36"/>
+  <mergeCells count="63">
     <mergeCell ref="F15:F16"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="B27:B28"/>
@@ -3687,7 +3813,9 @@
     <mergeCell ref="F25:F26"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C33:C34"/>
     <mergeCell ref="F12:F13"/>
+    <mergeCell ref="E33:E34"/>
     <mergeCell ref="C20:C23"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="A7:A8"/>
@@ -3707,18 +3835,22 @@
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E15:E16"/>
+    <mergeCell ref="F33:F34"/>
     <mergeCell ref="D12:D13"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="D15:D16"/>
     <mergeCell ref="E27:E28"/>
+    <mergeCell ref="D33:D34"/>
     <mergeCell ref="F27:F28"/>
+    <mergeCell ref="A33:A34"/>
     <mergeCell ref="C27:C28"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="D25:D26"/>
     <mergeCell ref="E7:E8"/>
+    <mergeCell ref="B33:B34"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
@@ -3739,7 +3871,7 @@
     <mergeCell ref="C5:C6"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="O3:O34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O3:O36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,N/A,Blocked"</formula1>
     </dataValidation>
   </dataValidations>
